--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -81,7 +81,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-09-20T12:32:45+08:00</t>
+    <t>2026-09-20T12:44:50+08:00</t>
   </si>
   <si>
     <t>周日023</t>
@@ -462,7 +462,7 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T12:37:45+08:00）</t>
+    <t>统计（截至 2026-09-20T12:44:50+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1559,16 +1559,16 @@
         <v>4.7</v>
       </c>
       <c r="H13" s="3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I13" s="3">
         <v>7.5</v>
       </c>
       <c r="J13" s="4">
-        <v>4.286</v>
+        <v>4.375</v>
       </c>
       <c r="K13" s="5">
-        <v>0.414</v>
+        <v>0.325</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -81,7 +81,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-09-20T12:44:50+08:00</t>
+    <t>2026-09-20T12:48:21+08:00</t>
   </si>
   <si>
     <t>周日023</t>
@@ -462,7 +462,7 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T12:44:50+08:00）</t>
+    <t>统计（截至 2026-09-20T12:48:21+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -81,7 +81,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-09-20T12:48:21+08:00</t>
+    <t>2026-09-20T13:00:45+08:00</t>
   </si>
   <si>
     <t>周日023</t>
@@ -462,7 +462,7 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T12:48:21+08:00）</t>
+    <t>统计（截至 2026-09-20T13:00:45+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="189">
   <si>
     <t>日期</t>
   </si>
@@ -81,129 +81,132 @@
     <t/>
   </si>
   <si>
+    <t>2026-09-20T14:32:26+08:00</t>
+  </si>
+  <si>
+    <t>周日023</t>
+  </si>
+  <si>
+    <t>西甲</t>
+  </si>
+  <si>
+    <t>比利亚雷</t>
+  </si>
+  <si>
+    <t>莱万特</t>
+  </si>
+  <si>
+    <t>09-21 00:30</t>
+  </si>
+  <si>
+    <t>周日024</t>
+  </si>
+  <si>
+    <t>拉科</t>
+  </si>
+  <si>
+    <t>贝蒂斯</t>
+  </si>
+  <si>
+    <t>周日025</t>
+  </si>
+  <si>
+    <t>德甲</t>
+  </si>
+  <si>
+    <t>帕德博恩</t>
+  </si>
+  <si>
+    <t>霍芬海姆</t>
+  </si>
+  <si>
+    <t>09-21 01:30</t>
+  </si>
+  <si>
+    <t>周日026</t>
+  </si>
+  <si>
+    <t>AC米兰</t>
+  </si>
+  <si>
+    <t>莱切</t>
+  </si>
+  <si>
+    <t>09-21 02:45</t>
+  </si>
+  <si>
+    <t>周日027</t>
+  </si>
+  <si>
+    <t>法甲</t>
+  </si>
+  <si>
+    <t>马赛</t>
+  </si>
+  <si>
+    <t>巴黎圣曼</t>
+  </si>
+  <si>
+    <t>周日028</t>
+  </si>
+  <si>
+    <t>巴伦西亚</t>
+  </si>
+  <si>
+    <t>皇家社会</t>
+  </si>
+  <si>
+    <t>09-21 03:00</t>
+  </si>
+  <si>
+    <t>周日029</t>
+  </si>
+  <si>
+    <t>葡超</t>
+  </si>
+  <si>
+    <t>波尔图</t>
+  </si>
+  <si>
+    <t>本菲卡</t>
+  </si>
+  <si>
+    <t>09-21 03:30</t>
+  </si>
+  <si>
+    <t>周日030</t>
+  </si>
+  <si>
+    <t>巴甲</t>
+  </si>
+  <si>
+    <t>巴竞技</t>
+  </si>
+  <si>
+    <t>巴伊亚</t>
+  </si>
+  <si>
+    <t>09-21 06:30</t>
+  </si>
+  <si>
+    <t>周日001</t>
+  </si>
+  <si>
+    <t>亚运男足</t>
+  </si>
+  <si>
+    <t>伊朗亚</t>
+  </si>
+  <si>
+    <t>中国亚</t>
+  </si>
+  <si>
+    <t>09-20 13:00</t>
+  </si>
+  <si>
     <t>2026-09-20T13:00:45+08:00</t>
   </si>
   <si>
-    <t>周日023</t>
-  </si>
-  <si>
-    <t>西甲</t>
-  </si>
-  <si>
-    <t>比利亚雷</t>
-  </si>
-  <si>
-    <t>莱万特</t>
-  </si>
-  <si>
-    <t>09-21 00:30</t>
-  </si>
-  <si>
-    <t>周日024</t>
-  </si>
-  <si>
-    <t>拉科</t>
-  </si>
-  <si>
-    <t>贝蒂斯</t>
-  </si>
-  <si>
-    <t>周日025</t>
-  </si>
-  <si>
-    <t>德甲</t>
-  </si>
-  <si>
-    <t>帕德博恩</t>
-  </si>
-  <si>
-    <t>霍芬海姆</t>
-  </si>
-  <si>
-    <t>09-21 01:30</t>
-  </si>
-  <si>
-    <t>周日026</t>
-  </si>
-  <si>
-    <t>AC米兰</t>
-  </si>
-  <si>
-    <t>莱切</t>
-  </si>
-  <si>
-    <t>09-21 02:45</t>
-  </si>
-  <si>
-    <t>周日027</t>
-  </si>
-  <si>
-    <t>法甲</t>
-  </si>
-  <si>
-    <t>马赛</t>
-  </si>
-  <si>
-    <t>巴黎圣曼</t>
-  </si>
-  <si>
-    <t>周日028</t>
-  </si>
-  <si>
-    <t>巴伦西亚</t>
-  </si>
-  <si>
-    <t>皇家社会</t>
-  </si>
-  <si>
-    <t>09-21 03:00</t>
-  </si>
-  <si>
-    <t>周日029</t>
-  </si>
-  <si>
-    <t>葡超</t>
-  </si>
-  <si>
-    <t>波尔图</t>
-  </si>
-  <si>
-    <t>本菲卡</t>
-  </si>
-  <si>
-    <t>09-21 03:30</t>
-  </si>
-  <si>
-    <t>周日030</t>
-  </si>
-  <si>
-    <t>巴甲</t>
-  </si>
-  <si>
-    <t>巴竞技</t>
-  </si>
-  <si>
-    <t>巴伊亚</t>
-  </si>
-  <si>
-    <t>09-21 06:30</t>
-  </si>
-  <si>
-    <t>周日001</t>
-  </si>
-  <si>
-    <t>亚运男足</t>
-  </si>
-  <si>
-    <t>伊朗亚</t>
-  </si>
-  <si>
-    <t>中国亚</t>
-  </si>
-  <si>
-    <t>09-20 13:00</t>
-  </si>
-  <si>
     <t>周日002</t>
   </si>
   <si>
@@ -462,7 +465,7 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T13:00:45+08:00）</t>
+    <t>统计（截至 2026-09-20T14:32:26+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1298,19 +1301,19 @@
         <v>39</v>
       </c>
       <c r="G7" s="3">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I7" s="3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J7" s="4">
-        <v>8</v>
+        <v>8.642</v>
       </c>
       <c r="K7" s="5">
-        <v>0.5</v>
+        <v>0.358</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1490,7 +1493,7 @@
         <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1498,19 +1501,19 @@
         <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3">
         <v>5.1</v>
@@ -1541,19 +1544,19 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G13" s="3">
         <v>4.7</v>
@@ -1584,22 +1587,22 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="3">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H14" s="3">
         <v>9.5</v>
@@ -1611,7 +1614,7 @@
         <v>4.401</v>
       </c>
       <c r="K14" s="5">
-        <v>0.299</v>
+        <v>0.499</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1627,19 +1630,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G15" s="3">
         <v>9.5</v>
@@ -1670,19 +1673,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G16" s="3">
         <v>5.1</v>
@@ -1713,19 +1716,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" s="3">
         <v>5.1</v>
@@ -1756,19 +1759,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G18" s="3">
         <v>3.45</v>
@@ -1799,34 +1802,34 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G19" s="3">
         <v>12</v>
       </c>
       <c r="H19" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="3">
         <v>19</v>
       </c>
       <c r="J19" s="4">
-        <v>10.405</v>
+        <v>10.605</v>
       </c>
       <c r="K19" s="5">
-        <v>1.595</v>
+        <v>1.395</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1842,19 +1845,19 @@
         <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3">
         <v>6</v>
@@ -1885,19 +1888,19 @@
         <v>15</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G21" s="3">
         <v>7.55</v>
@@ -1928,19 +1931,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G22" s="3">
         <v>6.1</v>
@@ -1971,22 +1974,22 @@
         <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G23" s="3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H23" s="3">
         <v>7.5</v>
@@ -1998,7 +2001,7 @@
         <v>3.409</v>
       </c>
       <c r="K23" s="5">
-        <v>0.291</v>
+        <v>0.391</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -2014,19 +2017,19 @@
         <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G24" s="3">
         <v>7.5</v>
@@ -2057,34 +2060,34 @@
         <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G25" s="3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H25" s="3">
         <v>17</v>
       </c>
       <c r="I25" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" s="4">
-        <v>9.59</v>
+        <v>9.775</v>
       </c>
       <c r="K25" s="5">
-        <v>0.41</v>
+        <v>0.725</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2100,34 +2103,34 @@
         <v>15</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G26" s="3">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="H26" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" s="3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J26" s="4">
-        <v>7.034</v>
+        <v>6.691</v>
       </c>
       <c r="K26" s="5">
-        <v>0.716</v>
+        <v>0.309</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2143,19 +2146,19 @@
         <v>15</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G27" s="3">
         <v>5.55</v>
@@ -2186,19 +2189,19 @@
         <v>15</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G28" s="3">
         <v>10</v>
@@ -2229,19 +2232,19 @@
         <v>15</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G29" s="3">
         <v>4.8</v>
@@ -2272,19 +2275,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G30" s="3">
         <v>6.7</v>
@@ -2315,34 +2318,34 @@
         <v>15</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G31" s="3">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="H31" s="3">
         <v>12</v>
       </c>
       <c r="I31" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4">
-        <v>6.667</v>
+        <v>6.857</v>
       </c>
       <c r="K31" s="5">
-        <v>0.333</v>
+        <v>0.643</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2355,22 +2358,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G32" s="3">
         <v>8.5</v>
@@ -2415,17 +2418,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B4">
         <v>31</v>
@@ -2433,7 +2436,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2441,7 +2444,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2449,7 +2452,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>21</v>
@@ -2457,57 +2460,57 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="9"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" s="9"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B10" s="9"/>
     </row>
     <row r="12" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2526,7 +2529,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2536,22 +2539,22 @@
     </row>
     <row r="3" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2561,17 +2564,17 @@
     </row>
     <row r="8" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2581,27 +2584,27 @@
     </row>
     <row r="12" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -2611,32 +2614,32 @@
     </row>
     <row r="18" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -2646,17 +2649,17 @@
     </row>
     <row r="25" spans="1:1" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="241">
   <si>
     <t>日期</t>
   </si>
@@ -327,6 +327,9 @@
     <t>09-20 22:15</t>
   </si>
   <si>
+    <t>09-20 19:05 / 09-20 19:17</t>
+  </si>
+  <si>
     <t>周日017</t>
   </si>
   <si>
@@ -519,7 +522,7 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T19:05:58+08:00）</t>
+    <t>统计（截至 2026-09-20T19:17:17+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -2310,7 +2313,7 @@
         <v>84</v>
       </c>
       <c r="H17" s="3">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="I17" s="3">
         <v>16</v>
@@ -2322,7 +2325,7 @@
         <v>6.691</v>
       </c>
       <c r="L17" s="5">
-        <v>0.309</v>
+        <v>0.559</v>
       </c>
       <c r="M17" s="3">
         <v>7.25</v>
@@ -2339,14 +2342,14 @@
       <c r="Q17" s="5">
         <v>0.559</v>
       </c>
-      <c r="R17" s="9" t="s">
-        <v>88</v>
+      <c r="R17" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="S17" s="4">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="U17" s="2" t="s">
         <v>30</v>
@@ -2366,19 +2369,19 @@
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>32</v>
@@ -2428,19 +2431,19 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>32</v>
@@ -2502,19 +2505,19 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>32</v>
@@ -2576,19 +2579,19 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>84</v>
@@ -2638,19 +2641,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>32</v>
@@ -2700,19 +2703,19 @@
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>32</v>
@@ -2774,19 +2777,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>32</v>
@@ -2848,19 +2851,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>32</v>
@@ -2922,19 +2925,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>96</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>32</v>
@@ -2996,19 +2999,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>32</v>
@@ -3070,19 +3073,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>32</v>
@@ -3144,19 +3147,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>32</v>
@@ -3218,19 +3221,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>32</v>
@@ -3239,16 +3242,16 @@
         <v>5.05</v>
       </c>
       <c r="I30" s="3">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="J30" s="3">
         <v>8.5</v>
       </c>
       <c r="K30" s="4">
-        <v>4.371</v>
+        <v>4.43</v>
       </c>
       <c r="L30" s="5">
-        <v>0.679</v>
+        <v>0.62</v>
       </c>
       <c r="M30" s="3">
         <v>5.05</v>
@@ -3265,14 +3268,14 @@
       <c r="Q30" s="5">
         <v>0.62</v>
       </c>
-      <c r="R30" s="7" t="s">
-        <v>68</v>
+      <c r="R30" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="S30" s="4">
-        <v>-0.059</v>
+        <v>0</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>30</v>
@@ -3292,19 +3295,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>32</v>
@@ -3363,22 +3366,22 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -3442,17 +3445,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B4">
         <v>31</v>
@@ -3460,7 +3463,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B5">
         <v>19</v>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -3476,7 +3479,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3484,7 +3487,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B8" s="12">
         <v>0</v>
@@ -3492,7 +3495,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B9" s="13">
         <v>0.403</v>
@@ -3500,13 +3503,13 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="13"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" s="13">
         <v>0.403</v>
@@ -3514,32 +3517,32 @@
     </row>
     <row r="13" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3557,7 +3560,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16">
         <v>20</v>
@@ -3575,37 +3578,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3625,7 +3628,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3641,7 +3644,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3657,7 +3660,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3673,7 +3676,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3689,7 +3692,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3705,7 +3708,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3721,7 +3724,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3737,7 +3740,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -3753,7 +3756,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3769,7 +3772,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -3805,7 +3808,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -3821,32 +3824,32 @@
     </row>
     <row r="35" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3862,7 +3865,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3878,7 +3881,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3894,7 +3897,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3910,7 +3913,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3926,12 +3929,12 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -3950,7 +3953,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -3960,22 +3963,22 @@
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3985,17 +3988,17 @@
     </row>
     <row r="8" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -4005,32 +4008,32 @@
     </row>
     <row r="12" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -4040,22 +4043,22 @@
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -4065,27 +4068,27 @@
     </row>
     <row r="24" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -4095,17 +4098,17 @@
     </row>
     <row r="30" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="266">
   <si>
     <t>日期</t>
   </si>
@@ -114,7 +114,7 @@
     <t>否</t>
   </si>
   <si>
-    <t>09-20 19:05</t>
+    <t>09-21 11:00</t>
   </si>
   <si>
     <t>周日002</t>
@@ -150,6 +150,12 @@
     <t>神户胜利</t>
   </si>
   <si>
+    <t>0:1</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
     <t>周日004</t>
   </si>
   <si>
@@ -165,6 +171,9 @@
     <t>09-20 18:00</t>
   </si>
   <si>
+    <t>1:1</t>
+  </si>
+  <si>
     <t>周日005</t>
   </si>
   <si>
@@ -177,6 +186,12 @@
     <t>09-20 18:30</t>
   </si>
   <si>
+    <t>0:7</t>
+  </si>
+  <si>
+    <t>0:3</t>
+  </si>
+  <si>
     <t>周日006</t>
   </si>
   <si>
@@ -243,6 +258,12 @@
     <t>→</t>
   </si>
   <si>
+    <t>3:2</t>
+  </si>
+  <si>
+    <t>1:2</t>
+  </si>
+  <si>
     <t>周日010</t>
   </si>
   <si>
@@ -267,9 +288,6 @@
     <t>利物浦</t>
   </si>
   <si>
-    <t>是</t>
-  </si>
-  <si>
     <t>周日012</t>
   </si>
   <si>
@@ -282,6 +300,9 @@
     <t>↑</t>
   </si>
   <si>
+    <t>5:3</t>
+  </si>
+  <si>
     <t>周日013</t>
   </si>
   <si>
@@ -291,6 +312,9 @@
     <t>热那亚</t>
   </si>
   <si>
+    <t>2:1</t>
+  </si>
+  <si>
     <t>周日014</t>
   </si>
   <si>
@@ -300,6 +324,9 @@
     <t>科莫</t>
   </si>
   <si>
+    <t>2:0</t>
+  </si>
+  <si>
     <t>周日015</t>
   </si>
   <si>
@@ -360,6 +387,9 @@
     <t>09-20 23:00</t>
   </si>
   <si>
+    <t>3:0</t>
+  </si>
+  <si>
     <t>周日019</t>
   </si>
   <si>
@@ -522,7 +552,10 @@
     <t>09-21 15:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-20T19:17:17+08:00）</t>
+    <t>09-20 14:32 / 09-21 11:00</t>
+  </si>
+  <si>
+    <t>统计（截至 2026-09-21T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -628,6 +661,48 @@
   </si>
   <si>
     <t>0.70 ~ 0.75</t>
+  </si>
+  <si>
+    <t>0.75 ~ 0.80</t>
+  </si>
+  <si>
+    <t>0.80 ~ 0.85</t>
+  </si>
+  <si>
+    <t>0.85 ~ 0.90</t>
+  </si>
+  <si>
+    <t>0.90 ~ 0.95</t>
+  </si>
+  <si>
+    <t>0.95 ~ 1.00</t>
+  </si>
+  <si>
+    <t>1.00 ~ 1.05</t>
+  </si>
+  <si>
+    <t>1.05 ~ 1.10</t>
+  </si>
+  <si>
+    <t>1.10 ~ 1.15</t>
+  </si>
+  <si>
+    <t>1.15 ~ 1.20</t>
+  </si>
+  <si>
+    <t>1.20 ~ 1.25</t>
+  </si>
+  <si>
+    <t>1.25 ~ 1.30</t>
+  </si>
+  <si>
+    <t>1.30 ~ 1.35</t>
+  </si>
+  <si>
+    <t>1.35 ~ 1.40</t>
+  </si>
+  <si>
+    <t>1.40 ~ 1.45</t>
   </si>
   <si>
     <t>差值变化分布 ①→②（第二次 − 第一次，按赛果分组）</t>
@@ -1450,16 +1525,16 @@
         <v>39</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W4" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -1467,19 +1542,19 @@
         <v>24</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>30</v>
@@ -1512,16 +1587,16 @@
         <v>39</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W5" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
@@ -1529,19 +1604,19 @@
         <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>30</v>
@@ -1574,16 +1649,16 @@
         <v>39</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="W6" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
@@ -1591,19 +1666,19 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
@@ -1636,16 +1711,16 @@
         <v>39</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W7" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -1653,19 +1728,19 @@
         <v>24</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>30</v>
@@ -1698,16 +1773,16 @@
         <v>39</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W8" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
@@ -1715,19 +1790,19 @@
         <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>32</v>
@@ -1763,25 +1838,25 @@
         <v>0.317</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="S9" s="4">
         <v>-0.028</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
@@ -1789,19 +1864,19 @@
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>32</v>
@@ -1837,25 +1912,25 @@
         <v>1.395</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S10" s="4">
         <v>0</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="W10" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
@@ -1863,19 +1938,19 @@
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>32</v>
@@ -1911,25 +1986,25 @@
         <v>0.677</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S11" s="4">
         <v>0</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W11" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
@@ -1937,22 +2012,22 @@
         <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H12" s="3">
         <v>7.55</v>
@@ -1982,16 +2057,16 @@
         <v>39</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W12" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
@@ -1999,19 +2074,19 @@
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>32</v>
@@ -2047,25 +2122,25 @@
         <v>0.731</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S13" s="4">
         <v>0.4</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
+      </c>
+      <c r="W13" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2073,19 +2148,19 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>32</v>
@@ -2121,25 +2196,25 @@
         <v>0.44</v>
       </c>
       <c r="R14" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S14" s="4">
         <v>0.049</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W14" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W14" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
@@ -2147,19 +2222,19 @@
         <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>32</v>
@@ -2195,25 +2270,25 @@
         <v>1.259</v>
       </c>
       <c r="R15" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S15" s="4">
         <v>0.2</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W15" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
@@ -2221,19 +2296,19 @@
         <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>32</v>
@@ -2269,25 +2344,25 @@
         <v>1.049</v>
       </c>
       <c r="R16" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S16" s="4">
         <v>0.324</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W16" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2295,22 +2370,22 @@
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H17" s="3">
         <v>7.25</v>
@@ -2343,25 +2418,25 @@
         <v>0.559</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S17" s="4">
         <v>0</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W17" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
@@ -2369,19 +2444,19 @@
         <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>32</v>
@@ -2414,16 +2489,16 @@
         <v>39</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W18" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
@@ -2431,19 +2506,19 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>32</v>
@@ -2479,25 +2554,25 @@
         <v>0.758</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="S19" s="4">
         <v>-0.172</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W19" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W19" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
@@ -2505,19 +2580,19 @@
         <v>24</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>32</v>
@@ -2553,25 +2628,25 @@
         <v>1.041</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S20" s="4">
         <v>0.7</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W20" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2579,22 +2654,22 @@
         <v>24</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H21" s="3">
         <v>6.7</v>
@@ -2624,16 +2699,16 @@
         <v>39</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W21" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -2641,19 +2716,19 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>32</v>
@@ -2686,16 +2761,16 @@
         <v>39</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W22" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -2703,19 +2778,19 @@
         <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>32</v>
@@ -2751,13 +2826,13 @@
         <v>0.344</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S23" s="4">
         <v>0</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>30</v>
@@ -2777,19 +2852,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>32</v>
@@ -2825,13 +2900,13 @@
         <v>0.891</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S24" s="4">
         <v>0.058</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>30</v>
@@ -2851,19 +2926,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>32</v>
@@ -2899,13 +2974,13 @@
         <v>0.624</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S25" s="4">
         <v>0</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>30</v>
@@ -2925,19 +3000,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>32</v>
@@ -2973,13 +3048,13 @@
         <v>1.029</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="S26" s="4">
         <v>0.35</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>30</v>
@@ -2999,19 +3074,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>32</v>
@@ -3047,13 +3122,13 @@
         <v>0.281</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S27" s="4">
         <v>0</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U27" s="2" t="s">
         <v>30</v>
@@ -3073,19 +3148,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>32</v>
@@ -3121,13 +3196,13 @@
         <v>0.358</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S28" s="4">
         <v>0</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U28" s="2" t="s">
         <v>30</v>
@@ -3147,19 +3222,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>32</v>
@@ -3195,13 +3270,13 @@
         <v>0.614</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S29" s="4">
         <v>0</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>30</v>
@@ -3221,19 +3296,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>32</v>
@@ -3269,13 +3344,13 @@
         <v>0.62</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S30" s="4">
         <v>0</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>30</v>
@@ -3295,19 +3370,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>32</v>
@@ -3343,13 +3418,13 @@
         <v>0.362</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S31" s="4">
         <v>0</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>30</v>
@@ -3366,22 +3441,22 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -3401,17 +3476,29 @@
       <c r="L32" s="5">
         <v>0.582</v>
       </c>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S32" s="4"/>
+      <c r="M32" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="N32" s="3">
+        <v>9.25</v>
+      </c>
+      <c r="O32" s="3">
+        <v>50</v>
+      </c>
+      <c r="P32" s="4">
+        <v>7.806</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>0.394</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S32" s="4">
+        <v>-0.188</v>
+      </c>
       <c r="T32" s="2" t="s">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>30</v>
@@ -3435,7 +3522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3445,17 +3532,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B4">
         <v>31</v>
@@ -3463,95 +3550,97 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B8" s="12">
-        <v>0</v>
+        <v>0.19047619047619047</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B9" s="13">
-        <v>0.403</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
-      </c>
-      <c r="B10" s="13"/>
+        <v>188</v>
+      </c>
+      <c r="B10" s="13">
+        <v>0.355</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B11" s="13">
-        <v>0.403</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13">
@@ -3560,16 +3649,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B16">
         <v>20</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13">
@@ -3578,37 +3667,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3628,7 +3717,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3644,23 +3733,27 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="12">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13">
+        <v>0.245</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3676,180 +3769,239 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="13"/>
+      <c r="E25" s="12">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13">
+        <v>0.321</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E26" s="12">
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E27" s="12">
+        <v>0</v>
+      </c>
+      <c r="F27" s="13">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E28" s="12">
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <v>0.499</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
-      <c r="E29" s="12"/>
-      <c r="F29" s="13"/>
+      <c r="E29" s="12">
+        <v>1</v>
+      </c>
+      <c r="F29" s="13">
+        <v>0.532</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="E30" s="12">
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
+        <v>0.561</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
-      </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E31" s="12">
+        <v>0</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0.643</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="12">
         <v>0</v>
       </c>
       <c r="F32" s="13">
-        <v>0.682</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="35" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>207</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E33" s="12">
+        <v>0</v>
+      </c>
+      <c r="F33" s="13">
+        <v>0.731</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" s="12">
+        <v>0</v>
+      </c>
+      <c r="F34" s="13">
+        <v>0.758</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="13"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3861,11 +4013,11 @@
         <v>0</v>
       </c>
       <c r="E37" s="12"/>
-      <c r="F37" s="16"/>
+      <c r="F37" s="13"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3877,27 +4029,31 @@
         <v>0</v>
       </c>
       <c r="E38" s="12"/>
-      <c r="F38" s="16"/>
+      <c r="F38" s="13"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" s="12"/>
-      <c r="F39" s="16"/>
+        <v>2</v>
+      </c>
+      <c r="E39" s="12">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>1.045</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -3909,11 +4065,11 @@
         <v>0</v>
       </c>
       <c r="E40" s="12"/>
-      <c r="F40" s="16"/>
+      <c r="F40" s="13"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -3925,16 +4081,245 @@
         <v>0</v>
       </c>
       <c r="E41" s="12"/>
-      <c r="F41" s="16"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>224</v>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="13"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" s="12"/>
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>226</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" s="12">
+        <v>0</v>
+      </c>
+      <c r="F44" s="13">
+        <v>1.259</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" s="12">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1.318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" s="12">
+        <v>0</v>
+      </c>
+      <c r="F46" s="13">
+        <v>1.395</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47" s="12"/>
+      <c r="F47" s="13"/>
+    </row>
+    <row r="49" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>233</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12">
+        <v>0</v>
+      </c>
+      <c r="F51" s="16">
+        <v>-0.172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>234</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52" s="12"/>
+      <c r="F52" s="16"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>235</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="F53" s="16">
+        <v>-0.007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>236</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" s="12">
+        <v>0</v>
+      </c>
+      <c r="F54" s="16">
+        <v>0.049</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>237</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" s="12">
+        <v>0</v>
+      </c>
+      <c r="F55" s="16">
+        <v>0.406</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3953,7 +4338,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -3963,22 +4348,22 @@
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -3988,17 +4373,17 @@
     </row>
     <row r="8" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -4008,32 +4393,32 @@
     </row>
     <row r="12" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -4043,22 +4428,22 @@
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -4068,27 +4453,27 @@
     </row>
     <row r="24" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -4098,17 +4483,17 @@
     </row>
     <row r="30" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="279">
   <si>
     <t>日期</t>
   </si>
@@ -555,7 +555,46 @@
     <t>09-20 14:32 / 09-21 11:00</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-21T11:00:04+08:00）</t>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>周二002</t>
+  </si>
+  <si>
+    <t>英锦标赛</t>
+  </si>
+  <si>
+    <t>米尔顿</t>
+  </si>
+  <si>
+    <t>克劳利</t>
+  </si>
+  <si>
+    <t>09-23 02:00</t>
+  </si>
+  <si>
+    <t>09-21 17:00</t>
+  </si>
+  <si>
+    <t>周二003</t>
+  </si>
+  <si>
+    <t>诺茨郡</t>
+  </si>
+  <si>
+    <t>格里姆</t>
+  </si>
+  <si>
+    <t>周二004</t>
+  </si>
+  <si>
+    <t>维冈</t>
+  </si>
+  <si>
+    <t>布莱克浦</t>
+  </si>
+  <si>
+    <t>统计（截至 2026-09-21T17:00:03+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1260,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3510,6 +3549,192 @@
         <v>30</v>
       </c>
       <c r="X32" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="3">
+        <v>8.35</v>
+      </c>
+      <c r="I33" s="3">
+        <v>12</v>
+      </c>
+      <c r="J33" s="3">
+        <v>22</v>
+      </c>
+      <c r="K33" s="4">
+        <v>7.765</v>
+      </c>
+      <c r="L33" s="5">
+        <v>0.585</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S33" s="4"/>
+      <c r="T33" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="I34" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="J34" s="3">
+        <v>13</v>
+      </c>
+      <c r="K34" s="4">
+        <v>5.809</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.391</v>
+      </c>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S34" s="4"/>
+      <c r="T34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X34" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7</v>
+      </c>
+      <c r="I35" s="3">
+        <v>12</v>
+      </c>
+      <c r="J35" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="K35" s="4">
+        <v>6.566</v>
+      </c>
+      <c r="L35" s="5">
+        <v>0.434</v>
+      </c>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S35" s="4"/>
+      <c r="T35" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X35" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3532,25 +3757,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B4">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -3558,7 +3783,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B6">
         <v>21</v>
@@ -3566,7 +3791,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -3574,7 +3799,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B8" s="12">
         <v>0.19047619047619047</v>
@@ -3582,7 +3807,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B9" s="13">
         <v>0.68</v>
@@ -3590,7 +3815,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B10" s="13">
         <v>0.355</v>
@@ -3598,7 +3823,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B11" s="13">
         <v>0.756</v>
@@ -3606,32 +3831,32 @@
     </row>
     <row r="13" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3649,10 +3874,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>11</v>
@@ -3662,42 +3887,42 @@
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3717,7 +3942,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3733,7 +3958,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -3753,7 +3978,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3769,7 +3994,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -3789,7 +4014,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -3809,7 +4034,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -3829,7 +4054,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -3849,7 +4074,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -3869,7 +4094,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -3889,7 +4114,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -3909,7 +4134,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -3929,7 +4154,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -3949,7 +4174,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -3969,7 +4194,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3985,7 +4210,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -4001,7 +4226,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4017,7 +4242,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4033,7 +4258,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -4053,7 +4278,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4069,7 +4294,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4085,7 +4310,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4101,7 +4326,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4117,7 +4342,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -4137,7 +4362,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -4157,7 +4382,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -4177,7 +4402,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4193,32 +4418,32 @@
     </row>
     <row r="49" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -4238,7 +4463,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4254,7 +4479,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B53">
         <v>4</v>
@@ -4274,7 +4499,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -4294,7 +4519,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -4314,12 +4539,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4338,7 +4563,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4348,22 +4573,22 @@
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -4373,17 +4598,17 @@
     </row>
     <row r="8" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -4393,32 +4618,32 @@
     </row>
     <row r="12" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -4428,22 +4653,22 @@
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -4453,27 +4678,27 @@
     </row>
     <row r="24" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -4483,17 +4708,17 @@
     </row>
     <row r="30" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="281">
   <si>
     <t>日期</t>
   </si>
@@ -114,7 +114,7 @@
     <t>否</t>
   </si>
   <si>
-    <t>09-21 11:00</t>
+    <t>09-21 18:12</t>
   </si>
   <si>
     <t>周日002</t>
@@ -450,6 +450,9 @@
     <t>09-21 00:30</t>
   </si>
   <si>
+    <t>3:1</t>
+  </si>
+  <si>
     <t>周日024</t>
   </si>
   <si>
@@ -504,6 +507,9 @@
     <t>09-21 03:00</t>
   </si>
   <si>
+    <t>2:3</t>
+  </si>
+  <si>
     <t>周日029</t>
   </si>
   <si>
@@ -594,7 +600,7 @@
     <t>布莱克浦</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-21T17:00:03+08:00）</t>
+    <t>统计（截至 2026-09-21T18:12:48+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -922,7 +928,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -960,6 +966,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2874,16 +2881,16 @@
         <v>74</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W23" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
@@ -2948,16 +2955,16 @@
         <v>74</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W24" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
@@ -2965,16 +2972,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>144</v>
@@ -3022,16 +3029,16 @@
         <v>74</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W25" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
@@ -3039,19 +3046,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>32</v>
@@ -3096,16 +3103,16 @@
         <v>74</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W26" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -3113,19 +3120,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>32</v>
@@ -3170,16 +3177,16 @@
         <v>74</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W27" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
@@ -3187,19 +3194,19 @@
         <v>24</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>126</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>32</v>
@@ -3244,16 +3251,16 @@
         <v>74</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W28" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -3261,19 +3268,19 @@
         <v>24</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>32</v>
@@ -3318,16 +3325,16 @@
         <v>74</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W29" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -3335,19 +3342,19 @@
         <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>32</v>
@@ -3392,16 +3399,16 @@
         <v>113</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W30" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -3409,19 +3416,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>32</v>
@@ -3466,36 +3473,36 @@
         <v>74</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W31" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>30</v>
@@ -3537,7 +3544,7 @@
         <v>-0.188</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>30</v>
@@ -3554,22 +3561,22 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>32</v>
@@ -3599,7 +3606,7 @@
       </c>
       <c r="S33" s="4"/>
       <c r="T33" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>30</v>
@@ -3616,22 +3623,22 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>32</v>
@@ -3661,7 +3668,7 @@
       </c>
       <c r="S34" s="4"/>
       <c r="T34" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>30</v>
@@ -3678,22 +3685,22 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>32</v>
@@ -3723,7 +3730,7 @@
       </c>
       <c r="S35" s="4"/>
       <c r="T35" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>30</v>
@@ -3757,17 +3764,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -3775,7 +3782,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -3783,15 +3790,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B6">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -3799,23 +3806,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B8" s="12">
-        <v>0.19047619047619047</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B9" s="13">
-        <v>0.68</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B10" s="13">
         <v>0.355</v>
@@ -3823,40 +3830,40 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B11" s="13">
-        <v>0.756</v>
+        <v>0.691</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3874,13 +3881,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B16">
         <v>23</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -3892,37 +3899,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -3942,7 +3949,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3958,7 +3965,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -3978,52 +3985,56 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E24" s="12">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <v>0.281</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="12">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F25" s="13">
-        <v>0.321</v>
+        <v>0.329</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" s="12">
         <v>0</v>
@@ -4034,7 +4045,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4054,7 +4065,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4074,7 +4085,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4094,7 +4105,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4114,27 +4125,27 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" s="12">
         <v>0</v>
       </c>
       <c r="F31" s="13">
-        <v>0.643</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4154,7 +4165,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4174,7 +4185,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -4194,7 +4205,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4210,23 +4221,27 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E36" s="12">
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <v>0.891</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -4242,7 +4257,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -4258,27 +4273,27 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" s="12">
         <v>0</v>
       </c>
       <c r="F39" s="13">
-        <v>1.045</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -4294,7 +4309,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -4310,7 +4325,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -4326,7 +4341,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -4342,7 +4357,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -4362,7 +4377,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -4382,7 +4397,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -4402,7 +4417,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -4418,32 +4433,32 @@
     </row>
     <row r="49" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -4463,7 +4478,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -4479,72 +4494,72 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>3</v>
-      </c>
-      <c r="E53" s="12">
-        <v>0.25</v>
+        <v>10</v>
+      </c>
+      <c r="E53" s="17">
+        <v>0.09090909090909091</v>
       </c>
       <c r="F53" s="16">
-        <v>-0.007</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="12">
         <v>0</v>
       </c>
       <c r="F54" s="16">
-        <v>0.049</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>4</v>
-      </c>
-      <c r="E55" s="12">
+        <v>5</v>
+      </c>
+      <c r="E55" s="17">
         <v>0</v>
       </c>
       <c r="F55" s="16">
-        <v>0.406</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -4563,7 +4578,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4573,22 +4588,22 @@
     </row>
     <row r="3" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -4598,17 +4613,17 @@
     </row>
     <row r="8" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -4618,32 +4633,32 @@
     </row>
     <row r="12" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -4653,22 +4668,22 @@
     </row>
     <row r="19" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -4678,27 +4693,27 @@
     </row>
     <row r="24" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -4708,17 +4723,17 @@
     </row>
     <row r="30" spans="1:1" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="314">
   <si>
     <t>日期</t>
   </si>
@@ -659,43 +659,31 @@
     <t>数据范围：2025-08-17 ~ 2026-09-21（共 380 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
   </si>
   <si>
-    <t>编号追踪：单元格 = 该编号该进球数"距今未出现天数"（截至 2026-09-21，警戒线 30 天）</t>
-  </si>
-  <si>
-    <t>⚠ 达到警戒线的项目（按"该出指数"排序：距今 ÷ 历史平均间隔，越大概率上越"该出"）</t>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-21，警戒线 30 次）</t>
+  </si>
+  <si>
+    <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
   </si>
   <si>
     <t>进球数</t>
   </si>
   <si>
-    <t>距今天数</t>
-  </si>
-  <si>
-    <t>历史平均间隔(天)</t>
-  </si>
-  <si>
-    <t>该出指数</t>
+    <t>连续未出现(次)</t>
   </si>
   <si>
     <t>最近出现</t>
   </si>
   <si>
-    <t>连续未出现(次)</t>
-  </si>
-  <si>
     <t>历史次数</t>
   </si>
   <si>
     <t>2026-05-30</t>
   </si>
   <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>全部编号 × 进球数矩阵（数字=距今未出现天数；"从未"=历史数据中未出现过）</t>
-  </si>
-  <si>
-    <t>统计（截至 2026-09-21T18:39:18+08:00）</t>
+    <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
+  </si>
+  <si>
+    <t>统计（截至 2026-09-21T18:52:08+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -935,19 +923,16 @@
     <t xml:space="preserve">  · 每场比赛按编号（001 起）记录赛后实际总进球数（见「编号统计」表）。</t>
   </si>
   <si>
-    <t xml:space="preserve">  · 当某个编号的某个进球数连续超过警戒线（config.json 的 alertDays，默认 30 天）没有出现时，</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    网页顶部会弹出横幅提醒，运行日志也会记录 —— 用于持续关注"该出了"的编号 × 进球数组合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 「距今」按日历天计（到最近数据日）；「连续未出现」按该编号实际出现的次数计；</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    只对近期仍活跃（近 7 天出现过）的编号、且历史上出现过至少一次的组合进入警戒。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  · 「编号追踪」表中：红色 = 超警戒，橙色 = 接近警戒（60%），从未 = 历史数据中未出现过。</t>
+    <t xml:space="preserve">  · 预警口径为「连续未出现次数」：该编号每踢一场而没打出该档进球数计 1 次（编号当天没有比赛不计入），</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    达到警戒线（config.json 的 alertCount，默认 30 次）即触发提醒（网页横幅/运行日志/油猴浮窗）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 只对近期仍活跃（近 7 天出现过）的编号、且历史上出现过至少一次的分档进入警戒。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  · 「编号追踪」表中：数字 = 连续未出现次数；红色 = 超警戒，橙色 = 接近警戒（60%），从未 = 历史数据中未出现过。</t>
   </si>
   <si>
     <t>【数据来源与口径】</t>
@@ -1037,12 +1022,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -1094,10 +1079,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3930,7 +3915,7 @@
         <v>203</v>
       </c>
       <c r="B2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C2">
         <v>18</v>
@@ -3948,7 +3933,7 @@
         <v>41</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -4198,7 +4183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4214,7 +4199,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>195</v>
       </c>
@@ -4230,17 +4215,8 @@
       <c r="E4" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F4" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>210</v>
       </c>
@@ -4248,110 +4224,98 @@
         <v>197</v>
       </c>
       <c r="C5" s="13">
-        <v>114</v>
-      </c>
-      <c r="D5" s="13">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>220</v>
       </c>
       <c r="E5" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="13">
-        <v>35</v>
-      </c>
-      <c r="H5" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C6" s="13">
-        <v>33</v>
-      </c>
-      <c r="D6" s="13">
-        <v>21</v>
-      </c>
-      <c r="E6" s="13">
-        <v>1.6</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G6" s="13">
-        <v>25</v>
-      </c>
-      <c r="H6" s="13">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="C8" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D8" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="2">
+        <v>204</v>
+      </c>
+      <c r="B10" s="15">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
-        <v>13</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
       <c r="F10" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G10" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="15">
-        <v>33</v>
+        <v>205</v>
+      </c>
+      <c r="B11" s="2">
+        <v>10</v>
       </c>
       <c r="C11" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
@@ -4368,33 +4332,33 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="2">
-        <v>13</v>
+        <v>206</v>
+      </c>
+      <c r="B12" s="15">
+        <v>21</v>
       </c>
       <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="2">
-        <v>3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>6</v>
-      </c>
-      <c r="F12" s="16">
-        <v>20</v>
-      </c>
       <c r="G12" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="16">
-        <v>27</v>
+        <v>207</v>
+      </c>
+      <c r="B13" s="2">
+        <v>5</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -4402,152 +4366,129 @@
       <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="16">
-        <v>22</v>
+      <c r="E13" s="2">
+        <v>12</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
       </c>
       <c r="G13" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B15" s="2">
-        <v>8</v>
-      </c>
-      <c r="C15" s="16">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
       </c>
       <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
+      <c r="F15" s="2">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2">
         <v>2</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="2">
-        <v>13</v>
+        <v>210</v>
+      </c>
+      <c r="B16" s="16">
+        <v>35</v>
       </c>
       <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2">
+        <v>11</v>
+      </c>
+      <c r="G16" s="2">
         <v>1</v>
-      </c>
-      <c r="D16" s="2">
-        <v>4</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2">
-        <v>9</v>
-      </c>
-      <c r="G16" s="2">
-        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B17" s="15">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2">
+        <v>16</v>
+      </c>
+      <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2">
-        <v>15</v>
+      <c r="F17" s="15">
+        <v>19</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B18" s="16">
-        <v>24</v>
+        <v>212</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
-      </c>
-      <c r="D18" s="16">
-        <v>22</v>
+        <v>13</v>
+      </c>
+      <c r="D18" s="2">
+        <v>10</v>
       </c>
       <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="16">
-        <v>25</v>
-      </c>
       <c r="G18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1</v>
-      </c>
-      <c r="C19" s="16">
-        <v>19</v>
-      </c>
-      <c r="D19" s="2">
-        <v>15</v>
-      </c>
-      <c r="E19" s="2">
-        <v>2</v>
-      </c>
-      <c r="F19" s="2">
-        <v>3</v>
-      </c>
-      <c r="G19" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4568,17 +4509,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -4586,7 +4527,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -4594,7 +4535,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B6">
         <v>30</v>
@@ -4602,7 +4543,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4610,7 +4551,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B8" s="18">
         <v>0.13333333333333333</v>
@@ -4618,7 +4559,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B9" s="19">
         <v>0.647</v>
@@ -4626,7 +4567,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4634,7 +4575,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B11" s="19">
         <v>0.691</v>
@@ -4642,32 +4583,32 @@
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -4685,7 +4626,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B16">
         <v>23</v>
@@ -4703,37 +4644,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4753,7 +4694,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4769,7 +4710,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -4789,7 +4730,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4809,7 +4750,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4829,7 +4770,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -4849,7 +4790,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4869,7 +4810,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4889,7 +4830,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4909,7 +4850,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4929,7 +4870,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4949,7 +4890,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4969,7 +4910,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4989,7 +4930,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5009,7 +4950,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5025,7 +4966,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5045,7 +4986,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5061,7 +5002,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5077,7 +5018,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -5097,7 +5038,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5113,7 +5054,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5129,7 +5070,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5145,7 +5086,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5161,7 +5102,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5181,7 +5122,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5201,7 +5142,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5221,7 +5162,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5237,32 +5178,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -5282,7 +5223,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5298,7 +5239,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B53">
         <v>11</v>
@@ -5318,7 +5259,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5338,7 +5279,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -5358,12 +5299,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -5374,7 +5315,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="112" customWidth="1"/>
@@ -5382,7 +5323,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5392,22 +5333,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5417,17 +5358,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5437,32 +5378,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5472,22 +5413,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5497,87 +5438,82 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
-        <v>311</v>
+    <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>316</v>
+    <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="315">
   <si>
     <t>日期</t>
   </si>
@@ -656,7 +656,7 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-21（共 380 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-21（共 378 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
   </si>
   <si>
     <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-21，警戒线 30 次）</t>
@@ -677,13 +677,16 @@
     <t>历史次数</t>
   </si>
   <si>
-    <t>2026-05-30</t>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-21T18:52:08+08:00）</t>
+    <t>统计（截至 2026-09-21T19:01:33+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1022,12 +1025,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1079,10 +1082,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3915,25 +3918,25 @@
         <v>203</v>
       </c>
       <c r="B2">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E2">
+        <v>67</v>
+      </c>
+      <c r="F2">
+        <v>67</v>
+      </c>
+      <c r="G2">
+        <v>51</v>
+      </c>
+      <c r="H2">
         <v>57</v>
-      </c>
-      <c r="F2">
-        <v>58</v>
-      </c>
-      <c r="G2">
-        <v>41</v>
-      </c>
-      <c r="H2">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3941,25 +3944,25 @@
         <v>204</v>
       </c>
       <c r="B3">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F3">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="H3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3967,25 +3970,25 @@
         <v>205</v>
       </c>
       <c r="B4">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="E4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F4">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G4">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H4">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3993,25 +3996,25 @@
         <v>206</v>
       </c>
       <c r="B5">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="F5">
+        <v>52</v>
+      </c>
+      <c r="G5">
         <v>62</v>
       </c>
-      <c r="F5">
-        <v>41</v>
-      </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
       <c r="H5">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4019,25 +4022,25 @@
         <v>207</v>
       </c>
       <c r="B6">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E6">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H6">
-        <v>35</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -4045,25 +4048,25 @@
         <v>208</v>
       </c>
       <c r="B7">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G7">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H7">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -4071,25 +4074,25 @@
         <v>209</v>
       </c>
       <c r="B8">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="F8">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G8">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H8">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -4097,25 +4100,25 @@
         <v>210</v>
       </c>
       <c r="B9">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D9">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E9">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F9">
+        <v>59</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+      <c r="H9">
         <v>48</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -4123,25 +4126,25 @@
         <v>211</v>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="C10">
         <v>11</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E10">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H10">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -4149,25 +4152,25 @@
         <v>212</v>
       </c>
       <c r="B11">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F11">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G11">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H11">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -4183,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4224,84 +4227,78 @@
         <v>197</v>
       </c>
       <c r="C5" s="13">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>220</v>
       </c>
       <c r="E5" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" s="13">
+        <v>33</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="E6" s="13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B9" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G9" s="11" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>11</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2">
-        <v>13</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B10" s="15">
-        <v>25</v>
+        <v>203</v>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -4309,186 +4306,209 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B11" s="2">
-        <v>10</v>
+        <v>204</v>
+      </c>
+      <c r="B11" s="15">
+        <v>33</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B12" s="15">
-        <v>21</v>
+        <v>205</v>
+      </c>
+      <c r="B12" s="2">
+        <v>13</v>
       </c>
       <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="16">
+        <v>20</v>
+      </c>
+      <c r="G12" s="2">
         <v>2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>16</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="2">
-        <v>5</v>
+        <v>206</v>
+      </c>
+      <c r="B13" s="16">
+        <v>27</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <v>18</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2">
         <v>3</v>
       </c>
       <c r="G14" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="C15" s="16">
+        <v>20</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B16" s="16">
-        <v>35</v>
+        <v>209</v>
+      </c>
+      <c r="B16" s="2">
+        <v>13</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2">
         <v>3</v>
-      </c>
-      <c r="E16" s="2">
-        <v>8</v>
-      </c>
-      <c r="F16" s="2">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B17" s="15">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="15">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="F17" s="2">
+        <v>8</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="16">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="16">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B18" s="2">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2">
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="F18" s="2">
+      <c r="E19" s="2">
         <v>2</v>
       </c>
-      <c r="G18" s="2">
-        <v>5</v>
+      <c r="F19" s="2">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4509,17 +4529,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -4527,7 +4547,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B5">
         <v>20</v>
@@ -4535,7 +4555,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B6">
         <v>30</v>
@@ -4543,7 +4563,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4551,7 +4571,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B8" s="18">
         <v>0.13333333333333333</v>
@@ -4559,7 +4579,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B9" s="19">
         <v>0.647</v>
@@ -4567,7 +4587,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4575,7 +4595,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B11" s="19">
         <v>0.691</v>
@@ -4583,32 +4603,32 @@
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -4626,7 +4646,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B16">
         <v>23</v>
@@ -4644,37 +4664,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4694,7 +4714,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4710,7 +4730,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -4730,7 +4750,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4750,7 +4770,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4770,7 +4790,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -4790,7 +4810,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4810,7 +4830,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4830,7 +4850,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4850,7 +4870,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4870,7 +4890,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4890,7 +4910,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4910,7 +4930,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4930,7 +4950,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -4950,7 +4970,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4966,7 +4986,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -4986,7 +5006,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5002,7 +5022,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5018,7 +5038,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -5038,7 +5058,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5054,7 +5074,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5070,7 +5090,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5086,7 +5106,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5102,7 +5122,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5122,7 +5142,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5142,7 +5162,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5162,7 +5182,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5178,32 +5198,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -5223,7 +5243,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5239,7 +5259,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B53">
         <v>11</v>
@@ -5259,7 +5279,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5279,7 +5299,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -5299,12 +5319,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5323,7 +5343,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5333,22 +5353,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5358,17 +5378,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5378,32 +5398,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5413,22 +5433,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5438,32 +5458,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -5473,27 +5493,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5503,17 +5523,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="317">
   <si>
     <t>日期</t>
   </si>
@@ -563,6 +563,12 @@
     <t>09-20 14:32 / 09-21 11:00</t>
   </si>
   <si>
+    <t>5:1</t>
+  </si>
+  <si>
+    <t>09-22 11:00</t>
+  </si>
+  <si>
     <t>2026-09-22</t>
   </si>
   <si>
@@ -581,7 +587,7 @@
     <t>09-23 02:00</t>
   </si>
   <si>
-    <t>09-21 17:00</t>
+    <t>09-21 17:00 / 09-22 11:00</t>
   </si>
   <si>
     <t>周二003</t>
@@ -686,7 +692,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-21T19:01:33+08:00）</t>
+    <t>统计（截至 2026-09-22T11:00:08+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -3673,36 +3679,36 @@
         <v>181</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W32" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W32" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>30</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>32</v>
@@ -3722,17 +3728,29 @@
       <c r="L33" s="5">
         <v>0.585</v>
       </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S33" s="4"/>
+      <c r="M33" s="3">
+        <v>8.35</v>
+      </c>
+      <c r="N33" s="3">
+        <v>12</v>
+      </c>
+      <c r="O33" s="3">
+        <v>22</v>
+      </c>
+      <c r="P33" s="4">
+        <v>7.765</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>0.585</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S33" s="4">
+        <v>0</v>
+      </c>
       <c r="T33" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>30</v>
@@ -3749,22 +3767,22 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>32</v>
@@ -3784,17 +3802,29 @@
       <c r="L34" s="5">
         <v>0.391</v>
       </c>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S34" s="4"/>
+      <c r="M34" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="N34" s="3">
+        <v>9.75</v>
+      </c>
+      <c r="O34" s="3">
+        <v>12</v>
+      </c>
+      <c r="P34" s="4">
+        <v>5.379</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>0.521</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S34" s="4">
+        <v>0.13</v>
+      </c>
       <c r="T34" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>30</v>
@@ -3811,22 +3841,22 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>32</v>
@@ -3846,17 +3876,29 @@
       <c r="L35" s="5">
         <v>0.434</v>
       </c>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S35" s="4"/>
+      <c r="M35" s="3">
+        <v>7</v>
+      </c>
+      <c r="N35" s="3">
+        <v>12</v>
+      </c>
+      <c r="O35" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="P35" s="4">
+        <v>6.566</v>
+      </c>
+      <c r="Q35" s="5">
+        <v>0.434</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S35" s="4">
+        <v>0</v>
+      </c>
       <c r="T35" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>30</v>
@@ -3889,33 +3931,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B2">
         <v>321</v>
@@ -3941,7 +3983,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B3">
         <v>320</v>
@@ -3967,7 +4009,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B4">
         <v>312</v>
@@ -3993,7 +4035,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B5">
         <v>305</v>
@@ -4019,7 +4061,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -4045,7 +4087,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -4071,7 +4113,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -4097,7 +4139,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -4123,7 +4165,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -4149,7 +4191,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -4175,7 +4217,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -4194,43 +4236,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -4238,16 +4280,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C6" s="13">
         <v>33</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -4255,35 +4297,35 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -4306,7 +4348,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B11" s="15">
         <v>33</v>
@@ -4329,7 +4371,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B12" s="2">
         <v>13</v>
@@ -4352,7 +4394,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B13" s="16">
         <v>27</v>
@@ -4375,7 +4417,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -4398,7 +4440,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -4421,7 +4463,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -4444,7 +4486,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" s="15">
         <v>44</v>
@@ -4467,7 +4509,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" s="16">
         <v>22</v>
@@ -4490,7 +4532,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -4529,17 +4571,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -4547,23 +4589,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4571,23 +4613,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B8" s="18">
-        <v>0.13333333333333333</v>
+        <v>0.12903225806451613</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B9" s="19">
-        <v>0.647</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4595,40 +4637,40 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B11" s="19">
-        <v>0.691</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -4646,7 +4688,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B16">
         <v>23</v>
@@ -4659,42 +4701,42 @@
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.67</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4714,7 +4756,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4730,7 +4772,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -4750,7 +4792,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4770,7 +4812,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4790,27 +4832,27 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="18">
         <v>0</v>
       </c>
       <c r="F26" s="19">
-        <v>0.36</v>
+        <v>0.369</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4830,7 +4872,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4850,7 +4892,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4870,7 +4912,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4890,7 +4932,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4910,7 +4952,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4930,7 +4972,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4950,7 +4992,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -4970,7 +5012,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -4986,7 +5028,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5006,7 +5048,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5022,7 +5064,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5038,7 +5080,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -5058,7 +5100,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5074,7 +5116,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5090,7 +5132,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5106,7 +5148,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5122,7 +5164,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5142,7 +5184,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5162,7 +5204,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5182,7 +5224,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5198,52 +5240,52 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="18">
         <v>0</v>
       </c>
       <c r="F51" s="20">
-        <v>-0.172</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5259,7 +5301,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B53">
         <v>11</v>
@@ -5279,7 +5321,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5299,7 +5341,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -5319,12 +5361,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -5343,7 +5385,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5353,22 +5395,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5378,17 +5420,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5398,32 +5440,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5433,22 +5475,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5458,32 +5500,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -5493,27 +5535,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5523,17 +5565,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="329">
   <si>
     <t>日期</t>
   </si>
@@ -572,6 +572,21 @@
     <t>2026-09-22</t>
   </si>
   <si>
+    <t>周二001</t>
+  </si>
+  <si>
+    <t>韩国亚</t>
+  </si>
+  <si>
+    <t>沙特亚</t>
+  </si>
+  <si>
+    <t>09-22 18:00</t>
+  </si>
+  <si>
+    <t>09-22 17:00</t>
+  </si>
+  <si>
     <t>周二002</t>
   </si>
   <si>
@@ -587,7 +602,7 @@
     <t>09-23 02:00</t>
   </si>
   <si>
-    <t>09-21 17:00 / 09-22 11:00</t>
+    <t>09-22 11:00 / 09-22 17:00</t>
   </si>
   <si>
     <t>周二003</t>
@@ -608,6 +623,27 @@
     <t>布莱克浦</t>
   </si>
   <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>周三001</t>
+  </si>
+  <si>
+    <t>阿联酋亚</t>
+  </si>
+  <si>
+    <t>09-23 13:30</t>
+  </si>
+  <si>
+    <t>周三002</t>
+  </si>
+  <si>
+    <t>泰国亚</t>
+  </si>
+  <si>
+    <t>09-23 18:30</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -692,7 +728,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-22T11:00:08+08:00）</t>
+    <t>统计（截至 2026-09-22T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1438,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X35"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3699,58 +3735,46 @@
         <v>185</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H33" s="3">
-        <v>8.35</v>
+        <v>7.25</v>
       </c>
       <c r="I33" s="3">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="J33" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K33" s="4">
-        <v>7.765</v>
+        <v>6.406</v>
       </c>
       <c r="L33" s="5">
-        <v>0.585</v>
-      </c>
-      <c r="M33" s="3">
-        <v>8.35</v>
-      </c>
-      <c r="N33" s="3">
-        <v>12</v>
-      </c>
-      <c r="O33" s="3">
-        <v>22</v>
-      </c>
-      <c r="P33" s="4">
-        <v>7.765</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>0.585</v>
-      </c>
-      <c r="R33" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="S33" s="4">
-        <v>0</v>
-      </c>
+        <v>0.844</v>
+      </c>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S33" s="4"/>
       <c r="T33" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>30</v>
@@ -3770,10 +3794,10 @@
         <v>184</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>192</v>
@@ -3782,49 +3806,49 @@
         <v>193</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H34" s="3">
-        <v>6.2</v>
+        <v>8.35</v>
       </c>
       <c r="I34" s="3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="J34" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K34" s="4">
-        <v>5.809</v>
+        <v>7.765</v>
       </c>
       <c r="L34" s="5">
-        <v>0.391</v>
+        <v>0.585</v>
       </c>
       <c r="M34" s="3">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="N34" s="3">
-        <v>9.75</v>
+        <v>11.5</v>
       </c>
       <c r="O34" s="3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="P34" s="4">
-        <v>5.379</v>
+        <v>7.973</v>
       </c>
       <c r="Q34" s="5">
-        <v>0.521</v>
+        <v>1.027</v>
       </c>
       <c r="R34" s="9" t="s">
         <v>94</v>
       </c>
       <c r="S34" s="4">
-        <v>0.13</v>
+        <v>0.442</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>30</v>
@@ -3844,52 +3868,52 @@
         <v>184</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H35" s="3">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="I35" s="3">
+        <v>9.75</v>
+      </c>
+      <c r="J35" s="3">
         <v>12</v>
       </c>
-      <c r="J35" s="3">
-        <v>14.5</v>
-      </c>
       <c r="K35" s="4">
-        <v>6.566</v>
+        <v>5.379</v>
       </c>
       <c r="L35" s="5">
-        <v>0.434</v>
+        <v>0.521</v>
       </c>
       <c r="M35" s="3">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="N35" s="3">
+        <v>9.75</v>
+      </c>
+      <c r="O35" s="3">
         <v>12</v>
       </c>
-      <c r="O35" s="3">
-        <v>14.5</v>
-      </c>
       <c r="P35" s="4">
-        <v>6.566</v>
+        <v>5.379</v>
       </c>
       <c r="Q35" s="5">
-        <v>0.434</v>
+        <v>0.521</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>80</v>
@@ -3898,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="U35" s="2" t="s">
         <v>30</v>
@@ -3910,6 +3934,204 @@
         <v>30</v>
       </c>
       <c r="X35" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H36" s="3">
+        <v>7</v>
+      </c>
+      <c r="I36" s="3">
+        <v>12</v>
+      </c>
+      <c r="J36" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="K36" s="4">
+        <v>6.566</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.434</v>
+      </c>
+      <c r="M36" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="N36" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="O36" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="P36" s="4">
+        <v>6.49</v>
+      </c>
+      <c r="Q36" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S36" s="4">
+        <v>-0.224</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="I37" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J37" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="K37" s="4">
+        <v>3.73</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S37" s="4"/>
+      <c r="T37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="I38" s="3">
+        <v>9</v>
+      </c>
+      <c r="J38" s="3">
+        <v>50</v>
+      </c>
+      <c r="K38" s="4">
+        <v>7.627</v>
+      </c>
+      <c r="L38" s="5">
+        <v>0.873</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S38" s="4"/>
+      <c r="T38" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X38" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3931,33 +4153,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B2">
         <v>321</v>
@@ -3983,7 +4205,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B3">
         <v>320</v>
@@ -4009,7 +4231,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B4">
         <v>312</v>
@@ -4035,7 +4257,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B5">
         <v>305</v>
@@ -4061,7 +4283,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -4087,7 +4309,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -4113,7 +4335,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -4139,7 +4361,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -4165,7 +4387,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -4191,7 +4413,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -4217,7 +4439,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4236,43 +4458,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -4280,16 +4502,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C6" s="13">
         <v>33</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -4297,35 +4519,35 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -4348,7 +4570,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="B11" s="15">
         <v>33</v>
@@ -4371,7 +4593,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B12" s="2">
         <v>13</v>
@@ -4394,7 +4616,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B13" s="16">
         <v>27</v>
@@ -4417,7 +4639,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -4440,7 +4662,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -4463,7 +4685,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -4486,7 +4708,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B17" s="15">
         <v>44</v>
@@ -4509,7 +4731,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B18" s="16">
         <v>22</v>
@@ -4532,7 +4754,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -4571,25 +4793,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B4">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B5">
         <v>23</v>
@@ -4597,7 +4819,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B6">
         <v>31</v>
@@ -4605,7 +4827,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4613,7 +4835,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B8" s="18">
         <v>0.12903225806451613</v>
@@ -4621,7 +4843,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B9" s="19">
         <v>0.638</v>
@@ -4629,7 +4851,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4637,7 +4859,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B11" s="19">
         <v>0.68</v>
@@ -4645,35 +4867,35 @@
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -4683,15 +4905,15 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.484</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>20</v>
@@ -4701,42 +4923,42 @@
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.675</v>
+        <v>0.692</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4756,7 +4978,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4772,7 +4994,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -4792,7 +5014,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4812,7 +5034,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -4832,7 +5054,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -4852,7 +5074,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -4872,7 +5094,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -4892,7 +5114,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -4912,7 +5134,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -4932,7 +5154,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -4952,7 +5174,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -4972,7 +5194,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4992,7 +5214,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5012,7 +5234,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -5028,7 +5250,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5048,7 +5270,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5064,7 +5286,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5080,7 +5302,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -5100,7 +5322,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5116,7 +5338,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5132,7 +5354,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5148,7 +5370,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5164,7 +5386,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5184,7 +5406,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5204,7 +5426,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5224,7 +5446,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5240,32 +5462,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="B51">
         <v>2</v>
@@ -5285,7 +5507,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5301,7 +5523,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B53">
         <v>11</v>
@@ -5321,7 +5543,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5341,7 +5563,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -5361,12 +5583,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -5385,7 +5607,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5395,22 +5617,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5420,17 +5642,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5440,32 +5662,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5475,22 +5697,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5500,32 +5722,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -5535,27 +5757,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5565,17 +5787,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="332">
   <si>
     <t>日期</t>
   </si>
@@ -587,6 +587,9 @@
     <t>09-22 17:00</t>
   </si>
   <si>
+    <t>09-23 11:00</t>
+  </si>
+  <si>
     <t>周二002</t>
   </si>
   <si>
@@ -605,6 +608,9 @@
     <t>09-22 11:00 / 09-22 17:00</t>
   </si>
   <si>
+    <t>4:1</t>
+  </si>
+  <si>
     <t>周二003</t>
   </si>
   <si>
@@ -635,6 +641,9 @@
     <t>09-23 13:30</t>
   </si>
   <si>
+    <t>09-22 17:00 / 09-23 11:00</t>
+  </si>
+  <si>
     <t>周三002</t>
   </si>
   <si>
@@ -698,10 +707,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-21（共 378 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-21，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-22（共 379 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-22，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -728,7 +737,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-22T17:00:05+08:00）</t>
+    <t>统计（截至 2026-09-23T11:00:03+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -3777,16 +3786,16 @@
         <v>189</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W33" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3794,19 +3803,19 @@
         <v>184</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>32</v>
@@ -3848,19 +3857,19 @@
         <v>0.442</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W34" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W34" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -3868,19 +3877,19 @@
         <v>184</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>32</v>
@@ -3922,19 +3931,19 @@
         <v>0</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W35" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W35" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -3942,19 +3951,19 @@
         <v>184</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>32</v>
@@ -3996,27 +4005,27 @@
         <v>-0.224</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W36" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W36" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>26</v>
@@ -4025,13 +4034,13 @@
         <v>28</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>46</v>
+        <v>207</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H37" s="3">
         <v>3.9</v>
@@ -4048,17 +4057,29 @@
       <c r="L37" s="5">
         <v>0.17</v>
       </c>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S37" s="4"/>
+      <c r="M37" s="3">
+        <v>4</v>
+      </c>
+      <c r="N37" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="O37" s="3">
+        <v>9</v>
+      </c>
+      <c r="P37" s="4">
+        <v>3.706</v>
+      </c>
+      <c r="Q37" s="5">
+        <v>0.294</v>
+      </c>
+      <c r="R37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S37" s="4">
+        <v>0.124</v>
+      </c>
       <c r="T37" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>30</v>
@@ -4075,10 +4096,10 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>26</v>
@@ -4087,10 +4108,10 @@
         <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>30</v>
@@ -4110,17 +4131,29 @@
       <c r="L38" s="5">
         <v>0.873</v>
       </c>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S38" s="4"/>
+      <c r="M38" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="N38" s="3">
+        <v>9</v>
+      </c>
+      <c r="O38" s="3">
+        <v>50</v>
+      </c>
+      <c r="P38" s="4">
+        <v>7.627</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>0.873</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0</v>
+      </c>
       <c r="T38" s="2" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>30</v>
@@ -4153,36 +4186,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C2">
         <v>22</v>
@@ -4191,7 +4224,7 @@
         <v>57</v>
       </c>
       <c r="E2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2">
         <v>67</v>
@@ -4205,10 +4238,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B3">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -4226,15 +4259,15 @@
         <v>45</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B4">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -4246,7 +4279,7 @@
         <v>66</v>
       </c>
       <c r="F4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>46</v>
@@ -4257,10 +4290,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B5">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -4278,12 +4311,12 @@
         <v>62</v>
       </c>
       <c r="H5">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -4309,7 +4342,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -4335,7 +4368,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -4361,7 +4394,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -4387,7 +4420,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -4413,7 +4446,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -4439,7 +4472,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -4458,43 +4491,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -4502,16 +4535,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C6" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -4519,73 +4552,73 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>6</v>
+      </c>
+      <c r="F10" s="2">
+        <v>17</v>
+      </c>
+      <c r="G10" s="2">
         <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-      <c r="F10" s="2">
-        <v>16</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B11" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
@@ -4593,53 +4626,53 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B12" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2">
         <v>3</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="16">
-        <v>20</v>
-      </c>
-      <c r="G12" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B13" s="16">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2">
         <v>3</v>
       </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <v>18</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2</v>
-      </c>
       <c r="G13" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -4662,7 +4695,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -4685,7 +4718,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -4708,7 +4741,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B17" s="15">
         <v>44</v>
@@ -4731,7 +4764,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B18" s="16">
         <v>22</v>
@@ -4754,7 +4787,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -4793,17 +4826,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B4">
         <v>37</v>
@@ -4811,23 +4844,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B6">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4835,23 +4868,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B8" s="18">
-        <v>0.12903225806451613</v>
+        <v>0.11428571428571428</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B9" s="19">
-        <v>0.638</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4859,43 +4892,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B11" s="19">
-        <v>0.68</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -4905,60 +4938,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.405</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B16">
+        <v>25</v>
+      </c>
+      <c r="C16">
         <v>24</v>
-      </c>
-      <c r="C16">
-        <v>20</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.692</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -4978,7 +5011,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -4994,27 +5027,27 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="19">
-        <v>0.245</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -5034,7 +5067,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -5054,7 +5087,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -5074,7 +5107,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -5094,7 +5127,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5114,27 +5147,27 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F29" s="19">
-        <v>0.532</v>
+        <v>0.527</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -5154,7 +5187,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -5174,7 +5207,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -5194,7 +5227,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5214,7 +5247,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5234,23 +5267,27 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="18">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0.844</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5270,7 +5307,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5286,7 +5323,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5302,27 +5339,27 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="18">
         <v>0</v>
       </c>
       <c r="F39" s="19">
-        <v>1.04</v>
+        <v>1.037</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5338,7 +5375,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5354,7 +5391,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5370,7 +5407,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5386,7 +5423,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5406,7 +5443,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5426,7 +5463,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5446,7 +5483,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5462,52 +5499,52 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="18">
         <v>0</v>
       </c>
       <c r="F51" s="20">
-        <v>-0.18</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5523,27 +5560,27 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B53">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E53" s="21">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F53" s="20">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5563,32 +5600,32 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E55" s="21">
         <v>0</v>
       </c>
       <c r="F55" s="20">
-        <v>0.395</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -5607,7 +5644,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5617,22 +5654,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5642,17 +5679,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5662,32 +5699,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5697,22 +5734,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5722,32 +5759,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -5757,27 +5794,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5787,17 +5824,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="370">
   <si>
     <t>日期</t>
   </si>
@@ -644,6 +644,9 @@
     <t>09-22 17:00 / 09-23 11:00</t>
   </si>
   <si>
+    <t>09-23 17:00</t>
+  </si>
+  <si>
     <t>周三002</t>
   </si>
   <si>
@@ -653,6 +656,117 @@
     <t>09-23 18:30</t>
   </si>
   <si>
+    <t>09-23 11:00 / 09-23 17:00</t>
+  </si>
+  <si>
+    <t>周三003</t>
+  </si>
+  <si>
+    <t>美职</t>
+  </si>
+  <si>
+    <t>西雅图</t>
+  </si>
+  <si>
+    <t>盐湖城</t>
+  </si>
+  <si>
+    <t>09-24 09:30</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>周四001</t>
+  </si>
+  <si>
+    <t>国际赛</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>乌拉圭</t>
+  </si>
+  <si>
+    <t>09-24 18:05</t>
+  </si>
+  <si>
+    <t>周四002</t>
+  </si>
+  <si>
+    <t>韩国</t>
+  </si>
+  <si>
+    <t>厄瓜多尔</t>
+  </si>
+  <si>
+    <t>09-24 19:00</t>
+  </si>
+  <si>
+    <t>周四003</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>马尔代夫</t>
+  </si>
+  <si>
+    <t>09-24 19:35</t>
+  </si>
+  <si>
+    <t>周四004</t>
+  </si>
+  <si>
+    <t>欧国联</t>
+  </si>
+  <si>
+    <t>科索沃</t>
+  </si>
+  <si>
+    <t>爱尔兰</t>
+  </si>
+  <si>
+    <t>09-25 02:45</t>
+  </si>
+  <si>
+    <t>周四005</t>
+  </si>
+  <si>
+    <t>葡萄牙</t>
+  </si>
+  <si>
+    <t>威尔士</t>
+  </si>
+  <si>
+    <t>周四006</t>
+  </si>
+  <si>
+    <t>荷兰</t>
+  </si>
+  <si>
+    <t>德国</t>
+  </si>
+  <si>
+    <t>周四007</t>
+  </si>
+  <si>
+    <t>塞尔维亚</t>
+  </si>
+  <si>
+    <t>希腊</t>
+  </si>
+  <si>
+    <t>周四008</t>
+  </si>
+  <si>
+    <t>挪威</t>
+  </si>
+  <si>
+    <t>丹麦</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -707,10 +821,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-22（共 379 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-22，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-23（共 380 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-23，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -737,7 +851,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-23T11:00:03+08:00）</t>
+    <t>统计（截至 2026-09-23T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1076,12 +1190,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -1133,10 +1247,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1483,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X38"/>
+  <dimension ref="A1:X47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4082,16 +4196,16 @@
         <v>208</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W37" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W37" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -4099,7 +4213,7 @@
         <v>204</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>26</v>
@@ -4108,10 +4222,10 @@
         <v>55</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>30</v>
@@ -4132,39 +4246,597 @@
         <v>0.873</v>
       </c>
       <c r="M38" s="3">
+        <v>11</v>
+      </c>
+      <c r="N38" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="O38" s="3">
+        <v>75</v>
+      </c>
+      <c r="P38" s="4">
+        <v>9.971</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>1.029</v>
+      </c>
+      <c r="R38" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S38" s="4">
+        <v>0.156</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H39" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="I39" s="3">
+        <v>10</v>
+      </c>
+      <c r="J39" s="3">
+        <v>17</v>
+      </c>
+      <c r="K39" s="4">
+        <v>6.296</v>
+      </c>
+      <c r="L39" s="5">
+        <v>0.604</v>
+      </c>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S39" s="4"/>
+      <c r="T39" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X39" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="I40" s="3">
+        <v>7</v>
+      </c>
+      <c r="J40" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="K40" s="4">
+        <v>4.03</v>
+      </c>
+      <c r="L40" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S40" s="4"/>
+      <c r="T40" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="3">
+        <v>4</v>
+      </c>
+      <c r="I41" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J41" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="K41" s="4">
+        <v>3.636</v>
+      </c>
+      <c r="L41" s="5">
+        <v>0.364</v>
+      </c>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S41" s="4"/>
+      <c r="T41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H42" s="3">
+        <v>20</v>
+      </c>
+      <c r="I42" s="3">
+        <v>21</v>
+      </c>
+      <c r="J42" s="3">
+        <v>120</v>
+      </c>
+      <c r="K42" s="4">
+        <v>17.872</v>
+      </c>
+      <c r="L42" s="5">
+        <v>2.128</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S42" s="4"/>
+      <c r="T42" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H43" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="I43" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J43" s="3">
+        <v>8</v>
+      </c>
+      <c r="K43" s="4">
+        <v>3.871</v>
+      </c>
+      <c r="L43" s="5">
+        <v>0.229</v>
+      </c>
+      <c r="M43" s="3"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S43" s="4"/>
+      <c r="T43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="I44" s="3">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
+        <v>29</v>
+      </c>
+      <c r="K44" s="4">
+        <v>6.27</v>
+      </c>
+      <c r="L44" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S44" s="4"/>
+      <c r="T44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X44" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="I45" s="3">
+        <v>13</v>
+      </c>
+      <c r="J45" s="3">
+        <v>14</v>
+      </c>
+      <c r="K45" s="4">
+        <v>6.741</v>
+      </c>
+      <c r="L45" s="5">
+        <v>0.509</v>
+      </c>
+      <c r="M45" s="3"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S45" s="4"/>
+      <c r="T45" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="I46" s="3">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3">
         <v>8.5</v>
       </c>
-      <c r="N38" s="3">
-        <v>9</v>
-      </c>
-      <c r="O38" s="3">
-        <v>50</v>
-      </c>
-      <c r="P38" s="4">
-        <v>7.627</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>0.873</v>
-      </c>
-      <c r="R38" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="S38" s="4">
-        <v>0</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X38" s="2" t="s">
+      <c r="K46" s="4">
+        <v>4.121</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S46" s="4"/>
+      <c r="T46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="3">
+        <v>6</v>
+      </c>
+      <c r="I47" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="J47" s="3">
+        <v>14</v>
+      </c>
+      <c r="K47" s="4">
+        <v>5.66</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S47" s="4"/>
+      <c r="T47" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X47" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4186,39 +4858,39 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2">
         <v>57</v>
@@ -4238,7 +4910,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B3">
         <v>321</v>
@@ -4264,7 +4936,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="B4">
         <v>313</v>
@@ -4290,7 +4962,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="B5">
         <v>306</v>
@@ -4316,7 +4988,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -4342,7 +5014,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -4368,7 +5040,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -4394,7 +5066,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -4420,7 +5092,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -4446,7 +5118,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -4472,7 +5144,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4491,43 +5163,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>232</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>233</v>
+        <v>271</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -4535,16 +5207,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C6" s="13">
         <v>34</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -4552,60 +5224,60 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>7</v>
+      </c>
+      <c r="F10" s="15">
+        <v>18</v>
+      </c>
+      <c r="G10" s="2">
         <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>13</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
-        <v>6</v>
-      </c>
-      <c r="F10" s="2">
-        <v>17</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B11" s="15">
+        <v>259</v>
+      </c>
+      <c r="B11" s="16">
         <v>34</v>
       </c>
       <c r="C11" s="2">
@@ -4626,7 +5298,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2">
         <v>14</v>
@@ -4640,7 +5312,7 @@
       <c r="E12" s="2">
         <v>0</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="15">
         <v>21</v>
       </c>
       <c r="G12" s="2">
@@ -4649,9 +5321,9 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" s="16">
+        <v>261</v>
+      </c>
+      <c r="B13" s="15">
         <v>28</v>
       </c>
       <c r="C13" s="2">
@@ -4660,7 +5332,7 @@
       <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="15">
         <v>19</v>
       </c>
       <c r="F13" s="2">
@@ -4672,7 +5344,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>262</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -4695,12 +5367,12 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>263</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="15">
         <v>20</v>
       </c>
       <c r="D15" s="2">
@@ -4718,7 +5390,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -4741,9 +5413,9 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="15">
+        <v>265</v>
+      </c>
+      <c r="B17" s="16">
         <v>44</v>
       </c>
       <c r="C17" s="2">
@@ -4764,9 +5436,9 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" s="16">
+        <v>266</v>
+      </c>
+      <c r="B18" s="15">
         <v>22</v>
       </c>
       <c r="C18" s="2">
@@ -4778,7 +5450,7 @@
       <c r="E18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="15">
         <v>23</v>
       </c>
       <c r="G18" s="2">
@@ -4787,7 +5459,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -4826,25 +5498,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>240</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>241</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="B4">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="B5">
         <v>25</v>
@@ -4852,15 +5524,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="B6">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -4868,23 +5540,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="B8" s="18">
-        <v>0.11428571428571428</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="B9" s="19">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -4892,43 +5564,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="B11" s="19">
-        <v>0.677</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>253</v>
+        <v>291</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -4938,60 +5610,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.484</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="B16">
+        <v>31</v>
+      </c>
+      <c r="C16">
         <v>25</v>
-      </c>
-      <c r="C16">
-        <v>24</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.676</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>260</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>261</v>
+        <v>299</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>242</v>
+        <v>280</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>256</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5011,7 +5683,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5027,7 +5699,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5047,27 +5719,27 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="18">
         <v>0</v>
       </c>
       <c r="F24" s="19">
-        <v>0.281</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -5087,7 +5759,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -5107,7 +5779,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>269</v>
+        <v>307</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -5127,7 +5799,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>308</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5147,7 +5819,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -5167,7 +5839,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>310</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -5187,7 +5859,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -5207,7 +5879,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>312</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -5227,7 +5899,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5247,7 +5919,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5267,7 +5939,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>277</v>
+        <v>315</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -5287,7 +5959,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5307,7 +5979,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5323,7 +5995,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>280</v>
+        <v>318</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -5339,7 +6011,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -5359,7 +6031,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -5375,7 +6047,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -5391,7 +6063,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -5407,7 +6079,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>285</v>
+        <v>323</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -5423,7 +6095,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>286</v>
+        <v>324</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -5443,7 +6115,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -5463,7 +6135,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -5483,7 +6155,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -5499,32 +6171,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>290</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>291</v>
+        <v>329</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>255</v>
+        <v>293</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>293</v>
+        <v>331</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -5544,7 +6216,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -5560,7 +6232,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>295</v>
+        <v>333</v>
       </c>
       <c r="B53">
         <v>12</v>
@@ -5580,7 +6252,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -5600,32 +6272,32 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>297</v>
+        <v>335</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E55" s="21">
         <v>0</v>
       </c>
       <c r="F55" s="20">
-        <v>0.403</v>
+        <v>0.363</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>298</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>299</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -5644,7 +6316,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>300</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -5654,22 +6326,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>303</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>304</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -5679,17 +6351,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>305</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -5699,32 +6371,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>308</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>312</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>313</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -5734,22 +6406,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>314</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -5759,32 +6431,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>322</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -5794,27 +6466,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -5824,17 +6496,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>329</v>
+        <v>367</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>331</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="372">
   <si>
     <t>日期</t>
   </si>
@@ -644,36 +644,39 @@
     <t>09-22 17:00 / 09-23 11:00</t>
   </si>
   <si>
+    <t>09-24 11:00</t>
+  </si>
+  <si>
+    <t>周三002</t>
+  </si>
+  <si>
+    <t>泰国亚</t>
+  </si>
+  <si>
+    <t>09-23 18:30</t>
+  </si>
+  <si>
+    <t>09-23 11:00 / 09-23 17:00</t>
+  </si>
+  <si>
+    <t>周三003</t>
+  </si>
+  <si>
+    <t>美职</t>
+  </si>
+  <si>
+    <t>西雅图</t>
+  </si>
+  <si>
+    <t>盐湖城</t>
+  </si>
+  <si>
+    <t>09-24 09:30</t>
+  </si>
+  <si>
     <t>09-23 17:00</t>
   </si>
   <si>
-    <t>周三002</t>
-  </si>
-  <si>
-    <t>泰国亚</t>
-  </si>
-  <si>
-    <t>09-23 18:30</t>
-  </si>
-  <si>
-    <t>09-23 11:00 / 09-23 17:00</t>
-  </si>
-  <si>
-    <t>周三003</t>
-  </si>
-  <si>
-    <t>美职</t>
-  </si>
-  <si>
-    <t>西雅图</t>
-  </si>
-  <si>
-    <t>盐湖城</t>
-  </si>
-  <si>
-    <t>09-24 09:30</t>
-  </si>
-  <si>
     <t>2026-09-24</t>
   </si>
   <si>
@@ -692,6 +695,9 @@
     <t>09-24 18:05</t>
   </si>
   <si>
+    <t>09-23 17:00 / 09-24 11:00</t>
+  </si>
+  <si>
     <t>周四002</t>
   </si>
   <si>
@@ -851,7 +857,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-23T17:00:05+08:00）</t>
+    <t>统计（截至 2026-09-24T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1256,8 +1262,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4270,16 +4276,16 @@
         <v>213</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W38" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
@@ -4329,7 +4335,7 @@
       </c>
       <c r="S39" s="4"/>
       <c r="T39" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="U39" s="2" t="s">
         <v>30</v>
@@ -4346,22 +4352,22 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>32</v>
@@ -4381,17 +4387,29 @@
       <c r="L40" s="5">
         <v>0.17</v>
       </c>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S40" s="4"/>
+      <c r="M40" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="N40" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O40" s="3">
+        <v>11</v>
+      </c>
+      <c r="P40" s="4">
+        <v>4.086</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>0.114</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S40" s="4">
+        <v>-0.056</v>
+      </c>
       <c r="T40" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U40" s="2" t="s">
         <v>30</v>
@@ -4408,22 +4426,22 @@
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>32</v>
@@ -4443,17 +4461,29 @@
       <c r="L41" s="5">
         <v>0.364</v>
       </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S41" s="4"/>
+      <c r="M41" s="3">
+        <v>4</v>
+      </c>
+      <c r="N41" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O41" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="P41" s="4">
+        <v>3.636</v>
+      </c>
+      <c r="Q41" s="5">
+        <v>0.364</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S41" s="4">
+        <v>0</v>
+      </c>
       <c r="T41" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U41" s="2" t="s">
         <v>30</v>
@@ -4470,22 +4500,22 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>30</v>
@@ -4505,17 +4535,29 @@
       <c r="L42" s="5">
         <v>2.128</v>
       </c>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S42" s="4"/>
+      <c r="M42" s="3">
+        <v>20</v>
+      </c>
+      <c r="N42" s="3">
+        <v>21</v>
+      </c>
+      <c r="O42" s="3">
+        <v>120</v>
+      </c>
+      <c r="P42" s="4">
+        <v>17.872</v>
+      </c>
+      <c r="Q42" s="5">
+        <v>2.128</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S42" s="4">
+        <v>0</v>
+      </c>
       <c r="T42" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>30</v>
@@ -4532,22 +4574,22 @@
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>32</v>
@@ -4567,17 +4609,29 @@
       <c r="L43" s="5">
         <v>0.229</v>
       </c>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S43" s="4"/>
+      <c r="M43" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="N43" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O43" s="3">
+        <v>8</v>
+      </c>
+      <c r="P43" s="4">
+        <v>3.871</v>
+      </c>
+      <c r="Q43" s="5">
+        <v>0.229</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S43" s="4">
+        <v>0</v>
+      </c>
       <c r="T43" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>30</v>
@@ -4594,22 +4648,22 @@
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>32</v>
@@ -4629,17 +4683,29 @@
       <c r="L44" s="5">
         <v>0.53</v>
       </c>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="4"/>
-      <c r="Q44" s="4"/>
-      <c r="R44" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S44" s="4"/>
+      <c r="M44" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="N44" s="3">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
+        <v>35</v>
+      </c>
+      <c r="P44" s="4">
+        <v>6.512</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>0.288</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S44" s="4">
+        <v>-0.242</v>
+      </c>
       <c r="T44" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>30</v>
@@ -4656,25 +4722,25 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>46</v>
+        <v>239</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H45" s="3">
         <v>7.25</v>
@@ -4691,17 +4757,29 @@
       <c r="L45" s="5">
         <v>0.509</v>
       </c>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="4"/>
-      <c r="Q45" s="4"/>
-      <c r="R45" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S45" s="4"/>
+      <c r="M45" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="N45" s="3">
+        <v>13</v>
+      </c>
+      <c r="O45" s="3">
+        <v>14</v>
+      </c>
+      <c r="P45" s="4">
+        <v>6.741</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>0.509</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S45" s="4">
+        <v>0</v>
+      </c>
       <c r="T45" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>30</v>
@@ -4718,22 +4796,22 @@
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>32</v>
@@ -4753,17 +4831,29 @@
       <c r="L46" s="5">
         <v>0.379</v>
       </c>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S46" s="4"/>
+      <c r="M46" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="N46" s="3">
+        <v>8</v>
+      </c>
+      <c r="O46" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="P46" s="4">
+        <v>4.121</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S46" s="4">
+        <v>0</v>
+      </c>
       <c r="T46" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U46" s="2" t="s">
         <v>30</v>
@@ -4780,25 +4870,25 @@
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>46</v>
+        <v>239</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H47" s="3">
         <v>6</v>
@@ -4815,17 +4905,29 @@
       <c r="L47" s="5">
         <v>0.34</v>
       </c>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S47" s="4"/>
+      <c r="M47" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="N47" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="O47" s="3">
+        <v>16</v>
+      </c>
+      <c r="P47" s="4">
+        <v>5.961</v>
+      </c>
+      <c r="Q47" s="5">
+        <v>0.539</v>
+      </c>
+      <c r="R47" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S47" s="4">
+        <v>0.199</v>
+      </c>
       <c r="T47" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="U47" s="2" t="s">
         <v>30</v>
@@ -4858,33 +4960,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B2">
         <v>323</v>
@@ -4910,10 +5012,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B3">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -4925,7 +5027,7 @@
         <v>86</v>
       </c>
       <c r="F3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3">
         <v>45</v>
@@ -4936,7 +5038,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B4">
         <v>313</v>
@@ -4962,7 +5064,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B5">
         <v>306</v>
@@ -4988,7 +5090,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -5014,7 +5116,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -5040,7 +5142,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -5066,7 +5168,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -5092,7 +5194,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -5118,7 +5220,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -5144,7 +5246,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5163,43 +5265,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -5207,16 +5309,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" s="13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -5224,35 +5326,35 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2">
         <v>0</v>
@@ -5275,30 +5377,30 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B11" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B12" s="2">
         <v>14</v>
@@ -5321,7 +5423,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B13" s="15">
         <v>28</v>
@@ -5344,7 +5446,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -5367,7 +5469,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -5390,7 +5492,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -5413,7 +5515,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B17" s="16">
         <v>44</v>
@@ -5436,7 +5538,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B18" s="15">
         <v>22</v>
@@ -5459,7 +5561,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -5498,17 +5600,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B4">
         <v>46</v>
@@ -5516,23 +5618,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B6">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -5540,23 +5642,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B8" s="18">
-        <v>0.1111111111111111</v>
+        <v>0.10810810810810811</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B9" s="19">
-        <v>0.63</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -5564,43 +5666,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B11" s="19">
-        <v>0.665</v>
+        <v>0.676</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -5610,15 +5712,15 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.46</v>
+        <v>0.484</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B16">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -5628,42 +5730,42 @@
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.618</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5683,7 +5785,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5699,7 +5801,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5719,7 +5821,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -5739,7 +5841,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -5759,7 +5861,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -5779,7 +5881,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -5799,7 +5901,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5819,7 +5921,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -5839,7 +5941,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -5859,7 +5961,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -5879,7 +5981,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -5899,7 +6001,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5919,7 +6021,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -5939,7 +6041,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -5959,7 +6061,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5979,7 +6081,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -5995,7 +6097,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6011,27 +6113,27 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>4</v>
-      </c>
-      <c r="E39" s="18">
+        <v>5</v>
+      </c>
+      <c r="E39" s="20">
         <v>0</v>
       </c>
       <c r="F39" s="19">
-        <v>1.037</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6047,7 +6149,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6063,7 +6165,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6079,7 +6181,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6095,7 +6197,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -6115,7 +6217,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -6135,7 +6237,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -6155,7 +6257,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6171,32 +6273,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -6210,13 +6312,13 @@
       <c r="E51" s="18">
         <v>0</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="21">
         <v>-0.195</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -6228,11 +6330,11 @@
         <v>0</v>
       </c>
       <c r="E52" s="18"/>
-      <c r="F52" s="20"/>
+      <c r="F52" s="21"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B53">
         <v>12</v>
@@ -6243,16 +6345,16 @@
       <c r="D53">
         <v>11</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="20">
         <v>0.08333333333333333</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="21">
         <v>-0.002</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -6266,38 +6368,38 @@
       <c r="E54" s="18">
         <v>0</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="21">
         <v>0.054</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>7</v>
-      </c>
-      <c r="E55" s="21">
-        <v>0</v>
-      </c>
-      <c r="F55" s="20">
-        <v>0.363</v>
+        <v>8</v>
+      </c>
+      <c r="E55" s="20">
+        <v>0</v>
+      </c>
+      <c r="F55" s="21">
+        <v>0.337</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -6316,7 +6418,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -6326,22 +6428,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -6351,17 +6453,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -6371,32 +6473,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -6406,22 +6508,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -6431,32 +6533,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -6466,27 +6568,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -6496,17 +6598,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="417">
   <si>
     <t>日期</t>
   </si>
@@ -644,7 +644,7 @@
     <t>09-22 17:00 / 09-23 11:00</t>
   </si>
   <si>
-    <t>09-24 11:00</t>
+    <t>09-24 17:00</t>
   </si>
   <si>
     <t>周三002</t>
@@ -695,7 +695,7 @@
     <t>09-24 18:05</t>
   </si>
   <si>
-    <t>09-23 17:00 / 09-24 11:00</t>
+    <t>09-24 11:00 / 09-24 17:00</t>
   </si>
   <si>
     <t>周四002</t>
@@ -773,6 +773,141 @@
     <t>丹麦</t>
   </si>
   <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>周五001</t>
+  </si>
+  <si>
+    <t>乌兹别亚</t>
+  </si>
+  <si>
+    <t>09-25 13:00</t>
+  </si>
+  <si>
+    <t>周五002</t>
+  </si>
+  <si>
+    <t>越南女</t>
+  </si>
+  <si>
+    <t>09-25 14:00</t>
+  </si>
+  <si>
+    <t>周五003</t>
+  </si>
+  <si>
+    <t>澳大利亚</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>09-25 18:00</t>
+  </si>
+  <si>
+    <t>周五004</t>
+  </si>
+  <si>
+    <t>越南亚</t>
+  </si>
+  <si>
+    <t>09-25 18:30</t>
+  </si>
+  <si>
+    <t>周五005</t>
+  </si>
+  <si>
+    <t>韩国女</t>
+  </si>
+  <si>
+    <t>乌兹别女</t>
+  </si>
+  <si>
+    <t>周五006</t>
+  </si>
+  <si>
+    <t>格鲁吉亚</t>
+  </si>
+  <si>
+    <t>北爱尔兰</t>
+  </si>
+  <si>
+    <t>09-26 00:00</t>
+  </si>
+  <si>
+    <t>周五007</t>
+  </si>
+  <si>
+    <t>亚美尼亚</t>
+  </si>
+  <si>
+    <t>拉脱维亚</t>
+  </si>
+  <si>
+    <t>周五008</t>
+  </si>
+  <si>
+    <t>意大利</t>
+  </si>
+  <si>
+    <t>比利时</t>
+  </si>
+  <si>
+    <t>09-26 02:45</t>
+  </si>
+  <si>
+    <t>周五009</t>
+  </si>
+  <si>
+    <t>黑山</t>
+  </si>
+  <si>
+    <t>塞浦路斯</t>
+  </si>
+  <si>
+    <t>周五010</t>
+  </si>
+  <si>
+    <t>波兰</t>
+  </si>
+  <si>
+    <t>波黑</t>
+  </si>
+  <si>
+    <t>周五011</t>
+  </si>
+  <si>
+    <t>土耳其</t>
+  </si>
+  <si>
+    <t>法国</t>
+  </si>
+  <si>
+    <t>周五012</t>
+  </si>
+  <si>
+    <t>瑞典</t>
+  </si>
+  <si>
+    <t>罗马尼亚</t>
+  </si>
+  <si>
+    <t>周五013</t>
+  </si>
+  <si>
+    <t>荷乙</t>
+  </si>
+  <si>
+    <t>多德勒支</t>
+  </si>
+  <si>
+    <t>阿尔梅勒</t>
+  </si>
+  <si>
+    <t>09-26 03:00</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -857,7 +992,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-24T11:00:04+08:00）</t>
+    <t>统计（截至 2026-09-24T17:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1603,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X47"/>
+  <dimension ref="A1:X60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4338,16 +4473,16 @@
         <v>219</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W39" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W39" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
@@ -4376,37 +4511,37 @@
         <v>4.2</v>
       </c>
       <c r="I40" s="3">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J40" s="3">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="K40" s="4">
-        <v>4.03</v>
+        <v>4.086</v>
       </c>
       <c r="L40" s="5">
-        <v>0.17</v>
+        <v>0.114</v>
       </c>
       <c r="M40" s="3">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="N40" s="3">
         <v>6.5</v>
       </c>
       <c r="O40" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="P40" s="4">
-        <v>4.086</v>
+        <v>4.439</v>
       </c>
       <c r="Q40" s="5">
-        <v>0.114</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>73</v>
+        <v>0.461</v>
+      </c>
+      <c r="R40" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S40" s="4">
-        <v>-0.056</v>
+        <v>0.347</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>226</v>
@@ -4542,19 +4677,19 @@
         <v>21</v>
       </c>
       <c r="O42" s="3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="P42" s="4">
-        <v>17.872</v>
+        <v>17.355</v>
       </c>
       <c r="Q42" s="5">
-        <v>2.128</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>80</v>
+        <v>2.645</v>
+      </c>
+      <c r="R42" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S42" s="4">
-        <v>0</v>
+        <v>0.517</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>226</v>
@@ -4675,34 +4810,34 @@
         <v>8</v>
       </c>
       <c r="J44" s="3">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K44" s="4">
-        <v>6.27</v>
+        <v>6.512</v>
       </c>
       <c r="L44" s="5">
-        <v>0.53</v>
+        <v>0.288</v>
       </c>
       <c r="M44" s="3">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="N44" s="3">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="O44" s="3">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="P44" s="4">
-        <v>6.512</v>
+        <v>6.81</v>
       </c>
       <c r="Q44" s="5">
-        <v>0.288</v>
-      </c>
-      <c r="R44" s="7" t="s">
-        <v>73</v>
+        <v>0.69</v>
+      </c>
+      <c r="R44" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S44" s="4">
-        <v>-0.242</v>
+        <v>0.402</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>226</v>
@@ -4739,8 +4874,8 @@
       <c r="F45" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>32</v>
+      <c r="G45" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H45" s="3">
         <v>7.25</v>
@@ -4758,25 +4893,25 @@
         <v>0.509</v>
       </c>
       <c r="M45" s="3">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
       <c r="N45" s="3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="O45" s="3">
         <v>14</v>
       </c>
       <c r="P45" s="4">
-        <v>6.741</v>
+        <v>7.123</v>
       </c>
       <c r="Q45" s="5">
-        <v>0.509</v>
-      </c>
-      <c r="R45" s="6" t="s">
-        <v>80</v>
+        <v>0.627</v>
+      </c>
+      <c r="R45" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S45" s="4">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>226</v>
@@ -4887,23 +5022,23 @@
       <c r="F47" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>32</v>
+      <c r="G47" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H47" s="3">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I47" s="3">
         <v>9.5</v>
       </c>
       <c r="J47" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K47" s="4">
-        <v>5.66</v>
+        <v>5.961</v>
       </c>
       <c r="L47" s="5">
-        <v>0.34</v>
+        <v>0.539</v>
       </c>
       <c r="M47" s="3">
         <v>6.5</v>
@@ -4912,19 +5047,19 @@
         <v>9.5</v>
       </c>
       <c r="O47" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P47" s="4">
-        <v>5.961</v>
+        <v>6.094</v>
       </c>
       <c r="Q47" s="5">
-        <v>0.539</v>
-      </c>
-      <c r="R47" s="9" t="s">
-        <v>94</v>
+        <v>0.406</v>
+      </c>
+      <c r="R47" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S47" s="4">
-        <v>0.199</v>
+        <v>-0.133</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>226</v>
@@ -4939,6 +5074,812 @@
         <v>30</v>
       </c>
       <c r="X47" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="J48" s="3">
+        <v>11</v>
+      </c>
+      <c r="K48" s="4">
+        <v>3.711</v>
+      </c>
+      <c r="L48" s="5">
+        <v>0.289</v>
+      </c>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S48" s="4"/>
+      <c r="T48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H49" s="3">
+        <v>9.75</v>
+      </c>
+      <c r="I49" s="3">
+        <v>10</v>
+      </c>
+      <c r="J49" s="3">
+        <v>80</v>
+      </c>
+      <c r="K49" s="4">
+        <v>8.889</v>
+      </c>
+      <c r="L49" s="5">
+        <v>0.861</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S49" s="4"/>
+      <c r="T49" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X49" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="I50" s="3">
+        <v>24</v>
+      </c>
+      <c r="J50" s="3">
+        <v>8</v>
+      </c>
+      <c r="K50" s="4">
+        <v>6</v>
+      </c>
+      <c r="L50" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S50" s="4"/>
+      <c r="T50" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X50" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" s="3">
+        <v>6</v>
+      </c>
+      <c r="I51" s="3">
+        <v>7</v>
+      </c>
+      <c r="J51" s="3">
+        <v>24</v>
+      </c>
+      <c r="K51" s="4">
+        <v>5.419</v>
+      </c>
+      <c r="L51" s="5">
+        <v>0.581</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S51" s="4"/>
+      <c r="T51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" s="3">
+        <v>9.25</v>
+      </c>
+      <c r="I52" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="J52" s="3">
+        <v>60</v>
+      </c>
+      <c r="K52" s="4">
+        <v>8.201</v>
+      </c>
+      <c r="L52" s="5">
+        <v>1.049</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S52" s="4"/>
+      <c r="T52" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H53" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="I53" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J53" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="K53" s="4">
+        <v>4.015</v>
+      </c>
+      <c r="L53" s="5">
+        <v>0.285</v>
+      </c>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S53" s="4"/>
+      <c r="T53" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H54" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="I54" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J54" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="K54" s="4">
+        <v>4.153</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0.247</v>
+      </c>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S54" s="4"/>
+      <c r="T54" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H55" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="I55" s="3">
+        <v>9</v>
+      </c>
+      <c r="J55" s="3">
+        <v>12</v>
+      </c>
+      <c r="K55" s="4">
+        <v>5.143</v>
+      </c>
+      <c r="L55" s="5">
+        <v>0.257</v>
+      </c>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S55" s="4"/>
+      <c r="T55" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I56" s="3">
+        <v>7</v>
+      </c>
+      <c r="J56" s="3">
+        <v>13</v>
+      </c>
+      <c r="K56" s="4">
+        <v>4.55</v>
+      </c>
+      <c r="L56" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S56" s="4"/>
+      <c r="T56" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H57" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="I57" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J57" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="K57" s="4">
+        <v>4.488</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.612</v>
+      </c>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S57" s="4"/>
+      <c r="T57" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="I58" s="3">
+        <v>21</v>
+      </c>
+      <c r="J58" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="K58" s="4">
+        <v>6.541</v>
+      </c>
+      <c r="L58" s="5">
+        <v>0.709</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S58" s="4"/>
+      <c r="T58" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="I59" s="3">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
+        <v>19</v>
+      </c>
+      <c r="K59" s="4">
+        <v>5.63</v>
+      </c>
+      <c r="L59" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S59" s="4"/>
+      <c r="T59" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H60" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="I60" s="3">
+        <v>16</v>
+      </c>
+      <c r="J60" s="3">
+        <v>14</v>
+      </c>
+      <c r="K60" s="4">
+        <v>7.467</v>
+      </c>
+      <c r="L60" s="5">
+        <v>1.283</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S60" s="4"/>
+      <c r="T60" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X60" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4960,33 +5901,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="B2">
         <v>323</v>
@@ -5012,7 +5953,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="B3">
         <v>322</v>
@@ -5038,10 +5979,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="B4">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -5050,7 +5991,7 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4">
         <v>67</v>
@@ -5064,7 +6005,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="B5">
         <v>306</v>
@@ -5090,7 +6031,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="B6">
         <v>298</v>
@@ -5116,7 +6057,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="B7">
         <v>280</v>
@@ -5142,7 +6083,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="B8">
         <v>271</v>
@@ -5168,7 +6109,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="B9">
         <v>250</v>
@@ -5194,7 +6135,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -5220,7 +6161,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -5246,7 +6187,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>270</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5265,43 +6206,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>271</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>272</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>276</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C5" s="13">
         <v>44</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -5309,16 +6250,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C6" s="13">
         <v>35</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -5326,35 +6267,35 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>279</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="B10" s="2">
         <v>0</v>
@@ -5377,7 +6318,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="B11" s="16">
         <v>35</v>
@@ -5400,30 +6341,30 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="B12" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="D12" s="2">
+      <c r="F12" s="15">
+        <v>22</v>
+      </c>
+      <c r="G12" s="2">
         <v>4</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="15">
-        <v>21</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="B13" s="15">
         <v>28</v>
@@ -5446,7 +6387,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
@@ -5469,7 +6410,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="B15" s="2">
         <v>7</v>
@@ -5492,7 +6433,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
       <c r="B16" s="2">
         <v>13</v>
@@ -5515,7 +6456,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>267</v>
+        <v>312</v>
       </c>
       <c r="B17" s="16">
         <v>44</v>
@@ -5538,7 +6479,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>268</v>
+        <v>313</v>
       </c>
       <c r="B18" s="15">
         <v>22</v>
@@ -5561,7 +6502,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -5600,25 +6541,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>281</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>283</v>
+        <v>328</v>
       </c>
       <c r="B5">
         <v>33</v>
@@ -5626,15 +6567,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>284</v>
+        <v>329</v>
       </c>
       <c r="B6">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -5642,23 +6583,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="B8" s="18">
-        <v>0.10810810810810811</v>
+        <v>0.10526315789473684</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="B9" s="19">
-        <v>0.641</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>288</v>
+        <v>333</v>
       </c>
       <c r="B10" s="19">
         <v>0.355</v>
@@ -5666,43 +6607,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>289</v>
+        <v>334</v>
       </c>
       <c r="B11" s="19">
-        <v>0.676</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>297</v>
+        <v>342</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -5712,60 +6653,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.484</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="B16">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.604</v>
+        <v>0.611</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>300</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>301</v>
+        <v>346</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>296</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -5785,7 +6726,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -5801,7 +6742,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>305</v>
+        <v>350</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5821,7 +6762,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>351</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -5841,7 +6782,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -5861,7 +6802,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>308</v>
+        <v>353</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -5881,7 +6822,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -5901,7 +6842,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>310</v>
+        <v>355</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5921,7 +6862,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>311</v>
+        <v>356</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -5941,7 +6882,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -5961,27 +6902,27 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>313</v>
+        <v>358</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>4</v>
-      </c>
-      <c r="E31" s="18">
+        <v>5</v>
+      </c>
+      <c r="E31" s="20">
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <v>0.625</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -6001,7 +6942,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -6021,7 +6962,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -6041,7 +6982,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -6061,7 +7002,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -6081,7 +7022,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -6097,7 +7038,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>320</v>
+        <v>365</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -6113,7 +7054,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -6133,7 +7074,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>322</v>
+        <v>367</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -6149,7 +7090,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>323</v>
+        <v>368</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -6165,7 +7106,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>324</v>
+        <v>369</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -6181,7 +7122,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>325</v>
+        <v>370</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -6197,7 +7138,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -6217,7 +7158,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>327</v>
+        <v>372</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -6237,7 +7178,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>328</v>
+        <v>373</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -6257,7 +7198,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>329</v>
+        <v>374</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -6273,32 +7214,32 @@
     </row>
     <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>330</v>
+        <v>375</v>
       </c>
     </row>
     <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>302</v>
+        <v>347</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>332</v>
+        <v>377</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>333</v>
+        <v>378</v>
       </c>
       <c r="B51">
         <v>3</v>
@@ -6318,7 +7259,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>334</v>
+        <v>379</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -6334,7 +7275,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>335</v>
+        <v>380</v>
       </c>
       <c r="B53">
         <v>12</v>
@@ -6354,7 +7295,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -6374,7 +7315,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="B55">
         <v>8</v>
@@ -6394,12 +7335,12 @@
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>339</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -6418,7 +7359,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>340</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -6428,22 +7369,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>341</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>342</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>344</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -6453,17 +7394,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>345</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -6473,32 +7414,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>348</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>351</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>353</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -6508,22 +7449,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>356</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -6533,32 +7474,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>362</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>363</v>
+        <v>408</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -6568,27 +7509,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>364</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>365</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>366</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>367</v>
+        <v>412</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>368</v>
+        <v>413</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -6598,17 +7539,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>369</v>
+        <v>414</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>370</v>
+        <v>415</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>371</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="444">
   <si>
     <t>日期</t>
   </si>
@@ -698,6 +698,9 @@
     <t>09-24 11:00 / 09-24 17:00</t>
   </si>
   <si>
+    <t>09-25 11:00</t>
+  </si>
+  <si>
     <t>周四002</t>
   </si>
   <si>
@@ -785,6 +788,9 @@
     <t>09-25 13:00</t>
   </si>
   <si>
+    <t>09-24 17:00 / 09-25 11:00</t>
+  </si>
+  <si>
     <t>周五002</t>
   </si>
   <si>
@@ -962,10 +968,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-23（共 380 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-23，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-24（共 381 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-24，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -992,7 +998,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-24T17:00:04+08:00）</t>
+    <t>统计（截至 2026-09-25T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1140,6 +1146,81 @@
   </si>
   <si>
     <t>1.40 ~ 1.45</t>
+  </si>
+  <si>
+    <t>1.45 ~ 1.50</t>
+  </si>
+  <si>
+    <t>1.50 ~ 1.55</t>
+  </si>
+  <si>
+    <t>1.55 ~ 1.60</t>
+  </si>
+  <si>
+    <t>1.60 ~ 1.65</t>
+  </si>
+  <si>
+    <t>1.65 ~ 1.70</t>
+  </si>
+  <si>
+    <t>1.70 ~ 1.75</t>
+  </si>
+  <si>
+    <t>1.75 ~ 1.80</t>
+  </si>
+  <si>
+    <t>1.80 ~ 1.85</t>
+  </si>
+  <si>
+    <t>1.85 ~ 1.90</t>
+  </si>
+  <si>
+    <t>1.90 ~ 1.95</t>
+  </si>
+  <si>
+    <t>1.95 ~ 2.00</t>
+  </si>
+  <si>
+    <t>2.00 ~ 2.05</t>
+  </si>
+  <si>
+    <t>2.05 ~ 2.10</t>
+  </si>
+  <si>
+    <t>2.10 ~ 2.15</t>
+  </si>
+  <si>
+    <t>2.15 ~ 2.20</t>
+  </si>
+  <si>
+    <t>2.20 ~ 2.25</t>
+  </si>
+  <si>
+    <t>2.25 ~ 2.30</t>
+  </si>
+  <si>
+    <t>2.30 ~ 2.35</t>
+  </si>
+  <si>
+    <t>2.35 ~ 2.40</t>
+  </si>
+  <si>
+    <t>2.40 ~ 2.45</t>
+  </si>
+  <si>
+    <t>2.45 ~ 2.50</t>
+  </si>
+  <si>
+    <t>2.50 ~ 2.55</t>
+  </si>
+  <si>
+    <t>2.55 ~ 2.60</t>
+  </si>
+  <si>
+    <t>2.60 ~ 2.65</t>
+  </si>
+  <si>
+    <t>2.65 ~ 2.70</t>
   </si>
   <si>
     <t>差值变化分布 ①→②（第二次 − 第一次，按赛果分组）</t>
@@ -1331,12 +1412,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1352,7 +1433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1388,10 +1469,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1399,6 +1480,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4547,16 +4629,16 @@
         <v>226</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W40" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W40" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
@@ -4564,19 +4646,19 @@
         <v>220</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>32</v>
@@ -4621,16 +4703,16 @@
         <v>226</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W41" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W41" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
@@ -4638,19 +4720,19 @@
         <v>220</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>30</v>
@@ -4695,16 +4777,16 @@
         <v>226</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W42" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W42" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -4712,19 +4794,19 @@
         <v>220</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>32</v>
@@ -4769,16 +4851,16 @@
         <v>226</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W43" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W43" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -4786,19 +4868,19 @@
         <v>220</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>32</v>
@@ -4843,16 +4925,16 @@
         <v>226</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W44" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W44" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
@@ -4860,19 +4942,19 @@
         <v>220</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>46</v>
@@ -4917,16 +4999,16 @@
         <v>226</v>
       </c>
       <c r="U45" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W45" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
@@ -4934,19 +5016,19 @@
         <v>220</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>32</v>
@@ -4991,16 +5073,16 @@
         <v>226</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W46" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W46" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -5008,19 +5090,19 @@
         <v>220</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>46</v>
@@ -5065,36 +5147,36 @@
         <v>226</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W47" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
+      </c>
+      <c r="W47" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>30</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>187</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>32</v>
@@ -5114,17 +5196,29 @@
       <c r="L48" s="5">
         <v>0.289</v>
       </c>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S48" s="4"/>
+      <c r="M48" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="N48" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="O48" s="3">
+        <v>11</v>
+      </c>
+      <c r="P48" s="4">
+        <v>3.711</v>
+      </c>
+      <c r="Q48" s="5">
+        <v>0.539</v>
+      </c>
+      <c r="R48" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S48" s="4">
+        <v>0.25</v>
+      </c>
       <c r="T48" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U48" s="2" t="s">
         <v>30</v>
@@ -5141,10 +5235,10 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>177</v>
@@ -5153,10 +5247,10 @@
         <v>178</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>30</v>
@@ -5176,17 +5270,29 @@
       <c r="L49" s="5">
         <v>0.861</v>
       </c>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S49" s="4"/>
+      <c r="M49" s="3">
+        <v>10</v>
+      </c>
+      <c r="N49" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="O49" s="3">
+        <v>80</v>
+      </c>
+      <c r="P49" s="4">
+        <v>9.282</v>
+      </c>
+      <c r="Q49" s="5">
+        <v>0.718</v>
+      </c>
+      <c r="R49" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S49" s="4">
+        <v>-0.143</v>
+      </c>
       <c r="T49" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>30</v>
@@ -5203,22 +5309,22 @@
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>32</v>
@@ -5238,17 +5344,29 @@
       <c r="L50" s="5">
         <v>0.5</v>
       </c>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S50" s="4"/>
+      <c r="M50" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="N50" s="3">
+        <v>26</v>
+      </c>
+      <c r="O50" s="3">
+        <v>8</v>
+      </c>
+      <c r="P50" s="4">
+        <v>6.118</v>
+      </c>
+      <c r="Q50" s="5">
+        <v>0.682</v>
+      </c>
+      <c r="R50" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S50" s="4">
+        <v>0.182</v>
+      </c>
       <c r="T50" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U50" s="2" t="s">
         <v>30</v>
@@ -5265,10 +5383,10 @@
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>26</v>
@@ -5277,10 +5395,10 @@
         <v>186</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>32</v>
@@ -5300,17 +5418,29 @@
       <c r="L51" s="5">
         <v>0.581</v>
       </c>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S51" s="4"/>
+      <c r="M51" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="N51" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O51" s="3">
+        <v>30</v>
+      </c>
+      <c r="P51" s="4">
+        <v>6</v>
+      </c>
+      <c r="Q51" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="R51" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S51" s="4">
+        <v>-0.081</v>
+      </c>
       <c r="T51" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>30</v>
@@ -5327,22 +5457,22 @@
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>30</v>
@@ -5362,17 +5492,29 @@
       <c r="L52" s="5">
         <v>1.049</v>
       </c>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S52" s="4"/>
+      <c r="M52" s="3">
+        <v>9.25</v>
+      </c>
+      <c r="N52" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="O52" s="3">
+        <v>60</v>
+      </c>
+      <c r="P52" s="4">
+        <v>8.201</v>
+      </c>
+      <c r="Q52" s="5">
+        <v>1.049</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S52" s="4">
+        <v>0</v>
+      </c>
       <c r="T52" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>30</v>
@@ -5389,22 +5531,22 @@
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>32</v>
@@ -5424,17 +5566,29 @@
       <c r="L53" s="5">
         <v>0.285</v>
       </c>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S53" s="4"/>
+      <c r="M53" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="N53" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O53" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="P53" s="4">
+        <v>4.015</v>
+      </c>
+      <c r="Q53" s="5">
+        <v>0.285</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S53" s="4">
+        <v>0</v>
+      </c>
       <c r="T53" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U53" s="2" t="s">
         <v>30</v>
@@ -5451,22 +5605,22 @@
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>32</v>
@@ -5486,17 +5640,29 @@
       <c r="L54" s="5">
         <v>0.247</v>
       </c>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S54" s="4"/>
+      <c r="M54" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="N54" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O54" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="P54" s="4">
+        <v>4.153</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>0.247</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S54" s="4">
+        <v>0</v>
+      </c>
       <c r="T54" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>30</v>
@@ -5513,25 +5679,25 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>46</v>
+        <v>281</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H55" s="3">
         <v>5.4</v>
@@ -5548,17 +5714,29 @@
       <c r="L55" s="5">
         <v>0.257</v>
       </c>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S55" s="4"/>
+      <c r="M55" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="N55" s="3">
+        <v>9</v>
+      </c>
+      <c r="O55" s="3">
+        <v>12</v>
+      </c>
+      <c r="P55" s="4">
+        <v>5.143</v>
+      </c>
+      <c r="Q55" s="5">
+        <v>0.257</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S55" s="4">
+        <v>0</v>
+      </c>
       <c r="T55" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U55" s="2" t="s">
         <v>30</v>
@@ -5575,22 +5753,22 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>32</v>
@@ -5610,17 +5788,29 @@
       <c r="L56" s="5">
         <v>0.25</v>
       </c>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S56" s="4"/>
+      <c r="M56" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="N56" s="3">
+        <v>7</v>
+      </c>
+      <c r="O56" s="3">
+        <v>13</v>
+      </c>
+      <c r="P56" s="4">
+        <v>4.55</v>
+      </c>
+      <c r="Q56" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S56" s="4">
+        <v>0</v>
+      </c>
       <c r="T56" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>30</v>
@@ -5637,22 +5827,22 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>32</v>
@@ -5672,17 +5862,29 @@
       <c r="L57" s="5">
         <v>0.612</v>
       </c>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S57" s="4"/>
+      <c r="M57" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="N57" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O57" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="P57" s="4">
+        <v>4.488</v>
+      </c>
+      <c r="Q57" s="5">
+        <v>0.612</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S57" s="4">
+        <v>0</v>
+      </c>
       <c r="T57" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>30</v>
@@ -5699,22 +5901,22 @@
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>32</v>
@@ -5734,17 +5936,29 @@
       <c r="L58" s="5">
         <v>0.709</v>
       </c>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S58" s="4"/>
+      <c r="M58" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="N58" s="3">
+        <v>25</v>
+      </c>
+      <c r="O58" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="P58" s="4">
+        <v>7.394</v>
+      </c>
+      <c r="Q58" s="5">
+        <v>0.856</v>
+      </c>
+      <c r="R58" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S58" s="4">
+        <v>0.147</v>
+      </c>
       <c r="T58" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>30</v>
@@ -5761,22 +5975,22 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>32</v>
@@ -5796,17 +6010,29 @@
       <c r="L59" s="5">
         <v>0.67</v>
       </c>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S59" s="4"/>
+      <c r="M59" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="N59" s="3">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
+        <v>19</v>
+      </c>
+      <c r="P59" s="4">
+        <v>5.63</v>
+      </c>
+      <c r="Q59" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S59" s="4">
+        <v>0</v>
+      </c>
       <c r="T59" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>30</v>
@@ -5823,22 +6049,22 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>32</v>
@@ -5858,17 +6084,29 @@
       <c r="L60" s="5">
         <v>1.283</v>
       </c>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S60" s="4"/>
+      <c r="M60" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="N60" s="3">
+        <v>16</v>
+      </c>
+      <c r="O60" s="3">
+        <v>14</v>
+      </c>
+      <c r="P60" s="4">
+        <v>7.467</v>
+      </c>
+      <c r="Q60" s="5">
+        <v>1.283</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S60" s="4">
+        <v>0</v>
+      </c>
       <c r="T60" s="2" t="s">
-        <v>209</v>
+        <v>257</v>
       </c>
       <c r="U60" s="2" t="s">
         <v>30</v>
@@ -5901,36 +6139,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -5945,7 +6183,7 @@
         <v>67</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2">
         <v>57</v>
@@ -5953,10 +6191,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B3">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -5968,7 +6206,7 @@
         <v>86</v>
       </c>
       <c r="F3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3">
         <v>45</v>
@@ -5979,10 +6217,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B4">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -5994,7 +6232,7 @@
         <v>67</v>
       </c>
       <c r="F4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>46</v>
@@ -6005,16 +6243,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B5">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C5">
         <v>15</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E5">
         <v>78</v>
@@ -6031,16 +6269,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B6">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>72</v>
@@ -6057,10 +6295,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -6069,7 +6307,7 @@
         <v>41</v>
       </c>
       <c r="E7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7">
         <v>76</v>
@@ -6083,10 +6321,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B8">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -6098,7 +6336,7 @@
         <v>65</v>
       </c>
       <c r="F8">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>45</v>
@@ -6109,10 +6347,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B9">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -6130,12 +6368,12 @@
         <v>25</v>
       </c>
       <c r="H9">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -6161,7 +6399,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -6187,7 +6425,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -6206,43 +6444,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C5" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -6250,16 +6488,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C6" s="13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -6267,221 +6505,221 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>7</v>
-      </c>
-      <c r="F10" s="15">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="16">
-        <v>35</v>
+        <v>308</v>
+      </c>
+      <c r="B11" s="15">
+        <v>36</v>
       </c>
       <c r="C11" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="15">
-        <v>22</v>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16">
+        <v>23</v>
       </c>
       <c r="G12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="B13" s="15">
-        <v>28</v>
+        <v>310</v>
+      </c>
+      <c r="B13" s="16">
+        <v>29</v>
       </c>
       <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="16">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="D13" s="2">
+      <c r="G13" s="2">
         <v>1</v>
-      </c>
-      <c r="E13" s="15">
-        <v>19</v>
-      </c>
-      <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B14" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9</v>
+      </c>
+      <c r="F14" s="2">
         <v>4</v>
       </c>
-      <c r="D14" s="2">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2">
-        <v>8</v>
-      </c>
-      <c r="F14" s="2">
-        <v>3</v>
-      </c>
       <c r="G14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2">
+        <v>8</v>
+      </c>
+      <c r="C15" s="16">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2">
         <v>7</v>
-      </c>
-      <c r="C15" s="15">
-        <v>20</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2">
-        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="B17" s="16">
-        <v>44</v>
+        <v>314</v>
+      </c>
+      <c r="B17" s="15">
+        <v>45</v>
       </c>
       <c r="C17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F17" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="B18" s="15">
+        <v>315</v>
+      </c>
+      <c r="B18" s="16">
         <v>22</v>
       </c>
       <c r="C18" s="2">
@@ -6493,7 +6731,7 @@
       <c r="E18" s="2">
         <v>2</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="16">
         <v>23</v>
       </c>
       <c r="G18" s="2">
@@ -6502,7 +6740,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -6531,7 +6769,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -6541,17 +6779,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B4">
         <v>59</v>
@@ -6559,154 +6797,154 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B6">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B8" s="18">
-        <v>0.10526315789473684</v>
+        <v>0.13043478260869565</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B9" s="19">
-        <v>0.64</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B10" s="19">
-        <v>0.355</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B11" s="19">
-        <v>0.674</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.457</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.611</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -6726,7 +6964,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6742,27 +6980,27 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
         <v>2</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" s="18">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F23" s="19">
-        <v>0.227</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -6782,7 +7020,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -6802,67 +7040,67 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="E26" s="18">
+        <v>6</v>
+      </c>
+      <c r="E26" s="20">
         <v>0</v>
       </c>
       <c r="F26" s="19">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="18">
         <v>0</v>
       </c>
       <c r="F27" s="19">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="18">
         <v>0</v>
       </c>
       <c r="F28" s="19">
-        <v>0.499</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -6882,7 +7120,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -6902,47 +7140,47 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="20">
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <v>0.621</v>
+        <v>0.622</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="18">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F32" s="19">
-        <v>0.68</v>
+        <v>0.683</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -6962,7 +7200,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -6982,7 +7220,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -7002,7 +7240,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -7022,7 +7260,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -7038,7 +7276,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7054,7 +7292,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -7074,7 +7312,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7090,7 +7328,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7106,7 +7344,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7122,7 +7360,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7138,7 +7376,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -7158,7 +7396,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -7178,7 +7416,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -7198,7 +7436,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7212,54 +7450,73 @@
       <c r="E47" s="18"/>
       <c r="F47" s="19"/>
     </row>
-    <row r="49" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="F50" s="11" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>377</v>
       </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" s="18"/>
+      <c r="F48" s="19"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>378</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" s="18"/>
+      <c r="F49" s="19"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>379</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>3</v>
-      </c>
-      <c r="E51" s="18">
-        <v>0</v>
-      </c>
-      <c r="F51" s="21">
-        <v>-0.195</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E51" s="18"/>
+      <c r="F51" s="19"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7271,76 +7528,461 @@
         <v>0</v>
       </c>
       <c r="E52" s="18"/>
-      <c r="F52" s="21"/>
+      <c r="F52" s="19"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B53">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>11</v>
-      </c>
-      <c r="E53" s="20">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="F53" s="21">
-        <v>-0.002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E53" s="18"/>
+      <c r="F53" s="19"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54" s="18">
-        <v>0</v>
-      </c>
-      <c r="F54" s="21">
-        <v>0.054</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B55">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>8</v>
-      </c>
-      <c r="E55" s="20">
-        <v>0</v>
-      </c>
-      <c r="F55" s="21">
-        <v>0.337</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>385</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56" s="18"/>
+      <c r="F56" s="19"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57" s="18"/>
+      <c r="F57" s="19"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>384</v>
+        <v>387</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" s="18"/>
+      <c r="F58" s="19"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>388</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" s="18"/>
+      <c r="F59" s="19"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60" s="18"/>
+      <c r="F60" s="19"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>390</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61" s="18"/>
+      <c r="F61" s="19"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>391</v>
+      </c>
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62" s="18"/>
+      <c r="F62" s="19"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>392</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" s="18"/>
+      <c r="F63" s="19"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>393</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" s="18"/>
+      <c r="F64" s="19"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>394</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="19"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>395</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="19"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>396</v>
+      </c>
+      <c r="B67">
+        <v>0</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67" s="18"/>
+      <c r="F67" s="19"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>397</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="19"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>398</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" s="18"/>
+      <c r="F69" s="19"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>399</v>
+      </c>
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+      <c r="E70" s="18"/>
+      <c r="F70" s="19"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>400</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71" s="18">
+        <v>0</v>
+      </c>
+      <c r="F71" s="19">
+        <v>2.645</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="19"/>
+    </row>
+    <row r="74" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>405</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76" s="18">
+        <v>0</v>
+      </c>
+      <c r="F76" s="21">
+        <v>-0.179</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>406</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77" s="18"/>
+      <c r="F77" s="21"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>407</v>
+      </c>
+      <c r="B78">
+        <v>15</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+      <c r="D78">
+        <v>13</v>
+      </c>
+      <c r="E78" s="22">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="F78" s="21">
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>408</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+      <c r="E79" s="18">
+        <v>0</v>
+      </c>
+      <c r="F79" s="21">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>409</v>
+      </c>
+      <c r="B80">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>11</v>
+      </c>
+      <c r="E80" s="20">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="F80" s="21">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -7359,7 +8001,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -7369,22 +8011,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -7394,17 +8036,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -7414,32 +8056,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -7449,22 +8091,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -7474,32 +8116,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -7509,27 +8151,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -7539,17 +8181,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="507">
   <si>
     <t>日期</t>
   </si>
@@ -791,6 +791,9 @@
     <t>09-24 17:00 / 09-25 11:00</t>
   </si>
   <si>
+    <t>09-25 17:00</t>
+  </si>
+  <si>
     <t>周五002</t>
   </si>
   <si>
@@ -812,6 +815,9 @@
     <t>09-25 18:00</t>
   </si>
   <si>
+    <t>09-25 11:00 / 09-25 17:00</t>
+  </si>
+  <si>
     <t>周五004</t>
   </si>
   <si>
@@ -914,6 +920,189 @@
     <t>09-26 03:00</t>
   </si>
   <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>周六001</t>
+  </si>
+  <si>
+    <t>09-26 14:00</t>
+  </si>
+  <si>
+    <t>周六002</t>
+  </si>
+  <si>
+    <t>日乙</t>
+  </si>
+  <si>
+    <t>磐城FC</t>
+  </si>
+  <si>
+    <t>仙台七夕</t>
+  </si>
+  <si>
+    <t>09-26 16:00</t>
+  </si>
+  <si>
+    <t>周六003</t>
+  </si>
+  <si>
+    <t>富山胜利</t>
+  </si>
+  <si>
+    <t>横滨FC</t>
+  </si>
+  <si>
+    <t>周六004</t>
+  </si>
+  <si>
+    <t>秋田闪电</t>
+  </si>
+  <si>
+    <t>新潟天鹅</t>
+  </si>
+  <si>
+    <t>周六005</t>
+  </si>
+  <si>
+    <t>大宫松鼠</t>
+  </si>
+  <si>
+    <t>甲府风林</t>
+  </si>
+  <si>
+    <t>周六006</t>
+  </si>
+  <si>
+    <t>大分三神</t>
+  </si>
+  <si>
+    <t>藤枝MYFC</t>
+  </si>
+  <si>
+    <t>周六007</t>
+  </si>
+  <si>
+    <t>朝鲜亚</t>
+  </si>
+  <si>
+    <t>09-26 18:30</t>
+  </si>
+  <si>
+    <t>周六008</t>
+  </si>
+  <si>
+    <t>斯洛文尼</t>
+  </si>
+  <si>
+    <t>苏格兰</t>
+  </si>
+  <si>
+    <t>09-26 21:00</t>
+  </si>
+  <si>
+    <t>周六009</t>
+  </si>
+  <si>
+    <t>赫拉克勒</t>
+  </si>
+  <si>
+    <t>维迪斯</t>
+  </si>
+  <si>
+    <t>09-26 22:30</t>
+  </si>
+  <si>
+    <t>周六010</t>
+  </si>
+  <si>
+    <t>法罗群岛</t>
+  </si>
+  <si>
+    <t>哈萨克</t>
+  </si>
+  <si>
+    <t>09-27 00:00</t>
+  </si>
+  <si>
+    <t>周六011</t>
+  </si>
+  <si>
+    <t>冰岛</t>
+  </si>
+  <si>
+    <t>爱沙尼亚</t>
+  </si>
+  <si>
+    <t>周六012</t>
+  </si>
+  <si>
+    <t>保加利亚</t>
+  </si>
+  <si>
+    <t>卢森堡</t>
+  </si>
+  <si>
+    <t>周六013</t>
+  </si>
+  <si>
+    <t>罗达JC</t>
+  </si>
+  <si>
+    <t>瓦尔韦克</t>
+  </si>
+  <si>
+    <t>09-27 02:00</t>
+  </si>
+  <si>
+    <t>周六014</t>
+  </si>
+  <si>
+    <t>捷克</t>
+  </si>
+  <si>
+    <t>克罗地亚</t>
+  </si>
+  <si>
+    <t>09-27 02:45</t>
+  </si>
+  <si>
+    <t>周六015</t>
+  </si>
+  <si>
+    <t>北马其顿</t>
+  </si>
+  <si>
+    <t>瑞士</t>
+  </si>
+  <si>
+    <t>周六016</t>
+  </si>
+  <si>
+    <t>英格兰</t>
+  </si>
+  <si>
+    <t>西班牙</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>江原FC</t>
+  </si>
+  <si>
+    <t>09-27 18:00</t>
+  </si>
+  <si>
+    <t>格拉夫</t>
+  </si>
+  <si>
+    <t>登博思</t>
+  </si>
+  <si>
+    <t>09-27 20:30</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -968,10 +1157,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-24（共 381 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-24，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-25（共 382 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-25，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -998,7 +1187,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-25T11:00:04+08:00）</t>
+    <t>统计（截至 2026-09-25T17:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1820,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5221,16 +5410,16 @@
         <v>257</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W48" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W48" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
@@ -5238,7 +5427,7 @@
         <v>253</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>177</v>
@@ -5247,10 +5436,10 @@
         <v>178</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>30</v>
@@ -5312,61 +5501,61 @@
         <v>253</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H50" s="3">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I50" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" s="3">
         <v>8</v>
       </c>
       <c r="K50" s="4">
-        <v>6</v>
+        <v>6.118</v>
       </c>
       <c r="L50" s="5">
-        <v>0.5</v>
+        <v>0.682</v>
       </c>
       <c r="M50" s="3">
-        <v>6.8</v>
+        <v>8.2</v>
       </c>
       <c r="N50" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O50" s="3">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="P50" s="4">
-        <v>6.118</v>
+        <v>7.272</v>
       </c>
       <c r="Q50" s="5">
-        <v>0.682</v>
+        <v>0.928</v>
       </c>
       <c r="R50" s="9" t="s">
         <v>94</v>
       </c>
       <c r="S50" s="4">
-        <v>0.182</v>
+        <v>0.246</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U50" s="2" t="s">
         <v>30</v>
@@ -5386,7 +5575,7 @@
         <v>253</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>26</v>
@@ -5395,52 +5584,52 @@
         <v>186</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H51" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J51" s="3">
+        <v>30</v>
+      </c>
+      <c r="K51" s="4">
         <v>6</v>
       </c>
-      <c r="I51" s="3">
-        <v>7</v>
-      </c>
-      <c r="J51" s="3">
-        <v>24</v>
-      </c>
-      <c r="K51" s="4">
-        <v>5.419</v>
-      </c>
       <c r="L51" s="5">
-        <v>0.581</v>
+        <v>0.5</v>
       </c>
       <c r="M51" s="3">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="N51" s="3">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="O51" s="3">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="P51" s="4">
-        <v>6</v>
+        <v>7.734</v>
       </c>
       <c r="Q51" s="5">
-        <v>0.5</v>
+        <v>0.266</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>73</v>
       </c>
       <c r="S51" s="4">
-        <v>-0.081</v>
+        <v>-0.234</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U51" s="2" t="s">
         <v>30</v>
@@ -5460,19 +5649,19 @@
         <v>253</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>30</v>
@@ -5493,28 +5682,28 @@
         <v>1.049</v>
       </c>
       <c r="M52" s="3">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="N52" s="3">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="O52" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P52" s="4">
-        <v>8.201</v>
+        <v>10.055</v>
       </c>
       <c r="Q52" s="5">
-        <v>1.049</v>
-      </c>
-      <c r="R52" s="6" t="s">
-        <v>80</v>
+        <v>0.945</v>
+      </c>
+      <c r="R52" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S52" s="4">
-        <v>0</v>
+        <v>-0.104</v>
       </c>
       <c r="T52" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U52" s="2" t="s">
         <v>30</v>
@@ -5534,19 +5723,19 @@
         <v>253</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>32</v>
@@ -5573,22 +5762,22 @@
         <v>6.5</v>
       </c>
       <c r="O53" s="3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="P53" s="4">
-        <v>4.015</v>
+        <v>4.086</v>
       </c>
       <c r="Q53" s="5">
-        <v>0.285</v>
-      </c>
-      <c r="R53" s="6" t="s">
-        <v>80</v>
+        <v>0.214</v>
+      </c>
+      <c r="R53" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S53" s="4">
-        <v>0</v>
+        <v>-0.071</v>
       </c>
       <c r="T53" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U53" s="2" t="s">
         <v>30</v>
@@ -5608,19 +5797,19 @@
         <v>253</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>32</v>
@@ -5641,7 +5830,7 @@
         <v>0.247</v>
       </c>
       <c r="M54" s="3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N54" s="3">
         <v>6.5</v>
@@ -5653,16 +5842,16 @@
         <v>4.153</v>
       </c>
       <c r="Q54" s="5">
-        <v>0.247</v>
-      </c>
-      <c r="R54" s="6" t="s">
-        <v>80</v>
+        <v>0.447</v>
+      </c>
+      <c r="R54" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S54" s="4">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T54" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U54" s="2" t="s">
         <v>30</v>
@@ -5682,22 +5871,22 @@
         <v>253</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>32</v>
+        <v>283</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H55" s="3">
         <v>5.4</v>
@@ -5715,28 +5904,28 @@
         <v>0.257</v>
       </c>
       <c r="M55" s="3">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="N55" s="3">
-        <v>9</v>
+        <v>9.75</v>
       </c>
       <c r="O55" s="3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="P55" s="4">
-        <v>5.143</v>
+        <v>5.478</v>
       </c>
       <c r="Q55" s="5">
-        <v>0.257</v>
-      </c>
-      <c r="R55" s="6" t="s">
-        <v>80</v>
+        <v>0.722</v>
+      </c>
+      <c r="R55" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S55" s="4">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="T55" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U55" s="2" t="s">
         <v>30</v>
@@ -5756,19 +5945,19 @@
         <v>253</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>32</v>
@@ -5810,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U56" s="2" t="s">
         <v>30</v>
@@ -5830,19 +6019,19 @@
         <v>253</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>32</v>
@@ -5884,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U57" s="2" t="s">
         <v>30</v>
@@ -5904,61 +6093,61 @@
         <v>253</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H58" s="3">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="I58" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J58" s="3">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="K58" s="4">
-        <v>6.541</v>
+        <v>7.394</v>
       </c>
       <c r="L58" s="5">
-        <v>0.709</v>
+        <v>0.856</v>
       </c>
       <c r="M58" s="3">
-        <v>8.25</v>
+        <v>9.9</v>
       </c>
       <c r="N58" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O58" s="3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="P58" s="4">
-        <v>7.394</v>
+        <v>8.313</v>
       </c>
       <c r="Q58" s="5">
-        <v>0.856</v>
+        <v>1.587</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>94</v>
       </c>
       <c r="S58" s="4">
-        <v>0.147</v>
+        <v>0.731</v>
       </c>
       <c r="T58" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U58" s="2" t="s">
         <v>30</v>
@@ -5978,19 +6167,19 @@
         <v>253</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>32</v>
@@ -6011,28 +6200,28 @@
         <v>0.67</v>
       </c>
       <c r="M59" s="3">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="N59" s="3">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="O59" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P59" s="4">
-        <v>5.63</v>
+        <v>6.072</v>
       </c>
       <c r="Q59" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="R59" s="6" t="s">
-        <v>80</v>
+        <v>0.428</v>
+      </c>
+      <c r="R59" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S59" s="4">
-        <v>0</v>
+        <v>-0.242</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U59" s="2" t="s">
         <v>30</v>
@@ -6052,19 +6241,19 @@
         <v>253</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>32</v>
@@ -6085,28 +6274,28 @@
         <v>1.283</v>
       </c>
       <c r="M60" s="3">
-        <v>8.75</v>
+        <v>9.8</v>
       </c>
       <c r="N60" s="3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="O60" s="3">
         <v>14</v>
       </c>
       <c r="P60" s="4">
-        <v>7.467</v>
+        <v>7.969</v>
       </c>
       <c r="Q60" s="5">
-        <v>1.283</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>80</v>
+        <v>1.831</v>
+      </c>
+      <c r="R60" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S60" s="4">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="U60" s="2" t="s">
         <v>30</v>
@@ -6118,6 +6307,1122 @@
         <v>30</v>
       </c>
       <c r="X60" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="I61" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="J61" s="3">
+        <v>9</v>
+      </c>
+      <c r="K61" s="4">
+        <v>3.527</v>
+      </c>
+      <c r="L61" s="5">
+        <v>0.273</v>
+      </c>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S61" s="4"/>
+      <c r="T61" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I62" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="J62" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K62" s="4">
+        <v>4.375</v>
+      </c>
+      <c r="L62" s="5">
+        <v>0.425</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S62" s="4"/>
+      <c r="T62" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H63" s="3">
+        <v>6</v>
+      </c>
+      <c r="I63" s="3">
+        <v>12</v>
+      </c>
+      <c r="J63" s="3">
+        <v>11</v>
+      </c>
+      <c r="K63" s="4">
+        <v>5.739</v>
+      </c>
+      <c r="L63" s="5">
+        <v>0.261</v>
+      </c>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S63" s="4"/>
+      <c r="T63" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H64" s="3">
+        <v>4</v>
+      </c>
+      <c r="I64" s="3">
+        <v>7</v>
+      </c>
+      <c r="J64" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K64" s="4">
+        <v>3.621</v>
+      </c>
+      <c r="L64" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S64" s="4"/>
+      <c r="T64" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X64" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="I65" s="3">
+        <v>8</v>
+      </c>
+      <c r="J65" s="3">
+        <v>15</v>
+      </c>
+      <c r="K65" s="4">
+        <v>5.217</v>
+      </c>
+      <c r="L65" s="5">
+        <v>0.383</v>
+      </c>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S65" s="4"/>
+      <c r="T65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="I66" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J66" s="3">
+        <v>7</v>
+      </c>
+      <c r="K66" s="4">
+        <v>3.37</v>
+      </c>
+      <c r="L66" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S66" s="4"/>
+      <c r="T66" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H67" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="I67" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="J67" s="3">
+        <v>21</v>
+      </c>
+      <c r="K67" s="4">
+        <v>5.362</v>
+      </c>
+      <c r="L67" s="5">
+        <v>0.338</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S67" s="4"/>
+      <c r="T67" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H68" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="I68" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J68" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="K68" s="4">
+        <v>3.984</v>
+      </c>
+      <c r="L68" s="5">
+        <v>0.216</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S68" s="4"/>
+      <c r="T68" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H69" s="3">
+        <v>9.3</v>
+      </c>
+      <c r="I69" s="3">
+        <v>13</v>
+      </c>
+      <c r="J69" s="3">
+        <v>24</v>
+      </c>
+      <c r="K69" s="4">
+        <v>8.432</v>
+      </c>
+      <c r="L69" s="5">
+        <v>0.868</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S69" s="4"/>
+      <c r="T69" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="3">
+        <v>3.9</v>
+      </c>
+      <c r="I70" s="3">
+        <v>7</v>
+      </c>
+      <c r="J70" s="3">
+        <v>8</v>
+      </c>
+      <c r="K70" s="4">
+        <v>3.733</v>
+      </c>
+      <c r="L70" s="5">
+        <v>0.167</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S70" s="4"/>
+      <c r="T70" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H71" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="I71" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="J71" s="3">
+        <v>23</v>
+      </c>
+      <c r="K71" s="4">
+        <v>5.189</v>
+      </c>
+      <c r="L71" s="5">
+        <v>0.511</v>
+      </c>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S71" s="4"/>
+      <c r="T71" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="I72" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="J72" s="3">
+        <v>8</v>
+      </c>
+      <c r="K72" s="4">
+        <v>3.646</v>
+      </c>
+      <c r="L72" s="5">
+        <v>0.154</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S72" s="4"/>
+      <c r="T72" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="I73" s="3">
+        <v>11</v>
+      </c>
+      <c r="J73" s="3">
+        <v>12</v>
+      </c>
+      <c r="K73" s="4">
+        <v>5.739</v>
+      </c>
+      <c r="L73" s="5">
+        <v>0.461</v>
+      </c>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S73" s="4"/>
+      <c r="T73" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X73" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="3">
+        <v>5</v>
+      </c>
+      <c r="I74" s="3">
+        <v>11</v>
+      </c>
+      <c r="J74" s="3">
+        <v>8</v>
+      </c>
+      <c r="K74" s="4">
+        <v>4.632</v>
+      </c>
+      <c r="L74" s="5">
+        <v>0.368</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S74" s="4"/>
+      <c r="T74" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H75" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="I75" s="3">
+        <v>16</v>
+      </c>
+      <c r="J75" s="3">
+        <v>7</v>
+      </c>
+      <c r="K75" s="4">
+        <v>4.87</v>
+      </c>
+      <c r="L75" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S75" s="4"/>
+      <c r="T75" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X75" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H76" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="I76" s="3">
+        <v>10</v>
+      </c>
+      <c r="J76" s="3">
+        <v>9</v>
+      </c>
+      <c r="K76" s="4">
+        <v>4.737</v>
+      </c>
+      <c r="L76" s="5">
+        <v>0.463</v>
+      </c>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S76" s="4"/>
+      <c r="T76" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J77" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="K77" s="4">
+        <v>3.525</v>
+      </c>
+      <c r="L77" s="5">
+        <v>0.175</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S77" s="4"/>
+      <c r="T77" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" s="3">
+        <v>13</v>
+      </c>
+      <c r="I78" s="3">
+        <v>22</v>
+      </c>
+      <c r="J78" s="3">
+        <v>23</v>
+      </c>
+      <c r="K78" s="4">
+        <v>11.244</v>
+      </c>
+      <c r="L78" s="5">
+        <v>1.756</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S78" s="4"/>
+      <c r="T78" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X78" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6139,36 +7444,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>300</v>
+        <v>363</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="B2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -6180,7 +7485,7 @@
         <v>68</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>52</v>
@@ -6191,7 +7496,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="B3">
         <v>323</v>
@@ -6217,7 +7522,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="B4">
         <v>315</v>
@@ -6243,7 +7548,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="B5">
         <v>307</v>
@@ -6269,7 +7574,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="B6">
         <v>299</v>
@@ -6295,7 +7600,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="B7">
         <v>281</v>
@@ -6321,7 +7626,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="B8">
         <v>272</v>
@@ -6347,7 +7652,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="B9">
         <v>251</v>
@@ -6373,7 +7678,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="B10">
         <v>232</v>
@@ -6399,7 +7704,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>316</v>
+        <v>379</v>
       </c>
       <c r="B11">
         <v>210</v>
@@ -6425,7 +7730,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -6444,43 +7749,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>318</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>319</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>320</v>
+        <v>383</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>321</v>
+        <v>384</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>322</v>
+        <v>385</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>323</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="C5" s="13">
         <v>45</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>324</v>
+        <v>387</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -6488,16 +7793,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="C6" s="13">
         <v>36</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>325</v>
+        <v>388</v>
       </c>
       <c r="E6" s="13">
         <v>25</v>
@@ -6505,58 +7810,58 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>326</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>301</v>
+        <v>364</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>303</v>
+        <v>366</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>304</v>
+        <v>367</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>305</v>
+        <v>368</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>307</v>
+        <v>370</v>
       </c>
       <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
       <c r="G10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>308</v>
+        <v>371</v>
       </c>
       <c r="B11" s="15">
         <v>36</v>
@@ -6579,7 +7884,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="B12" s="2">
         <v>16</v>
@@ -6602,7 +7907,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="B13" s="16">
         <v>29</v>
@@ -6625,7 +7930,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="B14" s="2">
         <v>8</v>
@@ -6648,7 +7953,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="B15" s="2">
         <v>8</v>
@@ -6671,7 +7976,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="B16" s="2">
         <v>14</v>
@@ -6694,7 +7999,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="B17" s="15">
         <v>45</v>
@@ -6717,7 +8022,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>315</v>
+        <v>378</v>
       </c>
       <c r="B18" s="16">
         <v>22</v>
@@ -6740,7 +8045,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>316</v>
+        <v>379</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -6779,25 +8084,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>327</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>328</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="B4">
-        <v>59</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="B5">
         <v>46</v>
@@ -6805,15 +8110,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="B6">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -6821,23 +8126,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>396</v>
       </c>
       <c r="B8" s="18">
-        <v>0.13043478260869565</v>
+        <v>0.1276595744680851</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>334</v>
+        <v>397</v>
       </c>
       <c r="B9" s="19">
-        <v>0.655</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>335</v>
+        <v>398</v>
       </c>
       <c r="B10" s="19">
         <v>0.39</v>
@@ -6845,43 +8150,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>336</v>
+        <v>399</v>
       </c>
       <c r="B11" s="19">
-        <v>0.695</v>
+        <v>0.691</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>337</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>340</v>
+        <v>403</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>344</v>
+        <v>407</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -6891,60 +8196,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.497</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>408</v>
       </c>
       <c r="B16">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.614</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>346</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>347</v>
+        <v>410</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>348</v>
+        <v>411</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>350</v>
+        <v>413</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -6964,7 +8269,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>351</v>
+        <v>414</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -6980,7 +8285,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>352</v>
+        <v>415</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -7000,7 +8305,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -7020,7 +8325,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>354</v>
+        <v>417</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -7040,7 +8345,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>355</v>
+        <v>418</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -7060,7 +8365,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>356</v>
+        <v>419</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -7080,7 +8385,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>357</v>
+        <v>420</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -7100,27 +8405,27 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>358</v>
+        <v>421</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="18">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F29" s="19">
-        <v>0.527</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -7140,7 +8445,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>360</v>
+        <v>423</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -7160,7 +8465,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>361</v>
+        <v>424</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -7180,7 +8485,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>362</v>
+        <v>425</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -7200,7 +8505,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>363</v>
+        <v>426</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -7220,7 +8525,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>364</v>
+        <v>427</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -7240,7 +8545,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -7260,7 +8565,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>366</v>
+        <v>429</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -7276,7 +8581,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -7292,7 +8597,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>368</v>
+        <v>431</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -7312,7 +8617,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>369</v>
+        <v>432</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -7328,7 +8633,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>370</v>
+        <v>433</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -7344,7 +8649,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>371</v>
+        <v>434</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -7360,7 +8665,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -7376,7 +8681,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>373</v>
+        <v>436</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -7396,7 +8701,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>374</v>
+        <v>437</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -7416,7 +8721,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>375</v>
+        <v>438</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -7436,7 +8741,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -7452,7 +8757,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>377</v>
+        <v>440</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -7468,7 +8773,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>378</v>
+        <v>441</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -7484,7 +8789,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>379</v>
+        <v>442</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -7500,7 +8805,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>380</v>
+        <v>443</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -7516,7 +8821,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>381</v>
+        <v>444</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -7532,7 +8837,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>382</v>
+        <v>445</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7548,7 +8853,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>383</v>
+        <v>446</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7564,7 +8869,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>384</v>
+        <v>447</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -7580,7 +8885,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>385</v>
+        <v>448</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -7596,7 +8901,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>386</v>
+        <v>449</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -7612,7 +8917,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>387</v>
+        <v>450</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -7628,7 +8933,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>388</v>
+        <v>451</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -7644,7 +8949,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>389</v>
+        <v>452</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -7660,7 +8965,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>390</v>
+        <v>453</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -7676,7 +8981,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>391</v>
+        <v>454</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -7692,7 +8997,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>392</v>
+        <v>455</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -7708,7 +9013,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>393</v>
+        <v>456</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -7724,7 +9029,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>394</v>
+        <v>457</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -7740,7 +9045,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>395</v>
+        <v>458</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -7756,7 +9061,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -7772,7 +9077,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>397</v>
+        <v>460</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -7788,7 +9093,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>398</v>
+        <v>461</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -7804,7 +9109,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -7820,7 +9125,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>400</v>
+        <v>463</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7840,7 +9145,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>401</v>
+        <v>464</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -7856,32 +9161,32 @@
     </row>
     <row r="74" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>402</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>403</v>
+        <v>466</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>339</v>
+        <v>402</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>341</v>
+        <v>404</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>349</v>
+        <v>412</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>404</v>
+        <v>467</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
       <c r="B76">
         <v>4</v>
@@ -7901,7 +9206,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>406</v>
+        <v>469</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -7917,7 +9222,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>407</v>
+        <v>470</v>
       </c>
       <c r="B78">
         <v>15</v>
@@ -7937,7 +9242,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>408</v>
+        <v>471</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -7957,32 +9262,32 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>409</v>
+        <v>472</v>
       </c>
       <c r="B80">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E80" s="20">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="F80" s="21">
-        <v>0.34</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>410</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>411</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -8001,7 +9306,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>412</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -8011,22 +9316,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>413</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>415</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>416</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -8036,17 +9341,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>417</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>418</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>419</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -8056,32 +9361,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>420</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>421</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>422</v>
+        <v>485</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>423</v>
+        <v>486</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>424</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>425</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -8091,22 +9396,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>426</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>427</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>428</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>429</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -8116,32 +9421,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>430</v>
+        <v>493</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>431</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>432</v>
+        <v>495</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>433</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>434</v>
+        <v>497</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>435</v>
+        <v>498</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -8151,27 +9456,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>436</v>
+        <v>499</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>437</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>438</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>439</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>440</v>
+        <v>503</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -8181,17 +9486,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>441</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>442</v>
+        <v>505</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>443</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="511">
   <si>
     <t>日期</t>
   </si>
@@ -791,7 +791,7 @@
     <t>09-24 17:00 / 09-25 11:00</t>
   </si>
   <si>
-    <t>09-25 17:00</t>
+    <t>09-26 11:00</t>
   </si>
   <si>
     <t>周五002</t>
@@ -827,6 +827,9 @@
     <t>09-25 18:30</t>
   </si>
   <si>
+    <t>4:0</t>
+  </si>
+  <si>
     <t>周五005</t>
   </si>
   <si>
@@ -836,6 +839,9 @@
     <t>乌兹别女</t>
   </si>
   <si>
+    <t>6:3</t>
+  </si>
+  <si>
     <t>周五006</t>
   </si>
   <si>
@@ -869,6 +875,9 @@
     <t>09-26 02:45</t>
   </si>
   <si>
+    <t>0:2</t>
+  </si>
+  <si>
     <t>周五009</t>
   </si>
   <si>
@@ -929,6 +938,9 @@
     <t>09-26 14:00</t>
   </si>
   <si>
+    <t>09-25 17:00 / 09-26 11:00</t>
+  </si>
+  <si>
     <t>周六002</t>
   </si>
   <si>
@@ -1181,13 +1193,13 @@
     <t>2026-05-29</t>
   </si>
   <si>
-    <t>2026-08-18</t>
+    <t>2026-08-24</t>
   </si>
   <si>
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-25T17:00:04+08:00）</t>
+    <t>统计（截至 2026-09-26T11:00:08+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1601,12 +1613,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7D7"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDEBD0"/>
+        <fgColor rgb="FFF8D7D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -1622,7 +1634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1658,10 +1670,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1669,7 +1681,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5484,16 +5495,16 @@
         <v>257</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W49" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W49" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
@@ -5558,16 +5569,16 @@
         <v>266</v>
       </c>
       <c r="U50" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W50" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
@@ -5632,16 +5643,16 @@
         <v>266</v>
       </c>
       <c r="U51" s="2" t="s">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W51" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W51" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
@@ -5649,16 +5660,16 @@
         <v>253</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>269</v>
@@ -5706,16 +5717,16 @@
         <v>266</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>30</v>
+        <v>274</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W52" s="2" t="s">
-        <v>30</v>
+        <v>197</v>
+      </c>
+      <c r="W52" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
@@ -5723,19 +5734,19 @@
         <v>253</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>32</v>
@@ -5780,16 +5791,16 @@
         <v>266</v>
       </c>
       <c r="U53" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V53" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W53" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
@@ -5797,19 +5808,19 @@
         <v>253</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>32</v>
@@ -5854,16 +5865,16 @@
         <v>266</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W54" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
@@ -5871,19 +5882,19 @@
         <v>253</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G55" s="8" t="s">
         <v>46</v>
@@ -5928,16 +5939,16 @@
         <v>266</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W55" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W55" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
@@ -5945,19 +5956,19 @@
         <v>253</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>32</v>
@@ -6002,16 +6013,16 @@
         <v>266</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W56" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W56" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
@@ -6019,19 +6030,19 @@
         <v>253</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>32</v>
@@ -6076,16 +6087,16 @@
         <v>266</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W57" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W57" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X57" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
@@ -6093,19 +6104,19 @@
         <v>253</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>32</v>
@@ -6150,16 +6161,16 @@
         <v>266</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W58" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W58" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X58" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
@@ -6167,19 +6178,19 @@
         <v>253</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>32</v>
@@ -6224,16 +6235,16 @@
         <v>266</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
+      </c>
+      <c r="W59" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X59" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
@@ -6241,19 +6252,19 @@
         <v>253</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>32</v>
@@ -6298,24 +6309,24 @@
         <v>266</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W60" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X60" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>26</v>
@@ -6327,7 +6338,7 @@
         <v>211</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>32</v>
@@ -6347,17 +6358,29 @@
       <c r="L61" s="5">
         <v>0.273</v>
       </c>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S61" s="4"/>
+      <c r="M61" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="N61" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="O61" s="3">
+        <v>9</v>
+      </c>
+      <c r="P61" s="4">
+        <v>3.527</v>
+      </c>
+      <c r="Q61" s="5">
+        <v>0.273</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S61" s="4">
+        <v>0</v>
+      </c>
       <c r="T61" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U61" s="2" t="s">
         <v>30</v>
@@ -6374,22 +6397,22 @@
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>32</v>
@@ -6409,17 +6432,29 @@
       <c r="L62" s="5">
         <v>0.425</v>
       </c>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S62" s="4"/>
+      <c r="M62" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="N62" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="O62" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="P62" s="4">
+        <v>4.375</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>0.425</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S62" s="4">
+        <v>0</v>
+      </c>
       <c r="T62" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U62" s="2" t="s">
         <v>30</v>
@@ -6436,22 +6471,22 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>32</v>
@@ -6471,17 +6506,29 @@
       <c r="L63" s="5">
         <v>0.261</v>
       </c>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S63" s="4"/>
+      <c r="M63" s="3">
+        <v>6</v>
+      </c>
+      <c r="N63" s="3">
+        <v>12</v>
+      </c>
+      <c r="O63" s="3">
+        <v>11</v>
+      </c>
+      <c r="P63" s="4">
+        <v>5.739</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>0.261</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S63" s="4">
+        <v>0</v>
+      </c>
       <c r="T63" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U63" s="2" t="s">
         <v>30</v>
@@ -6498,22 +6545,22 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>32</v>
@@ -6533,17 +6580,29 @@
       <c r="L64" s="5">
         <v>0.379</v>
       </c>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S64" s="4"/>
+      <c r="M64" s="3">
+        <v>4</v>
+      </c>
+      <c r="N64" s="3">
+        <v>7</v>
+      </c>
+      <c r="O64" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="P64" s="4">
+        <v>3.621</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>0.379</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S64" s="4">
+        <v>0</v>
+      </c>
       <c r="T64" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U64" s="2" t="s">
         <v>30</v>
@@ -6560,22 +6619,22 @@
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>32</v>
@@ -6595,17 +6654,29 @@
       <c r="L65" s="5">
         <v>0.383</v>
       </c>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S65" s="4"/>
+      <c r="M65" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="N65" s="3">
+        <v>8</v>
+      </c>
+      <c r="O65" s="3">
+        <v>15</v>
+      </c>
+      <c r="P65" s="4">
+        <v>5.217</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>0.383</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S65" s="4">
+        <v>0</v>
+      </c>
       <c r="T65" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U65" s="2" t="s">
         <v>30</v>
@@ -6622,22 +6693,22 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>32</v>
@@ -6657,17 +6728,29 @@
       <c r="L66" s="5">
         <v>0.13</v>
       </c>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S66" s="4"/>
+      <c r="M66" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="N66" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O66" s="3">
+        <v>7</v>
+      </c>
+      <c r="P66" s="4">
+        <v>3.37</v>
+      </c>
+      <c r="Q66" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S66" s="4">
+        <v>0</v>
+      </c>
       <c r="T66" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U66" s="2" t="s">
         <v>30</v>
@@ -6684,10 +6767,10 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>26</v>
@@ -6696,10 +6779,10 @@
         <v>55</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>32</v>
@@ -6719,17 +6802,29 @@
       <c r="L67" s="5">
         <v>0.338</v>
       </c>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S67" s="4"/>
+      <c r="M67" s="3">
+        <v>6</v>
+      </c>
+      <c r="N67" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="O67" s="3">
+        <v>25</v>
+      </c>
+      <c r="P67" s="4">
+        <v>5.59</v>
+      </c>
+      <c r="Q67" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="R67" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S67" s="4">
+        <v>0.072</v>
+      </c>
       <c r="T67" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>30</v>
@@ -6746,25 +6841,25 @@
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>46</v>
+        <v>331</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H68" s="3">
         <v>4.2</v>
@@ -6781,17 +6876,29 @@
       <c r="L68" s="5">
         <v>0.216</v>
       </c>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S68" s="4"/>
+      <c r="M68" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="N68" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="O68" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="P68" s="4">
+        <v>3.984</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>0.216</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S68" s="4">
+        <v>0</v>
+      </c>
       <c r="T68" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>30</v>
@@ -6808,22 +6915,22 @@
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>32</v>
@@ -6843,17 +6950,29 @@
       <c r="L69" s="5">
         <v>0.868</v>
       </c>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S69" s="4"/>
+      <c r="M69" s="3">
+        <v>9.3</v>
+      </c>
+      <c r="N69" s="3">
+        <v>13</v>
+      </c>
+      <c r="O69" s="3">
+        <v>24</v>
+      </c>
+      <c r="P69" s="4">
+        <v>8.432</v>
+      </c>
+      <c r="Q69" s="5">
+        <v>0.868</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S69" s="4">
+        <v>0</v>
+      </c>
       <c r="T69" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U69" s="2" t="s">
         <v>30</v>
@@ -6870,22 +6989,22 @@
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>32</v>
@@ -6905,17 +7024,29 @@
       <c r="L70" s="5">
         <v>0.167</v>
       </c>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S70" s="4"/>
+      <c r="M70" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="N70" s="3">
+        <v>6.75</v>
+      </c>
+      <c r="O70" s="3">
+        <v>8</v>
+      </c>
+      <c r="P70" s="4">
+        <v>3.661</v>
+      </c>
+      <c r="Q70" s="5">
+        <v>0.139</v>
+      </c>
+      <c r="R70" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S70" s="4">
+        <v>-0.028</v>
+      </c>
       <c r="T70" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U70" s="2" t="s">
         <v>30</v>
@@ -6932,22 +7063,22 @@
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>32</v>
@@ -6967,17 +7098,29 @@
       <c r="L71" s="5">
         <v>0.511</v>
       </c>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S71" s="4"/>
+      <c r="M71" s="3">
+        <v>5.7</v>
+      </c>
+      <c r="N71" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O71" s="3">
+        <v>23</v>
+      </c>
+      <c r="P71" s="4">
+        <v>5.189</v>
+      </c>
+      <c r="Q71" s="5">
+        <v>0.511</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S71" s="4">
+        <v>0</v>
+      </c>
       <c r="T71" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U71" s="2" t="s">
         <v>30</v>
@@ -6994,22 +7137,22 @@
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>32</v>
@@ -7029,17 +7172,29 @@
       <c r="L72" s="5">
         <v>0.154</v>
       </c>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S72" s="4"/>
+      <c r="M72" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="N72" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="O72" s="3">
+        <v>8</v>
+      </c>
+      <c r="P72" s="4">
+        <v>3.646</v>
+      </c>
+      <c r="Q72" s="5">
+        <v>0.154</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S72" s="4">
+        <v>0</v>
+      </c>
       <c r="T72" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U72" s="2" t="s">
         <v>30</v>
@@ -7056,22 +7211,22 @@
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>32</v>
@@ -7091,17 +7246,29 @@
       <c r="L73" s="5">
         <v>0.461</v>
       </c>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S73" s="4"/>
+      <c r="M73" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="N73" s="3">
+        <v>11</v>
+      </c>
+      <c r="O73" s="3">
+        <v>12</v>
+      </c>
+      <c r="P73" s="4">
+        <v>5.739</v>
+      </c>
+      <c r="Q73" s="5">
+        <v>0.461</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S73" s="4">
+        <v>0</v>
+      </c>
       <c r="T73" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U73" s="2" t="s">
         <v>30</v>
@@ -7118,22 +7285,22 @@
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>32</v>
@@ -7153,17 +7320,29 @@
       <c r="L74" s="5">
         <v>0.368</v>
       </c>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S74" s="4"/>
+      <c r="M74" s="3">
+        <v>5</v>
+      </c>
+      <c r="N74" s="3">
+        <v>11</v>
+      </c>
+      <c r="O74" s="3">
+        <v>8</v>
+      </c>
+      <c r="P74" s="4">
+        <v>4.632</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>0.368</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S74" s="4">
+        <v>0</v>
+      </c>
       <c r="T74" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U74" s="2" t="s">
         <v>30</v>
@@ -7180,22 +7359,22 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>32</v>
@@ -7215,17 +7394,29 @@
       <c r="L75" s="5">
         <v>0.53</v>
       </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S75" s="4"/>
+      <c r="M75" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="N75" s="3">
+        <v>16</v>
+      </c>
+      <c r="O75" s="3">
+        <v>7</v>
+      </c>
+      <c r="P75" s="4">
+        <v>4.87</v>
+      </c>
+      <c r="Q75" s="5">
+        <v>0.53</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S75" s="4">
+        <v>0</v>
+      </c>
       <c r="T75" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U75" s="2" t="s">
         <v>30</v>
@@ -7242,25 +7433,25 @@
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>46</v>
+        <v>353</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H76" s="3">
         <v>5.2</v>
@@ -7277,17 +7468,29 @@
       <c r="L76" s="5">
         <v>0.463</v>
       </c>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S76" s="4"/>
+      <c r="M76" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="N76" s="3">
+        <v>11</v>
+      </c>
+      <c r="O76" s="3">
+        <v>9</v>
+      </c>
+      <c r="P76" s="4">
+        <v>4.95</v>
+      </c>
+      <c r="Q76" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="R76" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S76" s="4">
+        <v>0.187</v>
+      </c>
       <c r="T76" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U76" s="2" t="s">
         <v>30</v>
@@ -7304,7 +7507,7 @@
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>25</v>
@@ -7313,13 +7516,13 @@
         <v>48</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>32</v>
@@ -7339,17 +7542,29 @@
       <c r="L77" s="5">
         <v>0.175</v>
       </c>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S77" s="4"/>
+      <c r="M77" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="N77" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O77" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="P77" s="4">
+        <v>3.525</v>
+      </c>
+      <c r="Q77" s="5">
+        <v>0.175</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S77" s="4">
+        <v>0</v>
+      </c>
       <c r="T77" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U77" s="2" t="s">
         <v>30</v>
@@ -7366,22 +7581,22 @@
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>32</v>
@@ -7401,17 +7616,29 @@
       <c r="L78" s="5">
         <v>1.756</v>
       </c>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S78" s="4"/>
+      <c r="M78" s="3">
+        <v>13</v>
+      </c>
+      <c r="N78" s="3">
+        <v>22</v>
+      </c>
+      <c r="O78" s="3">
+        <v>23</v>
+      </c>
+      <c r="P78" s="4">
+        <v>11.244</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>1.756</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S78" s="4">
+        <v>0</v>
+      </c>
       <c r="T78" s="2" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="U78" s="2" t="s">
         <v>30</v>
@@ -7444,33 +7671,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B2">
         <v>325</v>
@@ -7496,13 +7723,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B3">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>58</v>
@@ -7522,10 +7749,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B4">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -7534,7 +7761,7 @@
         <v>47</v>
       </c>
       <c r="E4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F4">
         <v>68</v>
@@ -7548,10 +7775,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B5">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -7566,7 +7793,7 @@
         <v>52</v>
       </c>
       <c r="G5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5">
         <v>48</v>
@@ -7574,10 +7801,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B6">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -7595,21 +7822,21 @@
         <v>41</v>
       </c>
       <c r="H6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>63</v>
@@ -7626,10 +7853,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B8">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -7638,7 +7865,7 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F8">
         <v>61</v>
@@ -7652,10 +7879,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B9">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C9">
         <v>14</v>
@@ -7664,7 +7891,7 @@
         <v>42</v>
       </c>
       <c r="E9">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F9">
         <v>59</v>
@@ -7678,10 +7905,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B10">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C10">
         <v>11</v>
@@ -7693,7 +7920,7 @@
         <v>54</v>
       </c>
       <c r="F10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>27</v>
@@ -7704,13 +7931,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B11">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>27</v>
@@ -7730,7 +7957,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -7749,43 +7976,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C5" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -7793,52 +8020,52 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C6" s="13">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E6" s="13">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -7861,209 +8088,209 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="B11" s="15">
-        <v>36</v>
+        <v>375</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B12" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="16">
-        <v>23</v>
+      <c r="F12" s="15">
+        <v>24</v>
       </c>
       <c r="G12" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B13" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="15">
+        <v>21</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>2</v>
-      </c>
-      <c r="E13" s="16">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2">
-        <v>4</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B14" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B15" s="2">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2">
         <v>8</v>
-      </c>
-      <c r="C15" s="16">
-        <v>21</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2">
-        <v>5</v>
-      </c>
-      <c r="G15" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B16" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
       <c r="F16" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="B17" s="15">
-        <v>45</v>
+        <v>381</v>
+      </c>
+      <c r="B17" s="16">
+        <v>46</v>
       </c>
       <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2">
+        <v>10</v>
+      </c>
+      <c r="G17" s="2">
         <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>5</v>
-      </c>
-      <c r="E17" s="2">
-        <v>11</v>
-      </c>
-      <c r="F17" s="2">
-        <v>9</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B18" s="16">
-        <v>22</v>
+        <v>382</v>
+      </c>
+      <c r="B18" s="15">
+        <v>23</v>
       </c>
       <c r="C18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="2">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
+        <v>24</v>
+      </c>
+      <c r="G18" s="2">
         <v>1</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18" s="16">
-        <v>23</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8084,17 +8311,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B4">
         <v>77</v>
@@ -8102,154 +8329,154 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B5">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B6">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B8" s="18">
-        <v>0.1276595744680851</v>
+        <v>0.13559322033898305</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B9" s="19">
-        <v>0.652</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B10" s="19">
-        <v>0.39</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B11" s="19">
-        <v>0.691</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.486</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B16">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.595</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -8269,7 +8496,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8285,47 +8512,47 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
         <v>3</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" s="18">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="F23" s="19">
-        <v>0.228</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E24" s="18">
         <v>0</v>
       </c>
       <c r="F24" s="19">
-        <v>0.288</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -8345,7 +8572,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -8365,27 +8592,27 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="18">
         <v>0</v>
       </c>
       <c r="F27" s="19">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -8405,7 +8632,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -8425,7 +8652,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -8445,27 +8672,27 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" s="20">
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <v>0.622</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -8485,27 +8712,27 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="18">
         <v>0</v>
       </c>
       <c r="F33" s="19">
-        <v>0.731</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -8525,7 +8752,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -8545,7 +8772,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -8565,23 +8792,27 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="19"/>
+        <v>2</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0.937</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -8597,7 +8828,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -8617,7 +8848,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -8633,7 +8864,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -8649,7 +8880,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -8665,7 +8896,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -8681,7 +8912,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -8701,7 +8932,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -8721,7 +8952,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -8741,7 +8972,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -8757,7 +8988,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -8773,7 +9004,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -8789,23 +9020,27 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="19"/>
+      <c r="E50" s="18">
+        <v>1</v>
+      </c>
+      <c r="F50" s="19">
+        <v>1.587</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -8821,7 +9056,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -8837,7 +9072,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -8853,7 +9088,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -8869,23 +9104,27 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
-      </c>
-      <c r="E55" s="18"/>
-      <c r="F55" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E55" s="18">
+        <v>0</v>
+      </c>
+      <c r="F55" s="19">
+        <v>1.831</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -8901,7 +9140,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -8917,7 +9156,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -8933,7 +9172,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -8949,7 +9188,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -8965,7 +9204,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -8981,7 +9220,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -8997,7 +9236,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -9013,7 +9252,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -9029,7 +9268,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -9045,7 +9284,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -9061,7 +9300,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -9077,7 +9316,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -9093,7 +9332,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -9109,7 +9348,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -9125,7 +9364,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -9145,7 +9384,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -9161,80 +9400,84 @@
     </row>
     <row r="74" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>4</v>
-      </c>
-      <c r="E76" s="18">
+        <v>8</v>
+      </c>
+      <c r="E76" s="20">
         <v>0</v>
       </c>
       <c r="F76" s="21">
-        <v>-0.179</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
-      <c r="E77" s="18"/>
-      <c r="F77" s="21"/>
+      <c r="E77" s="18">
+        <v>1</v>
+      </c>
+      <c r="F77" s="21">
+        <v>-0.071</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B78">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78">
-        <v>13</v>
-      </c>
-      <c r="E78" s="22">
-        <v>0.13333333333333333</v>
+        <v>15</v>
+      </c>
+      <c r="E78" s="20">
+        <v>0.11764705882352941</v>
       </c>
       <c r="F78" s="21">
         <v>-0.002</v>
@@ -9242,7 +9485,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -9262,32 +9505,32 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B80">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E80" s="20">
-        <v>0.07692307692307693</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F80" s="21">
-        <v>0.333</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -9306,7 +9549,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -9316,22 +9559,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -9341,17 +9584,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -9361,32 +9604,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -9396,22 +9639,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -9421,32 +9664,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -9456,27 +9699,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -9486,17 +9729,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="548">
   <si>
     <t>日期</t>
   </si>
@@ -941,6 +941,9 @@
     <t>09-25 17:00 / 09-26 11:00</t>
   </si>
   <si>
+    <t>09-26 17:00</t>
+  </si>
+  <si>
     <t>周六002</t>
   </si>
   <si>
@@ -1001,6 +1004,9 @@
     <t>09-26 18:30</t>
   </si>
   <si>
+    <t>09-26 11:00 / 09-26 17:00</t>
+  </si>
+  <si>
     <t>周六008</t>
   </si>
   <si>
@@ -1097,6 +1103,102 @@
     <t>西班牙</t>
   </si>
   <si>
+    <t>周六017</t>
+  </si>
+  <si>
+    <t>美国</t>
+  </si>
+  <si>
+    <t>秘鲁</t>
+  </si>
+  <si>
+    <t>09-27 04:30</t>
+  </si>
+  <si>
+    <t>周六018</t>
+  </si>
+  <si>
+    <t>加拿大</t>
+  </si>
+  <si>
+    <t>智利</t>
+  </si>
+  <si>
+    <t>09-27 07:00</t>
+  </si>
+  <si>
+    <t>周六019</t>
+  </si>
+  <si>
+    <t>纽约红牛</t>
+  </si>
+  <si>
+    <t>圣路易城</t>
+  </si>
+  <si>
+    <t>09-27 07:30</t>
+  </si>
+  <si>
+    <t>周六020</t>
+  </si>
+  <si>
+    <t>费城</t>
+  </si>
+  <si>
+    <t>奥兰多</t>
+  </si>
+  <si>
+    <t>周六021</t>
+  </si>
+  <si>
+    <t>达拉斯</t>
+  </si>
+  <si>
+    <t>洛杉矶FC</t>
+  </si>
+  <si>
+    <t>09-27 08:30</t>
+  </si>
+  <si>
+    <t>周六022</t>
+  </si>
+  <si>
+    <t>纳什维尔</t>
+  </si>
+  <si>
+    <t>多伦多</t>
+  </si>
+  <si>
+    <t>周六023</t>
+  </si>
+  <si>
+    <t>新英格兰</t>
+  </si>
+  <si>
+    <t>09-27 09:30</t>
+  </si>
+  <si>
+    <t>周六024</t>
+  </si>
+  <si>
+    <t>圣何塞</t>
+  </si>
+  <si>
+    <t>波特兰</t>
+  </si>
+  <si>
+    <t>09-27 10:30</t>
+  </si>
+  <si>
+    <t>周六025</t>
+  </si>
+  <si>
+    <t>洛城银河</t>
+  </si>
+  <si>
+    <t>科罗拉多</t>
+  </si>
+  <si>
     <t>2026-09-27</t>
   </si>
   <si>
@@ -1115,6 +1217,15 @@
     <t>09-27 20:30</t>
   </si>
   <si>
+    <t>哥伦布</t>
+  </si>
+  <si>
+    <t>迈国际</t>
+  </si>
+  <si>
+    <t>09-28 07:00</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1169,10 +1280,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-25（共 382 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-25，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-26（共 383 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-26，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1199,7 +1310,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-26T11:00:08+08:00）</t>
+    <t>统计（截至 2026-09-26T17:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -2020,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X88"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6383,16 +6494,16 @@
         <v>307</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W61" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W61" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X61" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
@@ -6400,19 +6511,19 @@
         <v>304</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>32</v>
@@ -6474,19 +6585,19 @@
         <v>304</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>32</v>
@@ -6548,19 +6659,19 @@
         <v>304</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>32</v>
@@ -6622,19 +6733,19 @@
         <v>304</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>32</v>
@@ -6696,19 +6807,19 @@
         <v>304</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>32</v>
@@ -6770,7 +6881,7 @@
         <v>304</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>26</v>
@@ -6779,52 +6890,52 @@
         <v>55</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H67" s="3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I67" s="3">
         <v>7.2</v>
       </c>
       <c r="J67" s="3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K67" s="4">
-        <v>5.362</v>
+        <v>5.59</v>
       </c>
       <c r="L67" s="5">
-        <v>0.338</v>
+        <v>0.41</v>
       </c>
       <c r="M67" s="3">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="N67" s="3">
-        <v>7.2</v>
+        <v>8.75</v>
       </c>
       <c r="O67" s="3">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="P67" s="4">
-        <v>5.59</v>
+        <v>7.112</v>
       </c>
       <c r="Q67" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="R67" s="9" t="s">
-        <v>94</v>
+        <v>0.388</v>
+      </c>
+      <c r="R67" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S67" s="4">
-        <v>0.072</v>
+        <v>-0.022</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U67" s="2" t="s">
         <v>30</v>
@@ -6844,22 +6955,22 @@
         <v>304</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>32</v>
+        <v>333</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H68" s="3">
         <v>4.2</v>
@@ -6898,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U68" s="2" t="s">
         <v>30</v>
@@ -6918,19 +7029,19 @@
         <v>304</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>32</v>
@@ -6951,7 +7062,7 @@
         <v>0.868</v>
       </c>
       <c r="M69" s="3">
-        <v>9.3</v>
+        <v>9</v>
       </c>
       <c r="N69" s="3">
         <v>13</v>
@@ -6963,16 +7074,16 @@
         <v>8.432</v>
       </c>
       <c r="Q69" s="5">
-        <v>0.868</v>
-      </c>
-      <c r="R69" s="6" t="s">
-        <v>80</v>
+        <v>0.568</v>
+      </c>
+      <c r="R69" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S69" s="4">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U69" s="2" t="s">
         <v>30</v>
@@ -6992,37 +7103,37 @@
         <v>304</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H70" s="3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I70" s="3">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="J70" s="3">
         <v>8</v>
       </c>
       <c r="K70" s="4">
-        <v>3.733</v>
+        <v>3.661</v>
       </c>
       <c r="L70" s="5">
-        <v>0.167</v>
+        <v>0.139</v>
       </c>
       <c r="M70" s="3">
         <v>3.8</v>
@@ -7039,14 +7150,14 @@
       <c r="Q70" s="5">
         <v>0.139</v>
       </c>
-      <c r="R70" s="7" t="s">
-        <v>73</v>
+      <c r="R70" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="S70" s="4">
-        <v>-0.028</v>
+        <v>0</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U70" s="2" t="s">
         <v>30</v>
@@ -7066,19 +7177,19 @@
         <v>304</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>32</v>
@@ -7099,28 +7210,28 @@
         <v>0.511</v>
       </c>
       <c r="M71" s="3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="N71" s="3">
         <v>6.7</v>
       </c>
       <c r="O71" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P71" s="4">
-        <v>5.189</v>
+        <v>5.136</v>
       </c>
       <c r="Q71" s="5">
-        <v>0.511</v>
-      </c>
-      <c r="R71" s="6" t="s">
-        <v>80</v>
+        <v>0.464</v>
+      </c>
+      <c r="R71" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S71" s="4">
-        <v>0</v>
+        <v>-0.047</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U71" s="2" t="s">
         <v>30</v>
@@ -7140,19 +7251,19 @@
         <v>304</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>32</v>
@@ -7173,28 +7284,28 @@
         <v>0.154</v>
       </c>
       <c r="M72" s="3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N72" s="3">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="O72" s="3">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="P72" s="4">
-        <v>3.646</v>
+        <v>3.535</v>
       </c>
       <c r="Q72" s="5">
-        <v>0.154</v>
-      </c>
-      <c r="R72" s="6" t="s">
-        <v>80</v>
+        <v>0.065</v>
+      </c>
+      <c r="R72" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S72" s="4">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U72" s="2" t="s">
         <v>30</v>
@@ -7214,19 +7325,19 @@
         <v>304</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>32</v>
@@ -7247,7 +7358,7 @@
         <v>0.461</v>
       </c>
       <c r="M73" s="3">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="N73" s="3">
         <v>11</v>
@@ -7259,16 +7370,16 @@
         <v>5.739</v>
       </c>
       <c r="Q73" s="5">
-        <v>0.461</v>
-      </c>
-      <c r="R73" s="6" t="s">
-        <v>80</v>
+        <v>0.561</v>
+      </c>
+      <c r="R73" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S73" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U73" s="2" t="s">
         <v>30</v>
@@ -7288,19 +7399,19 @@
         <v>304</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>32</v>
@@ -7342,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U74" s="2" t="s">
         <v>30</v>
@@ -7362,19 +7473,19 @@
         <v>304</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>32</v>
@@ -7395,28 +7506,28 @@
         <v>0.53</v>
       </c>
       <c r="M75" s="3">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="N75" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O75" s="3">
         <v>7</v>
       </c>
       <c r="P75" s="4">
-        <v>4.87</v>
+        <v>5.04</v>
       </c>
       <c r="Q75" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="R75" s="6" t="s">
-        <v>80</v>
+        <v>0.31</v>
+      </c>
+      <c r="R75" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S75" s="4">
-        <v>0</v>
+        <v>-0.22</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U75" s="2" t="s">
         <v>30</v>
@@ -7436,61 +7547,61 @@
         <v>304</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>32</v>
+        <v>355</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H76" s="3">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I76" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J76" s="3">
         <v>9</v>
       </c>
       <c r="K76" s="4">
-        <v>4.737</v>
+        <v>4.95</v>
       </c>
       <c r="L76" s="5">
-        <v>0.463</v>
+        <v>0.65</v>
       </c>
       <c r="M76" s="3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="N76" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O76" s="3">
         <v>9</v>
       </c>
       <c r="P76" s="4">
-        <v>4.95</v>
+        <v>5.143</v>
       </c>
       <c r="Q76" s="5">
-        <v>0.65</v>
+        <v>0.857</v>
       </c>
       <c r="R76" s="9" t="s">
         <v>94</v>
       </c>
       <c r="S76" s="4">
-        <v>0.187</v>
+        <v>0.207</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="U76" s="2" t="s">
         <v>30</v>
@@ -7507,64 +7618,52 @@
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>25</v>
+        <v>362</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>49</v>
+        <v>364</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H77" s="3">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="I77" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J77" s="3">
-        <v>7.7</v>
+        <v>15</v>
       </c>
       <c r="K77" s="4">
-        <v>3.525</v>
+        <v>4.773</v>
       </c>
       <c r="L77" s="5">
-        <v>0.175</v>
-      </c>
-      <c r="M77" s="3">
-        <v>3.7</v>
-      </c>
-      <c r="N77" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="O77" s="3">
-        <v>7.7</v>
-      </c>
-      <c r="P77" s="4">
-        <v>3.525</v>
-      </c>
-      <c r="Q77" s="5">
-        <v>0.175</v>
-      </c>
-      <c r="R77" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="S77" s="4">
-        <v>0</v>
-      </c>
+        <v>0.227</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S77" s="4"/>
       <c r="T77" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="U77" s="2" t="s">
         <v>30</v>
@@ -7581,75 +7680,707 @@
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I78" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J78" s="3">
+        <v>12</v>
+      </c>
+      <c r="K78" s="4">
+        <v>4.615</v>
+      </c>
+      <c r="L78" s="5">
+        <v>0.185</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S78" s="4"/>
+      <c r="T78" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H79" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="I79" s="3">
+        <v>16.5</v>
+      </c>
+      <c r="J79" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="K79" s="4">
+        <v>7.112</v>
+      </c>
+      <c r="L79" s="5">
+        <v>0.638</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S79" s="4"/>
+      <c r="T79" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X79" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H80" s="3">
+        <v>11</v>
+      </c>
+      <c r="I80" s="3">
+        <v>16</v>
+      </c>
+      <c r="J80" s="3">
+        <v>30</v>
+      </c>
+      <c r="K80" s="4">
+        <v>10.435</v>
+      </c>
+      <c r="L80" s="5">
+        <v>0.565</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S80" s="4"/>
+      <c r="T80" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="I81" s="3">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="K81" s="4">
+        <v>5.556</v>
+      </c>
+      <c r="L81" s="5">
+        <v>0.644</v>
+      </c>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S81" s="4"/>
+      <c r="T81" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X81" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H82" s="3">
+        <v>7.85</v>
+      </c>
+      <c r="I82" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="J82" s="3">
+        <v>26</v>
+      </c>
+      <c r="K82" s="4">
+        <v>6.958</v>
+      </c>
+      <c r="L82" s="5">
+        <v>0.892</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S82" s="4"/>
+      <c r="T82" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H83" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="I83" s="3">
+        <v>11.5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="K83" s="4">
+        <v>5.99</v>
+      </c>
+      <c r="L83" s="5">
+        <v>0.81</v>
+      </c>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S83" s="4"/>
+      <c r="T83" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H84" s="3">
+        <v>8.7</v>
+      </c>
+      <c r="I84" s="3">
+        <v>13</v>
+      </c>
+      <c r="J84" s="3">
+        <v>19</v>
+      </c>
+      <c r="K84" s="4">
+        <v>7.719</v>
+      </c>
+      <c r="L84" s="5">
+        <v>0.981</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S84" s="4"/>
+      <c r="T84" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="I85" s="3">
+        <v>11</v>
+      </c>
+      <c r="J85" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="K85" s="4">
+        <v>6.061</v>
+      </c>
+      <c r="L85" s="5">
+        <v>0.639</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S85" s="4"/>
+      <c r="T85" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X85" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H86" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="I86" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J86" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="K86" s="4">
+        <v>3.525</v>
+      </c>
+      <c r="L86" s="5">
+        <v>0.175</v>
+      </c>
+      <c r="M86" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="N86" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O86" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="P86" s="4">
+        <v>3.525</v>
+      </c>
+      <c r="Q86" s="5">
+        <v>0.175</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S86" s="4">
+        <v>0</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X86" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H78" s="3">
+      <c r="D87" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H87" s="3">
         <v>13</v>
       </c>
-      <c r="I78" s="3">
+      <c r="I87" s="3">
         <v>22</v>
       </c>
-      <c r="J78" s="3">
+      <c r="J87" s="3">
         <v>23</v>
       </c>
-      <c r="K78" s="4">
+      <c r="K87" s="4">
         <v>11.244</v>
       </c>
-      <c r="L78" s="5">
+      <c r="L87" s="5">
         <v>1.756</v>
       </c>
-      <c r="M78" s="3">
+      <c r="M87" s="3">
         <v>13</v>
       </c>
-      <c r="N78" s="3">
+      <c r="N87" s="3">
         <v>22</v>
       </c>
-      <c r="O78" s="3">
+      <c r="O87" s="3">
         <v>23</v>
       </c>
-      <c r="P78" s="4">
+      <c r="P87" s="4">
         <v>11.244</v>
       </c>
-      <c r="Q78" s="5">
+      <c r="Q87" s="5">
         <v>1.756</v>
       </c>
-      <c r="R78" s="6" t="s">
+      <c r="R87" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S78" s="4">
-        <v>0</v>
-      </c>
-      <c r="T78" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="U78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X78" s="2" t="s">
+      <c r="S87" s="4">
+        <v>0</v>
+      </c>
+      <c r="T87" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="U87" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H88" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="I88" s="3">
+        <v>22</v>
+      </c>
+      <c r="J88" s="3">
+        <v>17</v>
+      </c>
+      <c r="K88" s="4">
+        <v>9.59</v>
+      </c>
+      <c r="L88" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S88" s="4"/>
+      <c r="T88" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X88" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -7671,36 +8402,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="B2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C2">
         <v>23</v>
@@ -7712,7 +8443,7 @@
         <v>68</v>
       </c>
       <c r="F2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>52</v>
@@ -7723,7 +8454,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="B3">
         <v>324</v>
@@ -7749,7 +8480,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="B4">
         <v>316</v>
@@ -7775,7 +8506,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="B5">
         <v>308</v>
@@ -7801,7 +8532,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="B6">
         <v>300</v>
@@ -7827,7 +8558,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="B7">
         <v>282</v>
@@ -7853,7 +8584,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="B8">
         <v>273</v>
@@ -7879,7 +8610,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="B9">
         <v>252</v>
@@ -7905,7 +8636,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="B10">
         <v>233</v>
@@ -7931,7 +8662,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="B11">
         <v>211</v>
@@ -7957,7 +8688,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -7976,43 +8707,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>385</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>386</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>387</v>
+        <v>424</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>388</v>
+        <v>425</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="C5" s="13">
         <v>46</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="E5" s="13">
         <v>14</v>
@@ -8020,16 +8751,16 @@
     </row>
     <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="C6" s="13">
         <v>30</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="E6" s="13">
         <v>15</v>
@@ -8037,58 +8768,58 @@
     </row>
     <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>393</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>366</v>
+        <v>403</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>369</v>
+        <v>406</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>370</v>
+        <v>407</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>371</v>
+        <v>408</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>372</v>
+        <v>409</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>374</v>
+        <v>411</v>
       </c>
       <c r="B10" s="2">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="2">
-        <v>16</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
       <c r="G10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>375</v>
+        <v>412</v>
       </c>
       <c r="B11" s="2">
         <v>0</v>
@@ -8111,7 +8842,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>376</v>
+        <v>413</v>
       </c>
       <c r="B12" s="2">
         <v>17</v>
@@ -8134,7 +8865,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="B13" s="16">
         <v>30</v>
@@ -8157,7 +8888,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="B14" s="2">
         <v>9</v>
@@ -8180,7 +8911,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="B15" s="2">
         <v>9</v>
@@ -8203,7 +8934,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="B16" s="2">
         <v>15</v>
@@ -8226,7 +8957,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>381</v>
+        <v>418</v>
       </c>
       <c r="B17" s="16">
         <v>46</v>
@@ -8249,7 +8980,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>382</v>
+        <v>419</v>
       </c>
       <c r="B18" s="15">
         <v>23</v>
@@ -8272,7 +9003,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>383</v>
+        <v>420</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
@@ -8311,25 +9042,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>395</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="B4">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>434</v>
       </c>
       <c r="B5">
         <v>64</v>
@@ -8337,15 +9068,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="B6">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>436</v>
       </c>
       <c r="B7">
         <v>8</v>
@@ -8353,23 +9084,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>400</v>
+        <v>437</v>
       </c>
       <c r="B8" s="18">
-        <v>0.13559322033898305</v>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="B9" s="19">
-        <v>0.671</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>402</v>
+        <v>439</v>
       </c>
       <c r="B10" s="19">
         <v>0.517</v>
@@ -8377,43 +9108,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="B11" s="19">
-        <v>0.695</v>
+        <v>0.687</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>405</v>
+        <v>442</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>407</v>
+        <v>444</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -8423,60 +9154,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.534</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="B16">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.59</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>410</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -8496,7 +9227,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>418</v>
+        <v>455</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8512,7 +9243,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -8532,18 +9263,18 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24" s="18">
+        <v>5</v>
+      </c>
+      <c r="E24" s="20">
         <v>0</v>
       </c>
       <c r="F24" s="19">
@@ -8552,7 +9283,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -8572,7 +9303,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -8592,7 +9323,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -8612,7 +9343,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -8632,7 +9363,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -8652,7 +9383,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -8672,7 +9403,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
       <c r="B31">
         <v>7</v>
@@ -8692,7 +9423,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -8712,7 +9443,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>429</v>
+        <v>466</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -8732,7 +9463,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>430</v>
+        <v>467</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -8752,7 +9483,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>431</v>
+        <v>468</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -8772,7 +9503,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>432</v>
+        <v>469</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -8792,7 +9523,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -8812,7 +9543,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>434</v>
+        <v>471</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -8828,7 +9559,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="B39">
         <v>5</v>
@@ -8848,7 +9579,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>436</v>
+        <v>473</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -8864,7 +9595,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -8880,7 +9611,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -8896,7 +9627,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -8912,7 +9643,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>440</v>
+        <v>477</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -8932,7 +9663,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -8952,7 +9683,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>442</v>
+        <v>479</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -8972,7 +9703,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -8988,7 +9719,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -9004,7 +9735,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -9020,7 +9751,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -9040,7 +9771,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -9056,7 +9787,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -9072,7 +9803,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -9088,7 +9819,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -9104,7 +9835,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -9124,7 +9855,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -9140,7 +9871,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -9156,7 +9887,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -9172,7 +9903,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -9188,7 +9919,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -9204,7 +9935,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -9220,7 +9951,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -9236,7 +9967,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -9252,7 +9983,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -9268,7 +9999,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -9284,7 +10015,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -9300,7 +10031,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -9316,7 +10047,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -9332,7 +10063,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -9348,7 +10079,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -9364,7 +10095,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -9384,7 +10115,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -9400,32 +10131,32 @@
     </row>
     <row r="74" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>408</v>
+        <v>445</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>416</v>
+        <v>453</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="B76">
         <v>8</v>
@@ -9445,7 +10176,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -9465,19 +10196,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="B78">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E78" s="20">
-        <v>0.11764705882352941</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F78" s="21">
         <v>-0.002</v>
@@ -9485,7 +10216,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -9505,7 +10236,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="B80">
         <v>18</v>
@@ -9525,12 +10256,12 @@
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -9549,7 +10280,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -9559,22 +10290,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -9584,17 +10315,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -9604,32 +10335,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -9639,22 +10370,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -9664,32 +10395,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -9699,27 +10430,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -9729,17 +10460,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="554">
   <si>
     <t>日期</t>
   </si>
@@ -941,180 +941,192 @@
     <t>09-25 17:00 / 09-26 11:00</t>
   </si>
   <si>
+    <t>09-27 11:00</t>
+  </si>
+  <si>
+    <t>周六002</t>
+  </si>
+  <si>
+    <t>日乙</t>
+  </si>
+  <si>
+    <t>磐城FC</t>
+  </si>
+  <si>
+    <t>仙台七夕</t>
+  </si>
+  <si>
+    <t>09-26 16:00</t>
+  </si>
+  <si>
+    <t>周六003</t>
+  </si>
+  <si>
+    <t>富山胜利</t>
+  </si>
+  <si>
+    <t>横滨FC</t>
+  </si>
+  <si>
+    <t>3:3</t>
+  </si>
+  <si>
+    <t>1:3</t>
+  </si>
+  <si>
+    <t>周六004</t>
+  </si>
+  <si>
+    <t>秋田闪电</t>
+  </si>
+  <si>
+    <t>新潟天鹅</t>
+  </si>
+  <si>
+    <t>2:2</t>
+  </si>
+  <si>
+    <t>周六005</t>
+  </si>
+  <si>
+    <t>大宫松鼠</t>
+  </si>
+  <si>
+    <t>甲府风林</t>
+  </si>
+  <si>
+    <t>周六006</t>
+  </si>
+  <si>
+    <t>大分三神</t>
+  </si>
+  <si>
+    <t>藤枝MYFC</t>
+  </si>
+  <si>
+    <t>周六007</t>
+  </si>
+  <si>
+    <t>朝鲜亚</t>
+  </si>
+  <si>
+    <t>09-26 18:30</t>
+  </si>
+  <si>
+    <t>09-26 11:00 / 09-26 17:00</t>
+  </si>
+  <si>
+    <t>周六008</t>
+  </si>
+  <si>
+    <t>斯洛文尼</t>
+  </si>
+  <si>
+    <t>苏格兰</t>
+  </si>
+  <si>
+    <t>09-26 21:00</t>
+  </si>
+  <si>
+    <t>周六009</t>
+  </si>
+  <si>
+    <t>赫拉克勒</t>
+  </si>
+  <si>
+    <t>维迪斯</t>
+  </si>
+  <si>
+    <t>09-26 22:30</t>
+  </si>
+  <si>
+    <t>周六010</t>
+  </si>
+  <si>
+    <t>法罗群岛</t>
+  </si>
+  <si>
+    <t>哈萨克</t>
+  </si>
+  <si>
+    <t>09-27 00:00</t>
+  </si>
+  <si>
+    <t>周六011</t>
+  </si>
+  <si>
+    <t>冰岛</t>
+  </si>
+  <si>
+    <t>爱沙尼亚</t>
+  </si>
+  <si>
+    <t>周六012</t>
+  </si>
+  <si>
+    <t>保加利亚</t>
+  </si>
+  <si>
+    <t>卢森堡</t>
+  </si>
+  <si>
+    <t>周六013</t>
+  </si>
+  <si>
+    <t>罗达JC</t>
+  </si>
+  <si>
+    <t>瓦尔韦克</t>
+  </si>
+  <si>
+    <t>09-27 02:00</t>
+  </si>
+  <si>
+    <t>周六014</t>
+  </si>
+  <si>
+    <t>捷克</t>
+  </si>
+  <si>
+    <t>克罗地亚</t>
+  </si>
+  <si>
+    <t>09-27 02:45</t>
+  </si>
+  <si>
+    <t>周六015</t>
+  </si>
+  <si>
+    <t>北马其顿</t>
+  </si>
+  <si>
+    <t>瑞士</t>
+  </si>
+  <si>
+    <t>周六016</t>
+  </si>
+  <si>
+    <t>英格兰</t>
+  </si>
+  <si>
+    <t>西班牙</t>
+  </si>
+  <si>
+    <t>周六017</t>
+  </si>
+  <si>
+    <t>美国</t>
+  </si>
+  <si>
+    <t>秘鲁</t>
+  </si>
+  <si>
+    <t>09-27 04:30</t>
+  </si>
+  <si>
     <t>09-26 17:00</t>
   </si>
   <si>
-    <t>周六002</t>
-  </si>
-  <si>
-    <t>日乙</t>
-  </si>
-  <si>
-    <t>磐城FC</t>
-  </si>
-  <si>
-    <t>仙台七夕</t>
-  </si>
-  <si>
-    <t>09-26 16:00</t>
-  </si>
-  <si>
-    <t>周六003</t>
-  </si>
-  <si>
-    <t>富山胜利</t>
-  </si>
-  <si>
-    <t>横滨FC</t>
-  </si>
-  <si>
-    <t>周六004</t>
-  </si>
-  <si>
-    <t>秋田闪电</t>
-  </si>
-  <si>
-    <t>新潟天鹅</t>
-  </si>
-  <si>
-    <t>周六005</t>
-  </si>
-  <si>
-    <t>大宫松鼠</t>
-  </si>
-  <si>
-    <t>甲府风林</t>
-  </si>
-  <si>
-    <t>周六006</t>
-  </si>
-  <si>
-    <t>大分三神</t>
-  </si>
-  <si>
-    <t>藤枝MYFC</t>
-  </si>
-  <si>
-    <t>周六007</t>
-  </si>
-  <si>
-    <t>朝鲜亚</t>
-  </si>
-  <si>
-    <t>09-26 18:30</t>
-  </si>
-  <si>
-    <t>09-26 11:00 / 09-26 17:00</t>
-  </si>
-  <si>
-    <t>周六008</t>
-  </si>
-  <si>
-    <t>斯洛文尼</t>
-  </si>
-  <si>
-    <t>苏格兰</t>
-  </si>
-  <si>
-    <t>09-26 21:00</t>
-  </si>
-  <si>
-    <t>周六009</t>
-  </si>
-  <si>
-    <t>赫拉克勒</t>
-  </si>
-  <si>
-    <t>维迪斯</t>
-  </si>
-  <si>
-    <t>09-26 22:30</t>
-  </si>
-  <si>
-    <t>周六010</t>
-  </si>
-  <si>
-    <t>法罗群岛</t>
-  </si>
-  <si>
-    <t>哈萨克</t>
-  </si>
-  <si>
-    <t>09-27 00:00</t>
-  </si>
-  <si>
-    <t>周六011</t>
-  </si>
-  <si>
-    <t>冰岛</t>
-  </si>
-  <si>
-    <t>爱沙尼亚</t>
-  </si>
-  <si>
-    <t>周六012</t>
-  </si>
-  <si>
-    <t>保加利亚</t>
-  </si>
-  <si>
-    <t>卢森堡</t>
-  </si>
-  <si>
-    <t>周六013</t>
-  </si>
-  <si>
-    <t>罗达JC</t>
-  </si>
-  <si>
-    <t>瓦尔韦克</t>
-  </si>
-  <si>
-    <t>09-27 02:00</t>
-  </si>
-  <si>
-    <t>周六014</t>
-  </si>
-  <si>
-    <t>捷克</t>
-  </si>
-  <si>
-    <t>克罗地亚</t>
-  </si>
-  <si>
-    <t>09-27 02:45</t>
-  </si>
-  <si>
-    <t>周六015</t>
-  </si>
-  <si>
-    <t>北马其顿</t>
-  </si>
-  <si>
-    <t>瑞士</t>
-  </si>
-  <si>
-    <t>周六016</t>
-  </si>
-  <si>
-    <t>英格兰</t>
-  </si>
-  <si>
-    <t>西班牙</t>
-  </si>
-  <si>
-    <t>周六017</t>
-  </si>
-  <si>
-    <t>美国</t>
-  </si>
-  <si>
-    <t>秘鲁</t>
-  </si>
-  <si>
-    <t>09-27 04:30</t>
-  </si>
-  <si>
     <t>周六018</t>
   </si>
   <si>
@@ -1148,6 +1160,9 @@
     <t>奥兰多</t>
   </si>
   <si>
+    <t>4:2</t>
+  </si>
+  <si>
     <t>周六021</t>
   </si>
   <si>
@@ -1208,6 +1223,9 @@
     <t>09-27 18:00</t>
   </si>
   <si>
+    <t>09-26 17:00 / 09-27 11:00</t>
+  </si>
+  <si>
     <t>格拉夫</t>
   </si>
   <si>
@@ -1301,16 +1319,13 @@
     <t>历史次数</t>
   </si>
   <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
     <t>2026-08-24</t>
   </si>
   <si>
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-26T17:00:04+08:00）</t>
+    <t>统计（截至 2026-09-27T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1377,6 +1392,9 @@
   </si>
   <si>
     <t>非1球场次</t>
+  </si>
+  <si>
+    <t>0.05 ~ 0.10</t>
   </si>
   <si>
     <t>0.10 ~ 0.15</t>
@@ -1745,7 +1763,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1790,6 +1808,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -6568,16 +6587,16 @@
         <v>307</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W62" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X62" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
@@ -6642,16 +6661,16 @@
         <v>307</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>30</v>
+        <v>317</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>30</v>
+        <v>318</v>
+      </c>
+      <c r="W63" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X63" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
@@ -6659,16 +6678,16 @@
         <v>304</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>310</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>313</v>
@@ -6716,16 +6735,16 @@
         <v>307</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>30</v>
+        <v>322</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W64" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X64" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
@@ -6733,16 +6752,16 @@
         <v>304</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>310</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>313</v>
@@ -6790,16 +6809,16 @@
         <v>307</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W65" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
@@ -6807,16 +6826,16 @@
         <v>304</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>310</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>313</v>
@@ -6864,16 +6883,16 @@
         <v>307</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W66" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X66" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
@@ -6881,7 +6900,7 @@
         <v>304</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>26</v>
@@ -6890,10 +6909,10 @@
         <v>55</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>32</v>
@@ -6935,19 +6954,19 @@
         <v>-0.022</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W67" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W67" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X67" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
@@ -6955,19 +6974,19 @@
         <v>304</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G68" s="8" t="s">
         <v>46</v>
@@ -7009,19 +7028,19 @@
         <v>0</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W68" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X68" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
@@ -7029,19 +7048,19 @@
         <v>304</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>32</v>
@@ -7083,19 +7102,19 @@
         <v>-0.3</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V69" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W69" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W69" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X69" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
@@ -7103,19 +7122,19 @@
         <v>304</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>32</v>
@@ -7157,19 +7176,19 @@
         <v>0</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V70" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W70" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W70" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X70" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
@@ -7177,19 +7196,19 @@
         <v>304</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>32</v>
@@ -7231,19 +7250,19 @@
         <v>-0.047</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V71" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W71" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W71" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X71" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
@@ -7251,19 +7270,19 @@
         <v>304</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>32</v>
@@ -7305,19 +7324,19 @@
         <v>-0.089</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U72" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V72" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W72" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W72" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X72" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.25">
@@ -7325,19 +7344,19 @@
         <v>304</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>32</v>
@@ -7379,19 +7398,19 @@
         <v>0.1</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U73" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V73" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W73" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W73" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X73" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.25">
@@ -7399,19 +7418,19 @@
         <v>304</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>32</v>
@@ -7453,19 +7472,19 @@
         <v>0</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W74" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W74" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X74" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
@@ -7473,19 +7492,19 @@
         <v>304</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>32</v>
@@ -7527,19 +7546,19 @@
         <v>-0.22</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="V75" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W75" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
+      </c>
+      <c r="W75" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X75" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.25">
@@ -7547,19 +7566,19 @@
         <v>304</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>46</v>
@@ -7601,19 +7620,19 @@
         <v>0.207</v>
       </c>
       <c r="T76" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="U76" s="2" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="V76" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W76" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
+      </c>
+      <c r="W76" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X76" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
@@ -7621,19 +7640,19 @@
         <v>304</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>32</v>
@@ -7663,19 +7682,19 @@
       </c>
       <c r="S77" s="4"/>
       <c r="T77" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="W77" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="X77" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="U77" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W77" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X77" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
@@ -7683,19 +7702,19 @@
         <v>304</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>222</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>32</v>
@@ -7725,19 +7744,19 @@
       </c>
       <c r="S78" s="4"/>
       <c r="T78" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W78" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="X78" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="U78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W78" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X78" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
@@ -7745,19 +7764,19 @@
         <v>304</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>32</v>
@@ -7787,7 +7806,7 @@
       </c>
       <c r="S79" s="4"/>
       <c r="T79" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U79" s="2" t="s">
         <v>30</v>
@@ -7807,19 +7826,19 @@
         <v>304</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>32</v>
@@ -7849,19 +7868,19 @@
       </c>
       <c r="S80" s="4"/>
       <c r="T80" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="W80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="X80" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
@@ -7869,19 +7888,19 @@
         <v>304</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>32</v>
@@ -7911,7 +7930,7 @@
       </c>
       <c r="S81" s="4"/>
       <c r="T81" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U81" s="2" t="s">
         <v>30</v>
@@ -7931,19 +7950,19 @@
         <v>304</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>32</v>
@@ -7973,7 +7992,7 @@
       </c>
       <c r="S82" s="4"/>
       <c r="T82" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U82" s="2" t="s">
         <v>30</v>
@@ -7993,7 +8012,7 @@
         <v>304</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>215</v>
@@ -8002,10 +8021,10 @@
         <v>217</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>32</v>
@@ -8035,7 +8054,7 @@
       </c>
       <c r="S83" s="4"/>
       <c r="T83" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U83" s="2" t="s">
         <v>30</v>
@@ -8055,19 +8074,19 @@
         <v>304</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>32</v>
@@ -8097,7 +8116,7 @@
       </c>
       <c r="S84" s="4"/>
       <c r="T84" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U84" s="2" t="s">
         <v>30</v>
@@ -8117,19 +8136,19 @@
         <v>304</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>215</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>32</v>
@@ -8159,7 +8178,7 @@
       </c>
       <c r="S85" s="4"/>
       <c r="T85" s="2" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="U85" s="2" t="s">
         <v>30</v>
@@ -8176,7 +8195,7 @@
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>25</v>
@@ -8185,13 +8204,13 @@
         <v>48</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>49</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>32</v>
@@ -8233,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="T86" s="2" t="s">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="U86" s="2" t="s">
         <v>30</v>
@@ -8250,7 +8269,7 @@
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>42</v>
@@ -8259,13 +8278,13 @@
         <v>300</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>32</v>
@@ -8307,7 +8326,7 @@
         <v>0</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>30</v>
@@ -8324,7 +8343,7 @@
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>75</v>
@@ -8333,13 +8352,13 @@
         <v>215</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>32</v>
@@ -8359,17 +8378,29 @@
       <c r="L88" s="5">
         <v>0.91</v>
       </c>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
-      <c r="O88" s="3"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" s="4"/>
+      <c r="M88" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="N88" s="3">
+        <v>22</v>
+      </c>
+      <c r="O88" s="3">
+        <v>17</v>
+      </c>
+      <c r="P88" s="4">
+        <v>9.59</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S88" s="4">
+        <v>0</v>
+      </c>
       <c r="T88" s="2" t="s">
-        <v>308</v>
+        <v>402</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>30</v>
@@ -8402,33 +8433,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B2">
         <v>326</v>
@@ -8454,10 +8485,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B3">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -8466,7 +8497,7 @@
         <v>58</v>
       </c>
       <c r="E3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3">
         <v>72</v>
@@ -8480,10 +8511,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B4">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -8501,15 +8532,15 @@
         <v>46</v>
       </c>
       <c r="H4">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="B5">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -8524,7 +8555,7 @@
         <v>52</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5">
         <v>48</v>
@@ -8532,10 +8563,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B6">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -8553,15 +8584,15 @@
         <v>41</v>
       </c>
       <c r="H6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -8570,7 +8601,7 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7">
         <v>76</v>
@@ -8584,16 +8615,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>66</v>
@@ -8610,13 +8641,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B9">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -8636,10 +8667,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B10">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C10">
         <v>11</v>
@@ -8648,7 +8679,7 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F10">
         <v>59</v>
@@ -8662,10 +8693,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B11">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -8674,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11">
         <v>53</v>
@@ -8688,7 +8719,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -8699,7 +8730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8707,214 +8738,220 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C5" s="13">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E5" s="13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="C6" s="13">
-        <v>30</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="E6" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>405</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>406</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>409</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>410</v>
+      <c r="F8" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>14</v>
+      </c>
+      <c r="G10" s="2">
         <v>4</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
+        <v>419</v>
+      </c>
+      <c r="B11" s="15">
+        <v>18</v>
       </c>
       <c r="C11" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D11" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="F11" s="15">
+        <v>25</v>
       </c>
       <c r="G11" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B12" s="2">
-        <v>17</v>
+        <v>420</v>
+      </c>
+      <c r="B12" s="16">
+        <v>31</v>
       </c>
       <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
         <v>4</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
-      <c r="F12" s="15">
-        <v>24</v>
+      <c r="E12" s="15">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="B13" s="16">
-        <v>30</v>
+        <v>421</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
-      </c>
-      <c r="E13" s="15">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>11</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B14" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
       </c>
       <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="2">
-        <v>10</v>
-      </c>
       <c r="F14" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B15" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
@@ -8923,105 +8960,82 @@
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="2">
+        <v>12</v>
+      </c>
+      <c r="G15" s="2">
         <v>6</v>
-      </c>
-      <c r="G15" s="2">
-        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B16" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F16" s="2">
         <v>11</v>
       </c>
       <c r="G16" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B17" s="16">
-        <v>46</v>
+        <v>425</v>
+      </c>
+      <c r="B17" s="15">
+        <v>24</v>
       </c>
       <c r="C17" s="2">
+        <v>6</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15">
+        <v>25</v>
+      </c>
+      <c r="G17" s="2">
         <v>2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B18" s="15">
-        <v>23</v>
-      </c>
-      <c r="C18" s="2">
+        <v>426</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="15">
+        <v>18</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2">
         <v>5</v>
       </c>
-      <c r="D18" s="2">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15">
-        <v>24</v>
-      </c>
       <c r="G18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B19" s="2">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>17</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2">
-        <v>4</v>
-      </c>
-      <c r="G19" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9032,7 +9046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -9042,17 +9056,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B4">
         <v>87</v>
@@ -9060,94 +9074,94 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B5">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B6">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B8" s="18">
-        <v>0.13333333333333333</v>
+        <v>0.1282051282051282</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B9" s="19">
-        <v>0.665</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B10" s="19">
-        <v>0.517</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B11" s="19">
-        <v>0.687</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B15">
         <v>8</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -9159,16 +9173,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B16">
         <v>67</v>
       </c>
       <c r="C16">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
@@ -9177,37 +9191,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>452</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -9222,288 +9236,292 @@
         <v>0</v>
       </c>
       <c r="F21" s="19">
-        <v>0.124</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="E22" s="18">
+        <v>0</v>
+      </c>
+      <c r="F22" s="19">
+        <v>0.131</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="18">
         <v>1</v>
       </c>
-      <c r="E23" s="18">
-        <v>0.75</v>
-      </c>
       <c r="F23" s="19">
-        <v>0.224</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E24" s="20">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F24" s="19">
-        <v>0.273</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" s="18">
-        <v>0.6666666666666666</v>
+        <v>6</v>
+      </c>
+      <c r="E25" s="21">
+        <v>0</v>
       </c>
       <c r="F25" s="19">
-        <v>0.329</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26" s="20">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0.5</v>
       </c>
       <c r="F26" s="19">
-        <v>0.37</v>
+        <v>0.324</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27" s="18">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="E27" s="21">
+        <v>0.1</v>
       </c>
       <c r="F27" s="19">
-        <v>0.43</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28" s="18">
+        <v>5</v>
+      </c>
+      <c r="E28" s="21">
         <v>0</v>
       </c>
       <c r="F28" s="19">
-        <v>0.48</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="18">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F29" s="19">
-        <v>0.531</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>2</v>
       </c>
       <c r="E30" s="18">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F30" s="19">
-        <v>0.561</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>7</v>
-      </c>
-      <c r="E31" s="20">
+        <v>5</v>
+      </c>
+      <c r="E31" s="21">
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <v>0.621</v>
+        <v>0.563</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
-      </c>
-      <c r="E32" s="18">
-        <v>0.3333333333333333</v>
+        <v>7</v>
+      </c>
+      <c r="E32" s="21">
+        <v>0</v>
       </c>
       <c r="F32" s="19">
-        <v>0.683</v>
+        <v>0.621</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B33">
         <v>3</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="18">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F33" s="19">
-        <v>0.724</v>
+        <v>0.683</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="18">
         <v>0</v>
       </c>
       <c r="F34" s="19">
-        <v>0.758</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="18">
         <v>0</v>
       </c>
       <c r="F35" s="19">
-        <v>0.844</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -9518,12 +9536,12 @@
         <v>0</v>
       </c>
       <c r="F36" s="19">
-        <v>0.891</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -9538,64 +9556,68 @@
         <v>0</v>
       </c>
       <c r="F37" s="19">
-        <v>0.937</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="19"/>
+        <v>2</v>
+      </c>
+      <c r="E38" s="18">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19">
+        <v>0.937</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>5</v>
-      </c>
-      <c r="E39" s="20">
-        <v>0</v>
-      </c>
-      <c r="F39" s="19">
-        <v>1.035</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" s="18"/>
+      <c r="F39" s="19"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="19"/>
+        <v>5</v>
+      </c>
+      <c r="E40" s="21">
+        <v>0</v>
+      </c>
+      <c r="F40" s="19">
+        <v>1.035</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -9611,7 +9633,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -9627,7 +9649,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -9643,27 +9665,23 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" s="18">
-        <v>0</v>
-      </c>
-      <c r="F44" s="19">
-        <v>1.259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" s="18"/>
+      <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -9678,12 +9696,12 @@
         <v>0</v>
       </c>
       <c r="F45" s="19">
-        <v>1.318</v>
+        <v>1.259</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -9698,28 +9716,32 @@
         <v>0</v>
       </c>
       <c r="F46" s="19">
-        <v>1.395</v>
+        <v>1.318</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47" s="18"/>
-      <c r="F47" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E47" s="18">
+        <v>0</v>
+      </c>
+      <c r="F47" s="19">
+        <v>1.395</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -9735,7 +9757,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -9751,43 +9773,43 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="18">
-        <v>1</v>
-      </c>
-      <c r="F50" s="19">
-        <v>1.587</v>
-      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
-      <c r="E51" s="18"/>
-      <c r="F51" s="19"/>
+      <c r="E51" s="18">
+        <v>1</v>
+      </c>
+      <c r="F51" s="19">
+        <v>1.587</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -9803,7 +9825,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -9819,7 +9841,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -9835,43 +9857,43 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" s="18">
-        <v>0</v>
-      </c>
-      <c r="F55" s="19">
-        <v>1.831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
-      </c>
-      <c r="E56" s="18"/>
-      <c r="F56" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E56" s="18">
+        <v>0</v>
+      </c>
+      <c r="F56" s="19">
+        <v>1.831</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -9887,7 +9909,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -9903,7 +9925,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -9919,7 +9941,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -9935,7 +9957,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -9951,7 +9973,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -9967,7 +9989,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -9983,7 +10005,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -9999,7 +10021,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -10015,7 +10037,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -10031,7 +10053,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -10047,7 +10069,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -10063,7 +10085,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -10079,7 +10101,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -10095,173 +10117,189 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
-      </c>
-      <c r="E71" s="18">
-        <v>0</v>
-      </c>
-      <c r="F71" s="19">
-        <v>2.645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E71" s="18"/>
+      <c r="F71" s="19"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
-      </c>
-      <c r="E72" s="18"/>
-      <c r="F72" s="19"/>
-    </row>
-    <row r="74" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="E75" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="F75" s="11" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>509</v>
-      </c>
-      <c r="B76">
-        <v>8</v>
-      </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <v>8</v>
-      </c>
-      <c r="E76" s="20">
-        <v>0</v>
-      </c>
-      <c r="F76" s="21">
-        <v>-0.18</v>
+        <v>1</v>
+      </c>
+      <c r="E72" s="18">
+        <v>0</v>
+      </c>
+      <c r="F72" s="19">
+        <v>2.645</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>511</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" s="18"/>
+      <c r="F73" s="19"/>
+    </row>
+    <row r="75" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
-      </c>
-      <c r="E77" s="18">
-        <v>1</v>
-      </c>
-      <c r="F77" s="21">
-        <v>-0.071</v>
+        <v>10</v>
+      </c>
+      <c r="E77" s="21">
+        <v>0</v>
+      </c>
+      <c r="F77" s="22">
+        <v>-0.196</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B78">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
         <v>2</v>
       </c>
-      <c r="D78">
-        <v>16</v>
-      </c>
-      <c r="E78" s="20">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F78" s="21">
-        <v>-0.002</v>
+      <c r="E78" s="18">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F78" s="22">
+        <v>-0.069</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D79">
-        <v>2</v>
-      </c>
-      <c r="E79" s="18">
-        <v>0</v>
-      </c>
-      <c r="F79" s="21">
-        <v>0.054</v>
+        <v>24</v>
+      </c>
+      <c r="E79" s="21">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="F79" s="22">
+        <v>-0.002</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80" s="18">
+        <v>0</v>
+      </c>
+      <c r="F80" s="22">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>519</v>
+      </c>
+      <c r="B81">
+        <v>20</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+      <c r="D81">
         <v>18</v>
       </c>
-      <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80">
-        <v>16</v>
-      </c>
-      <c r="E80" s="20">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="F80" s="21">
-        <v>0.362</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>514</v>
+      <c r="E81" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="F81" s="22">
+        <v>0.341</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>515</v>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -10280,7 +10318,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -10290,22 +10328,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -10315,17 +10353,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -10335,32 +10373,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -10370,22 +10408,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -10395,32 +10433,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -10430,27 +10468,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -10460,17 +10498,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="559">
   <si>
     <t>日期</t>
   </si>
@@ -941,7 +941,7 @@
     <t>09-25 17:00 / 09-26 11:00</t>
   </si>
   <si>
-    <t>09-27 11:00</t>
+    <t>09-27 17:00</t>
   </si>
   <si>
     <t>周六002</t>
@@ -1223,7 +1223,13 @@
     <t>09-27 18:00</t>
   </si>
   <si>
-    <t>09-26 17:00 / 09-27 11:00</t>
+    <t>09-27 11:00 / 09-27 17:00</t>
+  </si>
+  <si>
+    <t>新西兰</t>
+  </si>
+  <si>
+    <t>09-27 19:35</t>
   </si>
   <si>
     <t>格拉夫</t>
@@ -1235,6 +1241,15 @@
     <t>09-27 20:30</t>
   </si>
   <si>
+    <t>09-28 00:00</t>
+  </si>
+  <si>
+    <t>奥地利</t>
+  </si>
+  <si>
+    <t>09-28 02:45</t>
+  </si>
+  <si>
     <t>哥伦布</t>
   </si>
   <si>
@@ -1325,7 +1340,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-27T11:00:04+08:00）</t>
+    <t>统计（截至 2026-09-27T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -2150,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X88"/>
+  <dimension ref="A1:X94"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7933,16 +7948,16 @@
         <v>369</v>
       </c>
       <c r="U81" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W81" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W81" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X81" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.25">
@@ -7995,16 +8010,16 @@
         <v>369</v>
       </c>
       <c r="U82" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W82" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W82" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X82" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.25">
@@ -8057,16 +8072,16 @@
         <v>369</v>
       </c>
       <c r="U83" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W83" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W83" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X83" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.25">
@@ -8119,16 +8134,16 @@
         <v>369</v>
       </c>
       <c r="U84" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W84" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
+      </c>
+      <c r="W84" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X84" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.25">
@@ -8181,16 +8196,16 @@
         <v>369</v>
       </c>
       <c r="U85" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W85" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
+      </c>
+      <c r="W85" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X85" s="2" t="s">
-        <v>30</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.25">
@@ -8231,25 +8246,25 @@
         <v>0.175</v>
       </c>
       <c r="M86" s="3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N86" s="3">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="O86" s="3">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="P86" s="4">
-        <v>3.525</v>
+        <v>3.602</v>
       </c>
       <c r="Q86" s="5">
-        <v>0.175</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>80</v>
+        <v>0.198</v>
+      </c>
+      <c r="R86" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S86" s="4">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="T86" s="2" t="s">
         <v>402</v>
@@ -8272,61 +8287,49 @@
         <v>399</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>300</v>
+        <v>222</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>32</v>
+      <c r="G87" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H87" s="3">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="I87" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J87" s="3">
-        <v>23</v>
+        <v>6.75</v>
       </c>
       <c r="K87" s="4">
-        <v>11.244</v>
+        <v>4.03</v>
       </c>
       <c r="L87" s="5">
-        <v>1.756</v>
-      </c>
-      <c r="M87" s="3">
-        <v>13</v>
-      </c>
-      <c r="N87" s="3">
-        <v>22</v>
-      </c>
-      <c r="O87" s="3">
-        <v>23</v>
-      </c>
-      <c r="P87" s="4">
-        <v>11.244</v>
-      </c>
-      <c r="Q87" s="5">
-        <v>1.756</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="S87" s="4">
-        <v>0</v>
-      </c>
+        <v>0.07</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S87" s="4"/>
       <c r="T87" s="2" t="s">
-        <v>402</v>
+        <v>308</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>30</v>
@@ -8346,58 +8349,58 @@
         <v>399</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="G88" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="3">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="I88" s="3">
         <v>22</v>
       </c>
       <c r="J88" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K88" s="4">
-        <v>9.59</v>
+        <v>11.244</v>
       </c>
       <c r="L88" s="5">
-        <v>0.91</v>
+        <v>1.756</v>
       </c>
       <c r="M88" s="3">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="N88" s="3">
         <v>22</v>
       </c>
       <c r="O88" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P88" s="4">
-        <v>9.59</v>
+        <v>11.478</v>
       </c>
       <c r="Q88" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>80</v>
+        <v>1.522</v>
+      </c>
+      <c r="R88" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="S88" s="4">
-        <v>0</v>
+        <v>-0.234</v>
       </c>
       <c r="T88" s="2" t="s">
         <v>402</v>
@@ -8412,6 +8415,390 @@
         <v>30</v>
       </c>
       <c r="X88" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H89" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="I89" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="J89" s="3">
+        <v>22</v>
+      </c>
+      <c r="K89" s="4">
+        <v>5.731</v>
+      </c>
+      <c r="L89" s="5">
+        <v>0.769</v>
+      </c>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S89" s="4"/>
+      <c r="T89" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U89" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X89" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H90" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="I90" s="3">
+        <v>25</v>
+      </c>
+      <c r="J90" s="3">
+        <v>9</v>
+      </c>
+      <c r="K90" s="4">
+        <v>6.618</v>
+      </c>
+      <c r="L90" s="5">
+        <v>0.582</v>
+      </c>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S90" s="4"/>
+      <c r="T90" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="I91" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="J91" s="3">
+        <v>16</v>
+      </c>
+      <c r="K91" s="4">
+        <v>4.989</v>
+      </c>
+      <c r="L91" s="5">
+        <v>0.111</v>
+      </c>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S91" s="4"/>
+      <c r="T91" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" s="3">
+        <v>7.8</v>
+      </c>
+      <c r="I92" s="3">
+        <v>10</v>
+      </c>
+      <c r="J92" s="3">
+        <v>25</v>
+      </c>
+      <c r="K92" s="4">
+        <v>7.143</v>
+      </c>
+      <c r="L92" s="5">
+        <v>0.657</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S92" s="4"/>
+      <c r="T92" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H93" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="I93" s="3">
+        <v>13</v>
+      </c>
+      <c r="J93" s="3">
+        <v>15.5</v>
+      </c>
+      <c r="K93" s="4">
+        <v>7.07</v>
+      </c>
+      <c r="L93" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S93" s="4"/>
+      <c r="T93" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="U93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="I94" s="3">
+        <v>22</v>
+      </c>
+      <c r="J94" s="3">
+        <v>17</v>
+      </c>
+      <c r="K94" s="4">
+        <v>9.59</v>
+      </c>
+      <c r="L94" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="M94" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="N94" s="3">
+        <v>22</v>
+      </c>
+      <c r="O94" s="3">
+        <v>17</v>
+      </c>
+      <c r="P94" s="4">
+        <v>9.59</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S94" s="4">
+        <v>0</v>
+      </c>
+      <c r="T94" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="U94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X94" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -8433,33 +8820,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B2">
         <v>326</v>
@@ -8485,7 +8872,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B3">
         <v>325</v>
@@ -8511,7 +8898,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B4">
         <v>317</v>
@@ -8537,7 +8924,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B5">
         <v>309</v>
@@ -8563,7 +8950,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B6">
         <v>301</v>
@@ -8589,7 +8976,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B7">
         <v>283</v>
@@ -8615,7 +9002,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B8">
         <v>274</v>
@@ -8641,7 +9028,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B9">
         <v>253</v>
@@ -8667,7 +9054,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B10">
         <v>234</v>
@@ -8693,7 +9080,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B11">
         <v>212</v>
@@ -8719,7 +9106,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -8738,43 +9125,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C5" s="13">
         <v>31</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -8782,35 +9169,35 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B9" s="2">
         <v>3</v>
@@ -8833,7 +9220,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="B10" s="2">
         <v>1</v>
@@ -8856,7 +9243,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B11" s="15">
         <v>18</v>
@@ -8879,7 +9266,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B12" s="16">
         <v>31</v>
@@ -8902,7 +9289,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B13" s="2">
         <v>10</v>
@@ -8925,7 +9312,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B14" s="2">
         <v>10</v>
@@ -8948,7 +9335,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B15" s="2">
         <v>16</v>
@@ -8971,7 +9358,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -8994,7 +9381,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B17" s="15">
         <v>24</v>
@@ -9017,7 +9404,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -9056,25 +9443,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B4">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -9082,83 +9469,83 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B6">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B8" s="18">
-        <v>0.1282051282051282</v>
+        <v>0.13253012048192772</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B9" s="19">
-        <v>0.595</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B10" s="19">
-        <v>0.471</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B11" s="19">
-        <v>0.613</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -9168,60 +9555,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.535</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B16">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.595</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="F20" s="11" t="s">
         <v>457</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>450</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -9241,7 +9628,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -9261,7 +9648,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -9281,7 +9668,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -9301,7 +9688,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -9321,7 +9708,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -9341,7 +9728,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -9361,7 +9748,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -9381,7 +9768,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -9401,7 +9788,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -9421,7 +9808,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B31">
         <v>5</v>
@@ -9441,27 +9828,27 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" s="21">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F32" s="19">
-        <v>0.621</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -9481,7 +9868,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -9501,7 +9888,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B35">
         <v>2</v>
@@ -9521,47 +9908,47 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="18">
         <v>0</v>
       </c>
       <c r="F36" s="19">
-        <v>0.844</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" s="18">
         <v>0</v>
       </c>
       <c r="F37" s="19">
-        <v>0.874</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -9581,23 +9968,27 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="19">
+        <v>0.981</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -9617,7 +10008,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -9633,7 +10024,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -9649,7 +10040,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -9665,7 +10056,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -9681,7 +10072,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -9701,7 +10092,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -9721,7 +10112,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -9741,7 +10132,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -9757,7 +10148,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -9773,7 +10164,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -9789,7 +10180,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -9809,7 +10200,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -9825,7 +10216,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -9841,7 +10232,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -9857,7 +10248,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -9873,7 +10264,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -9893,7 +10284,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -9909,7 +10300,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -9925,7 +10316,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -9941,7 +10332,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -9957,7 +10348,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -9973,7 +10364,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -9989,7 +10380,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -10005,7 +10396,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -10021,7 +10412,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -10037,7 +10428,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -10053,7 +10444,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -10069,7 +10460,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -10085,7 +10476,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -10101,7 +10492,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -10117,7 +10508,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -10133,7 +10524,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -10153,7 +10544,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -10169,32 +10560,32 @@
     </row>
     <row r="75" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -10214,7 +10605,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -10234,7 +10625,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B79">
         <v>27</v>
@@ -10254,7 +10645,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -10274,7 +10665,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B81">
         <v>20</v>
@@ -10294,12 +10685,12 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -10318,7 +10709,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -10328,22 +10719,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -10353,17 +10744,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -10373,32 +10764,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -10408,22 +10799,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -10433,32 +10824,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -10468,27 +10859,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -10498,17 +10889,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="560">
   <si>
     <t>日期</t>
   </si>
@@ -1226,6 +1226,9 @@
     <t>09-27 11:00 / 09-27 17:00</t>
   </si>
   <si>
+    <t>09-28 11:00</t>
+  </si>
+  <si>
     <t>新西兰</t>
   </si>
   <si>
@@ -1313,10 +1316,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-26（共 383 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-26，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-27（共 384 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-27，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1340,7 +1343,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-27T17:00:05+08:00）</t>
+    <t>统计（截至 2026-09-28T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -8270,16 +8273,16 @@
         <v>402</v>
       </c>
       <c r="U86" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W86" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W86" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.25">
@@ -8296,10 +8299,10 @@
         <v>233</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>46</v>
@@ -8332,16 +8335,16 @@
         <v>308</v>
       </c>
       <c r="U87" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W87" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
+      </c>
+      <c r="W87" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X87" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.25">
@@ -8355,13 +8358,13 @@
         <v>300</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>32</v>
@@ -8406,16 +8409,16 @@
         <v>402</v>
       </c>
       <c r="U88" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W88" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W88" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X88" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.25">
@@ -8435,7 +8438,7 @@
         <v>243</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>32</v>
@@ -8468,16 +8471,16 @@
         <v>308</v>
       </c>
       <c r="U89" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V89" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W89" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W89" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X89" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.25">
@@ -8497,7 +8500,7 @@
         <v>245</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>46</v>
@@ -8530,16 +8533,16 @@
         <v>308</v>
       </c>
       <c r="U90" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V90" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W90" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W90" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X90" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.25">
@@ -8553,13 +8556,13 @@
         <v>237</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>32</v>
@@ -8592,16 +8595,16 @@
         <v>308</v>
       </c>
       <c r="U91" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V91" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W91" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
+      </c>
+      <c r="W91" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X91" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.25">
@@ -8621,7 +8624,7 @@
         <v>249</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>32</v>
@@ -8654,16 +8657,16 @@
         <v>308</v>
       </c>
       <c r="U92" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V92" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W92" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W92" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X92" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.25">
@@ -8683,7 +8686,7 @@
         <v>242</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>46</v>
@@ -8716,16 +8719,16 @@
         <v>308</v>
       </c>
       <c r="U93" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W93" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W93" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X93" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.25">
@@ -8739,13 +8742,13 @@
         <v>215</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>32</v>
@@ -8790,16 +8793,16 @@
         <v>402</v>
       </c>
       <c r="U94" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W94" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W94" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X94" s="2" t="s">
-        <v>30</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -8820,39 +8823,39 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2">
         <v>57</v>
@@ -8872,10 +8875,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B3">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -8887,7 +8890,7 @@
         <v>87</v>
       </c>
       <c r="F3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3">
         <v>45</v>
@@ -8898,16 +8901,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B4">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4">
         <v>22</v>
       </c>
       <c r="D4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4">
         <v>68</v>
@@ -8924,10 +8927,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B5">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -8936,7 +8939,7 @@
         <v>52</v>
       </c>
       <c r="E5">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F5">
         <v>52</v>
@@ -8950,10 +8953,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B6">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -8965,7 +8968,7 @@
         <v>72</v>
       </c>
       <c r="F6">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>41</v>
@@ -8976,10 +8979,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -8994,7 +8997,7 @@
         <v>76</v>
       </c>
       <c r="G7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H7">
         <v>32</v>
@@ -9002,16 +9005,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C8">
         <v>20</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>66</v>
@@ -9028,10 +9031,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B9">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -9043,7 +9046,7 @@
         <v>63</v>
       </c>
       <c r="F9">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>25</v>
@@ -9054,10 +9057,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B10">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C10">
         <v>11</v>
@@ -9069,7 +9072,7 @@
         <v>55</v>
       </c>
       <c r="F10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>27</v>
@@ -9080,7 +9083,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B11">
         <v>212</v>
@@ -9106,7 +9109,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -9125,43 +9128,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C5" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -9169,242 +9172,242 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="C9" s="2">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2">
-        <v>4</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2</v>
-      </c>
       <c r="G9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="C10" s="2">
-        <v>10</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
       <c r="E10" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B11" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
+      <c r="F11" s="15">
+        <v>26</v>
+      </c>
+      <c r="G11" s="2">
         <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="F11" s="15">
-        <v>25</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B12" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>23</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
         <v>4</v>
-      </c>
-      <c r="E12" s="15">
-        <v>22</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B13" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B14" s="2">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
         <v>10</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2">
-        <v>7</v>
-      </c>
-      <c r="G14" s="2">
-        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B15" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>12</v>
+      </c>
+      <c r="G16" s="2">
         <v>3</v>
-      </c>
-      <c r="D16" s="2">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2">
-        <v>11</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -9443,17 +9446,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B4">
         <v>93</v>
@@ -9461,7 +9464,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -9469,86 +9472,86 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B6">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B8" s="18">
-        <v>0.13253012048192772</v>
+        <v>0.14130434782608695</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B9" s="19">
-        <v>0.606</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B10" s="19">
-        <v>0.487</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B11" s="19">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B15">
         <v>11</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -9560,16 +9563,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B16">
         <v>70</v>
       </c>
       <c r="C16">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
@@ -9578,97 +9581,97 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="19">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="18">
         <v>0</v>
       </c>
       <c r="F22" s="19">
-        <v>0.131</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="19">
-        <v>0.185</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -9688,7 +9691,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -9708,7 +9711,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -9728,7 +9731,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -9748,7 +9751,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -9768,7 +9771,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -9788,7 +9791,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -9808,27 +9811,27 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="21">
         <v>0</v>
       </c>
       <c r="F31" s="19">
-        <v>0.563</v>
+        <v>0.566</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B32">
         <v>9</v>
@@ -9848,27 +9851,27 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="18">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F33" s="19">
-        <v>0.683</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -9888,27 +9891,27 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" s="18">
         <v>0</v>
       </c>
       <c r="F35" s="19">
-        <v>0.758</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -9928,7 +9931,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -9948,27 +9951,27 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" s="18">
         <v>0</v>
       </c>
       <c r="F38" s="19">
-        <v>0.937</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -9988,7 +9991,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -10008,7 +10011,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -10024,23 +10027,27 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E42" s="18">
+        <v>0</v>
+      </c>
+      <c r="F42" s="19">
+        <v>1.13</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -10056,7 +10063,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -10072,7 +10079,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -10092,7 +10099,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -10112,7 +10119,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -10132,7 +10139,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -10148,7 +10155,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10164,23 +10171,27 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="19"/>
+      <c r="E50" s="18">
+        <v>1</v>
+      </c>
+      <c r="F50" s="19">
+        <v>1.522</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -10200,7 +10211,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -10216,7 +10227,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -10232,7 +10243,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -10248,7 +10259,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -10264,7 +10275,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -10284,7 +10295,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -10300,7 +10311,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -10316,7 +10327,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -10332,7 +10343,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -10348,7 +10359,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -10364,7 +10375,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -10380,7 +10391,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -10396,7 +10407,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -10412,7 +10423,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -10428,7 +10439,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -10444,7 +10455,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -10460,7 +10471,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -10476,7 +10487,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -10492,7 +10503,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -10508,7 +10519,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -10524,7 +10535,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -10544,7 +10555,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -10560,52 +10571,52 @@
     </row>
     <row r="75" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B77">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>10</v>
       </c>
       <c r="E77" s="21">
-        <v>0</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="F77" s="22">
-        <v>-0.196</v>
+        <v>-0.199</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -10625,27 +10636,27 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B79">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C79">
         <v>3</v>
       </c>
       <c r="D79">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E79" s="21">
-        <v>0.1111111111111111</v>
+        <v>0.10344827586206896</v>
       </c>
       <c r="F79" s="22">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -10665,7 +10676,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B81">
         <v>20</v>
@@ -10685,12 +10696,12 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -10709,7 +10720,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -10719,22 +10730,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -10744,17 +10755,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -10764,32 +10775,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -10799,22 +10810,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -10824,32 +10835,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -10859,27 +10870,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -10889,17 +10900,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="581">
   <si>
     <t>日期</t>
   </si>
@@ -1262,6 +1262,69 @@
     <t>09-28 07:00</t>
   </si>
   <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>委内瑞拉</t>
+  </si>
+  <si>
+    <t>09-28 18:25</t>
+  </si>
+  <si>
+    <t>09-28 17:00</t>
+  </si>
+  <si>
+    <t>周一002</t>
+  </si>
+  <si>
+    <t>09-28 19:00</t>
+  </si>
+  <si>
+    <t>周一003</t>
+  </si>
+  <si>
+    <t>09-29 00:00</t>
+  </si>
+  <si>
+    <t>周一004</t>
+  </si>
+  <si>
+    <t>09-29 02:45</t>
+  </si>
+  <si>
+    <t>周一005</t>
+  </si>
+  <si>
+    <t>周一006</t>
+  </si>
+  <si>
+    <t>周一007</t>
+  </si>
+  <si>
+    <t>周一008</t>
+  </si>
+  <si>
+    <t>匈牙利</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>朝鲜女</t>
+  </si>
+  <si>
+    <t>09-29 14:00</t>
+  </si>
+  <si>
+    <t>周二007</t>
+  </si>
+  <si>
+    <t>日本女</t>
+  </si>
+  <si>
+    <t>09-29 18:30</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1343,7 +1406,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-28T11:00:04+08:00）</t>
+    <t>统计（截至 2026-09-28T17:00:08+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -2168,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X94"/>
+  <dimension ref="A1:X104"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8805,6 +8868,626 @@
         <v>403</v>
       </c>
     </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="I95" s="3">
+        <v>6.75</v>
+      </c>
+      <c r="J95" s="3">
+        <v>30</v>
+      </c>
+      <c r="K95" s="4">
+        <v>5.51</v>
+      </c>
+      <c r="L95" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S95" s="4"/>
+      <c r="T95" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" s="3">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J96" s="3">
+        <v>8.25</v>
+      </c>
+      <c r="K96" s="4">
+        <v>3.929</v>
+      </c>
+      <c r="L96" s="5">
+        <v>0.071</v>
+      </c>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S96" s="4"/>
+      <c r="T96" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="I97" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="J97" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="K97" s="4">
+        <v>4.054</v>
+      </c>
+      <c r="L97" s="5">
+        <v>0.346</v>
+      </c>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S97" s="4"/>
+      <c r="T97" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H98" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="I98" s="3">
+        <v>11</v>
+      </c>
+      <c r="J98" s="3">
+        <v>10</v>
+      </c>
+      <c r="K98" s="4">
+        <v>5.238</v>
+      </c>
+      <c r="L98" s="5">
+        <v>0.562</v>
+      </c>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S98" s="4"/>
+      <c r="T98" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H99" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="I99" s="3">
+        <v>18</v>
+      </c>
+      <c r="J99" s="3">
+        <v>11</v>
+      </c>
+      <c r="K99" s="4">
+        <v>6.828</v>
+      </c>
+      <c r="L99" s="5">
+        <v>0.622</v>
+      </c>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S99" s="4"/>
+      <c r="T99" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U99" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="I100" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="K100" s="4">
+        <v>4.375</v>
+      </c>
+      <c r="L100" s="5">
+        <v>0.325</v>
+      </c>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3"/>
+      <c r="O100" s="3"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S100" s="4"/>
+      <c r="T100" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="I101" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="J101" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="K101" s="4">
+        <v>5.147</v>
+      </c>
+      <c r="L101" s="5">
+        <v>1.053</v>
+      </c>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S101" s="4"/>
+      <c r="T101" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U101" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="I102" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="K102" s="4">
+        <v>3.686</v>
+      </c>
+      <c r="L102" s="5">
+        <v>0.014</v>
+      </c>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S102" s="4"/>
+      <c r="T102" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" s="3">
+        <v>5.25</v>
+      </c>
+      <c r="I103" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="J103" s="3">
+        <v>18</v>
+      </c>
+      <c r="K103" s="4">
+        <v>4.776</v>
+      </c>
+      <c r="L103" s="5">
+        <v>0.474</v>
+      </c>
+      <c r="M103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S103" s="4"/>
+      <c r="T103" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="I104" s="3">
+        <v>8</v>
+      </c>
+      <c r="J104" s="3">
+        <v>26</v>
+      </c>
+      <c r="K104" s="4">
+        <v>6.118</v>
+      </c>
+      <c r="L104" s="5">
+        <v>0.382</v>
+      </c>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S104" s="4"/>
+      <c r="T104" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8823,33 +9506,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="B2">
         <v>327</v>
@@ -8875,7 +9558,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="B3">
         <v>326</v>
@@ -8901,7 +9584,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B4">
         <v>318</v>
@@ -8927,7 +9610,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B5">
         <v>310</v>
@@ -8953,7 +9636,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="B6">
         <v>302</v>
@@ -8979,7 +9662,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B7">
         <v>284</v>
@@ -9005,7 +9688,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="B8">
         <v>275</v>
@@ -9031,7 +9714,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B9">
         <v>254</v>
@@ -9057,7 +9740,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B10">
         <v>235</v>
@@ -9083,7 +9766,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B11">
         <v>212</v>
@@ -9109,7 +9792,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -9128,43 +9811,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C5" s="13">
         <v>32</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -9172,35 +9855,35 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
@@ -9223,7 +9906,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -9246,7 +9929,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="B11" s="15">
         <v>19</v>
@@ -9269,7 +9952,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="B12" s="16">
         <v>32</v>
@@ -9292,7 +9975,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="B13" s="2">
         <v>11</v>
@@ -9315,7 +9998,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="B14" s="2">
         <v>11</v>
@@ -9338,7 +10021,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="B15" s="2">
         <v>17</v>
@@ -9361,7 +10044,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -9384,7 +10067,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B17" s="15">
         <v>25</v>
@@ -9407,7 +10090,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -9446,25 +10129,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="B4">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -9472,7 +10155,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="B6">
         <v>92</v>
@@ -9480,7 +10163,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -9488,7 +10171,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="B8" s="18">
         <v>0.14130434782608695</v>
@@ -9496,7 +10179,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B9" s="19">
         <v>0.612</v>
@@ -9504,7 +10187,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="B10" s="19">
         <v>0.58</v>
@@ -9512,7 +10195,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="B11" s="19">
         <v>0.617</v>
@@ -9520,35 +10203,35 @@
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -9558,15 +10241,15 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.551</v>
+        <v>0.557</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="B16">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C16">
         <v>69</v>
@@ -9576,42 +10259,42 @@
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.588</v>
+        <v>0.566</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>465</v>
+        <v>486</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -9631,7 +10314,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>466</v>
+        <v>487</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -9651,7 +10334,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>467</v>
+        <v>488</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -9671,7 +10354,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>468</v>
+        <v>489</v>
       </c>
       <c r="B24">
         <v>6</v>
@@ -9691,7 +10374,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>469</v>
+        <v>490</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -9711,7 +10394,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>470</v>
+        <v>491</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -9731,7 +10414,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="B27">
         <v>10</v>
@@ -9751,7 +10434,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -9771,7 +10454,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -9791,7 +10474,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -9811,7 +10494,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="B31">
         <v>6</v>
@@ -9831,7 +10514,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>476</v>
+        <v>497</v>
       </c>
       <c r="B32">
         <v>9</v>
@@ -9851,7 +10534,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="B33">
         <v>4</v>
@@ -9871,7 +10554,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -9891,7 +10574,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -9911,7 +10594,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -9931,7 +10614,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -9951,7 +10634,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>482</v>
+        <v>503</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -9971,7 +10654,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -9991,7 +10674,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="B40">
         <v>5</v>
@@ -10011,7 +10694,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -10027,7 +10710,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>486</v>
+        <v>507</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -10047,7 +10730,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>487</v>
+        <v>508</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -10063,7 +10746,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -10079,7 +10762,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>489</v>
+        <v>510</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -10099,7 +10782,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -10119,7 +10802,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -10139,7 +10822,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -10155,7 +10838,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10171,7 +10854,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -10191,7 +10874,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -10211,7 +10894,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -10227,7 +10910,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -10243,7 +10926,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -10259,7 +10942,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -10275,7 +10958,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -10295,7 +10978,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -10311,7 +10994,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -10327,7 +11010,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -10343,7 +11026,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -10359,7 +11042,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -10375,7 +11058,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -10391,7 +11074,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -10407,7 +11090,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -10423,7 +11106,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -10439,7 +11122,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>510</v>
+        <v>531</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -10455,7 +11138,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -10471,7 +11154,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>512</v>
+        <v>533</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -10487,7 +11170,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>513</v>
+        <v>534</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -10503,7 +11186,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -10519,7 +11202,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -10535,7 +11218,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -10555,7 +11238,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -10571,32 +11254,32 @@
     </row>
     <row r="75" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
     </row>
     <row r="76" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="B77">
         <v>11</v>
@@ -10616,7 +11299,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="B78">
         <v>3</v>
@@ -10636,7 +11319,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="B79">
         <v>29</v>
@@ -10656,7 +11339,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -10676,7 +11359,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B81">
         <v>20</v>
@@ -10696,12 +11379,12 @@
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -10720,7 +11403,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -10730,22 +11413,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>531</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>532</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -10755,17 +11438,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>535</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -10775,32 +11458,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>536</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>538</v>
+        <v>559</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -10810,22 +11493,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -10835,32 +11518,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>550</v>
+        <v>571</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -10870,27 +11553,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>552</v>
+        <v>573</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>554</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -10900,17 +11583,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="585">
   <si>
     <t>日期</t>
   </si>
@@ -1274,12 +1274,18 @@
     <t>09-28 17:00</t>
   </si>
   <si>
+    <t>09-29 11:00</t>
+  </si>
+  <si>
     <t>周一002</t>
   </si>
   <si>
     <t>09-28 19:00</t>
   </si>
   <si>
+    <t>1:4</t>
+  </si>
+  <si>
     <t>周一003</t>
   </si>
   <si>
@@ -1316,6 +1322,9 @@
     <t>09-29 14:00</t>
   </si>
   <si>
+    <t>09-28 17:00 / 09-29 11:00</t>
+  </si>
+  <si>
     <t>周二007</t>
   </si>
   <si>
@@ -1379,10 +1388,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-27（共 384 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-27，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-28（共 385 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-28，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1406,7 +1415,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-28T17:00:08+08:00）</t>
+    <t>统计（截至 2026-09-29T11:00:06+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -1473,6 +1482,9 @@
   </si>
   <si>
     <t>非1球场次</t>
+  </si>
+  <si>
+    <t>0.00 ~ 0.05</t>
   </si>
   <si>
     <t>0.05 ~ 0.10</t>
@@ -8918,16 +8930,16 @@
         <v>418</v>
       </c>
       <c r="U95" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W95" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W95" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X95" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.25">
@@ -8935,7 +8947,7 @@
         <v>415</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>222</v>
@@ -8947,7 +8959,7 @@
         <v>224</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>32</v>
@@ -8980,16 +8992,16 @@
         <v>418</v>
       </c>
       <c r="U96" s="2" t="s">
-        <v>30</v>
+        <v>422</v>
       </c>
       <c r="V96" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W96" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="W96" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X96" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.25">
@@ -8997,7 +9009,7 @@
         <v>415</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>237</v>
@@ -9009,7 +9021,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>32</v>
@@ -9042,16 +9054,16 @@
         <v>418</v>
       </c>
       <c r="U97" s="2" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W97" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
+      </c>
+      <c r="W97" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X97" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.25">
@@ -9059,7 +9071,7 @@
         <v>415</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>237</v>
@@ -9071,7 +9083,7 @@
         <v>283</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>46</v>
@@ -9104,16 +9116,16 @@
         <v>418</v>
       </c>
       <c r="U98" s="2" t="s">
-        <v>30</v>
+        <v>422</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W98" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="W98" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.25">
@@ -9121,7 +9133,7 @@
         <v>415</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>237</v>
@@ -9133,7 +9145,7 @@
         <v>295</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>46</v>
@@ -9166,16 +9178,16 @@
         <v>418</v>
       </c>
       <c r="U99" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="V99" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W99" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W99" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="X99" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.25">
@@ -9183,7 +9195,7 @@
         <v>415</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>237</v>
@@ -9195,7 +9207,7 @@
         <v>292</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>32</v>
@@ -9228,16 +9240,16 @@
         <v>418</v>
       </c>
       <c r="U100" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="V100" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W100" s="2" t="s">
-        <v>30</v>
+        <v>318</v>
+      </c>
+      <c r="W100" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.25">
@@ -9245,7 +9257,7 @@
         <v>415</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>237</v>
@@ -9257,7 +9269,7 @@
         <v>291</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>32</v>
@@ -9290,16 +9302,16 @@
         <v>418</v>
       </c>
       <c r="U101" s="2" t="s">
-        <v>30</v>
+        <v>145</v>
       </c>
       <c r="V101" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W101" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W101" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X101" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.25">
@@ -9307,7 +9319,7 @@
         <v>415</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>237</v>
@@ -9316,10 +9328,10 @@
         <v>277</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>32</v>
@@ -9352,21 +9364,21 @@
         <v>418</v>
       </c>
       <c r="U102" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V102" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W102" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W102" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X102" s="2" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>185</v>
@@ -9375,13 +9387,13 @@
         <v>177</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>178</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>32</v>
@@ -9401,17 +9413,29 @@
       <c r="L103" s="5">
         <v>0.474</v>
       </c>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
-      <c r="O103" s="3"/>
-      <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S103" s="4"/>
+      <c r="M103" s="3">
+        <v>5.25</v>
+      </c>
+      <c r="N103" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="O103" s="3">
+        <v>18</v>
+      </c>
+      <c r="P103" s="4">
+        <v>4.776</v>
+      </c>
+      <c r="Q103" s="5">
+        <v>0.474</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S103" s="4">
+        <v>0</v>
+      </c>
       <c r="T103" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="U103" s="2" t="s">
         <v>30</v>
@@ -9428,22 +9452,22 @@
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>272</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>32</v>
@@ -9463,17 +9487,29 @@
       <c r="L104" s="5">
         <v>0.382</v>
       </c>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3"/>
-      <c r="O104" s="3"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S104" s="4"/>
+      <c r="M104" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="N104" s="3">
+        <v>8</v>
+      </c>
+      <c r="O104" s="3">
+        <v>28</v>
+      </c>
+      <c r="P104" s="4">
+        <v>6.222</v>
+      </c>
+      <c r="Q104" s="5">
+        <v>0.478</v>
+      </c>
+      <c r="R104" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S104" s="4">
+        <v>0.096</v>
+      </c>
       <c r="T104" s="2" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="U104" s="2" t="s">
         <v>30</v>
@@ -9506,36 +9542,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -9547,7 +9583,7 @@
         <v>68</v>
       </c>
       <c r="F2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2">
         <v>52</v>
@@ -9558,10 +9594,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B3">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -9579,15 +9615,15 @@
         <v>45</v>
       </c>
       <c r="H3">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B4">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -9605,15 +9641,15 @@
         <v>46</v>
       </c>
       <c r="H4">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B5">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -9631,21 +9667,21 @@
         <v>64</v>
       </c>
       <c r="H5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B6">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6">
         <v>72</v>
@@ -9662,10 +9698,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -9683,15 +9719,15 @@
         <v>53</v>
       </c>
       <c r="H7">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B8">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -9706,7 +9742,7 @@
         <v>61</v>
       </c>
       <c r="G8">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>45</v>
@@ -9714,13 +9750,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B9">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>42</v>
@@ -9740,7 +9776,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B10">
         <v>235</v>
@@ -9766,7 +9802,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B11">
         <v>212</v>
@@ -9792,7 +9828,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -9811,43 +9847,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C5" s="13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -9855,219 +9891,219 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B10" s="2">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="C10" s="2">
-        <v>11</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
       <c r="F10" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G10" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B11" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B12" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B13" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B14" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2">
         <v>2</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
+        <v>6</v>
+      </c>
+      <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
-        <v>5</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
       <c r="G14" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B15" s="2">
-        <v>17</v>
+        <v>453</v>
+      </c>
+      <c r="B15" s="15">
+        <v>18</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="F16" s="2">
+        <v>13</v>
+      </c>
+      <c r="G16" s="2">
         <v>4</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2">
-        <v>12</v>
-      </c>
-      <c r="G16" s="2">
-        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B17" s="15">
         <v>25</v>
@@ -10090,7 +10126,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -10119,7 +10155,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -10129,17 +10165,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B4">
         <v>103</v>
@@ -10147,97 +10183,97 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B5">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B8" s="18">
-        <v>0.14130434782608695</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B9" s="19">
-        <v>0.612</v>
+        <v>0.596</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B10" s="19">
-        <v>0.58</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B11" s="19">
-        <v>0.617</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
@@ -10246,335 +10282,335 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B16">
         <v>78</v>
       </c>
       <c r="C16">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D16">
         <v>10</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.566</v>
+        <v>0.567</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="18">
         <v>0</v>
       </c>
       <c r="F21" s="19">
-        <v>0.068</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="18">
         <v>0</v>
       </c>
       <c r="F22" s="19">
-        <v>0.126</v>
+        <v>0.069</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="18">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F23" s="19">
-        <v>0.192</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24" s="20">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18">
         <v>0.5</v>
       </c>
       <c r="F24" s="19">
-        <v>0.224</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B25">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>6</v>
-      </c>
-      <c r="E25" s="21">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E25" s="20">
+        <v>0.5</v>
       </c>
       <c r="F25" s="19">
-        <v>0.271</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B26">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26" s="18">
-        <v>0.5</v>
+        <v>7</v>
+      </c>
+      <c r="E26" s="21">
+        <v>0</v>
       </c>
       <c r="F26" s="19">
-        <v>0.324</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27" s="21">
-        <v>0.1</v>
+        <v>4</v>
+      </c>
+      <c r="E27" s="20">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F27" s="19">
-        <v>0.374</v>
+        <v>0.328</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E28" s="21">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="19">
-        <v>0.429</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" s="18">
+        <v>5</v>
+      </c>
+      <c r="E29" s="21">
         <v>0</v>
       </c>
       <c r="F29" s="19">
-        <v>0.475</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B30">
         <v>3</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="18">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="F30" s="19">
-        <v>0.531</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>6</v>
-      </c>
-      <c r="E31" s="21">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E31" s="18">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F31" s="19">
-        <v>0.566</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" s="21">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="F32" s="19">
-        <v>0.625</v>
+        <v>0.566</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33" s="18">
-        <v>0.5</v>
+        <v>8</v>
+      </c>
+      <c r="E33" s="20">
+        <v>0.2</v>
       </c>
       <c r="F33" s="19">
-        <v>0.677</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="18">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F34" s="19">
-        <v>0.724</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -10589,52 +10625,52 @@
         <v>0</v>
       </c>
       <c r="F35" s="19">
-        <v>0.761</v>
+        <v>0.724</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="18">
         <v>0</v>
       </c>
       <c r="F36" s="19">
-        <v>0.827</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="18">
         <v>0</v>
       </c>
       <c r="F37" s="19">
-        <v>0.88</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -10649,68 +10685,72 @@
         <v>0</v>
       </c>
       <c r="F38" s="19">
-        <v>0.928</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E39" s="18">
         <v>0</v>
       </c>
       <c r="F39" s="19">
-        <v>0.981</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>5</v>
-      </c>
-      <c r="E40" s="21">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18">
         <v>0</v>
       </c>
       <c r="F40" s="19">
-        <v>1.035</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="19"/>
+        <v>5</v>
+      </c>
+      <c r="E41" s="21">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19">
+        <v>1.035</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -10725,28 +10765,32 @@
         <v>0</v>
       </c>
       <c r="F42" s="19">
-        <v>1.13</v>
+        <v>1.053</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E43" s="18">
+        <v>0</v>
+      </c>
+      <c r="F43" s="19">
+        <v>1.13</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -10762,27 +10806,23 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" s="18">
-        <v>0</v>
-      </c>
-      <c r="F45" s="19">
-        <v>1.259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="19"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -10797,12 +10837,12 @@
         <v>0</v>
       </c>
       <c r="F46" s="19">
-        <v>1.318</v>
+        <v>1.259</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -10817,28 +10857,32 @@
         <v>0</v>
       </c>
       <c r="F47" s="19">
-        <v>1.395</v>
+        <v>1.318</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E48" s="18">
+        <v>0</v>
+      </c>
+      <c r="F48" s="19">
+        <v>1.395</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10854,27 +10898,23 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="18">
-        <v>1</v>
-      </c>
-      <c r="F50" s="19">
-        <v>1.522</v>
-      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -10889,28 +10929,32 @@
         <v>1</v>
       </c>
       <c r="F51" s="19">
-        <v>1.587</v>
+        <v>1.522</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
-      <c r="E52" s="18"/>
-      <c r="F52" s="19"/>
+      <c r="E52" s="18">
+        <v>1</v>
+      </c>
+      <c r="F52" s="19">
+        <v>1.587</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -10926,7 +10970,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -10942,7 +10986,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -10958,43 +11002,43 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" s="18">
-        <v>0</v>
-      </c>
-      <c r="F56" s="19">
-        <v>1.831</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E56" s="18"/>
+      <c r="F56" s="19"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
-      </c>
-      <c r="E57" s="18"/>
-      <c r="F57" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E57" s="18">
+        <v>0</v>
+      </c>
+      <c r="F57" s="19">
+        <v>1.831</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -11010,7 +11054,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -11026,7 +11070,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -11042,7 +11086,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -11058,7 +11102,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -11074,7 +11118,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -11090,7 +11134,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -11106,7 +11150,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -11122,7 +11166,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -11138,7 +11182,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -11154,7 +11198,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -11170,7 +11214,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -11186,7 +11230,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -11202,7 +11246,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -11218,173 +11262,189 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
-      </c>
-      <c r="E72" s="18">
-        <v>0</v>
-      </c>
-      <c r="F72" s="19">
-        <v>2.645</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E72" s="18"/>
+      <c r="F72" s="19"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
-      </c>
-      <c r="E73" s="18"/>
-      <c r="F73" s="19"/>
-    </row>
-    <row r="75" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="12" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="C76" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>485</v>
-      </c>
-      <c r="E76" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E73" s="18">
+        <v>0</v>
+      </c>
+      <c r="F73" s="19">
+        <v>2.645</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>542</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" s="18"/>
+      <c r="F74" s="19"/>
+    </row>
+    <row r="76" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="F76" s="11" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>542</v>
-      </c>
-      <c r="B77">
-        <v>11</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
-      </c>
-      <c r="D77">
-        <v>10</v>
-      </c>
-      <c r="E77" s="21">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="F77" s="22">
-        <v>-0.199</v>
+      <c r="C77" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="F77" s="11" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B78">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78">
-        <v>2</v>
-      </c>
-      <c r="E78" s="18">
-        <v>0.3333333333333333</v>
+        <v>10</v>
+      </c>
+      <c r="E78" s="21">
+        <v>0.09090909090909091</v>
       </c>
       <c r="F78" s="22">
-        <v>-0.069</v>
+        <v>-0.199</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B79">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>26</v>
-      </c>
-      <c r="E79" s="21">
-        <v>0.10344827586206896</v>
+        <v>2</v>
+      </c>
+      <c r="E79" s="18">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F79" s="22">
-        <v>-0.001</v>
+        <v>-0.069</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D80">
-        <v>2</v>
-      </c>
-      <c r="E80" s="18">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="E80" s="21">
+        <v>0.10344827586206896</v>
       </c>
       <c r="F80" s="22">
-        <v>0.054</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B81">
+        <v>2</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+      <c r="E81" s="18">
+        <v>0</v>
+      </c>
+      <c r="F81" s="22">
+        <v>0.054</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>550</v>
+      </c>
+      <c r="B82">
         <v>20</v>
       </c>
-      <c r="C81">
+      <c r="C82">
         <v>2</v>
       </c>
-      <c r="D81">
+      <c r="D82">
         <v>18</v>
       </c>
-      <c r="E81" s="21">
+      <c r="E82" s="21">
         <v>0.1</v>
       </c>
-      <c r="F81" s="22">
+      <c r="F82" s="22">
         <v>0.341</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>548</v>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -11403,7 +11463,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -11413,22 +11473,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -11438,17 +11498,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -11458,32 +11518,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -11493,22 +11553,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -11518,32 +11578,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -11553,27 +11613,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -11583,17 +11643,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="611">
   <si>
     <t>日期</t>
   </si>
@@ -1325,6 +1325,39 @@
     <t>09-28 17:00 / 09-29 11:00</t>
   </si>
   <si>
+    <t>09-29 18:00</t>
+  </si>
+  <si>
+    <t>09-29 17:00</t>
+  </si>
+  <si>
+    <t>日联赛杯</t>
+  </si>
+  <si>
+    <t>大阪樱花</t>
+  </si>
+  <si>
+    <t>枥木城</t>
+  </si>
+  <si>
+    <t>广岛三箭</t>
+  </si>
+  <si>
+    <t>周二005</t>
+  </si>
+  <si>
+    <t>浦和红钻</t>
+  </si>
+  <si>
+    <t>周二006</t>
+  </si>
+  <si>
+    <t>山形山神</t>
+  </si>
+  <si>
+    <t>横滨水手</t>
+  </si>
+  <si>
     <t>周二007</t>
   </si>
   <si>
@@ -1334,6 +1367,51 @@
     <t>09-29 18:30</t>
   </si>
   <si>
+    <t>09-29 11:00 / 09-29 17:00</t>
+  </si>
+  <si>
+    <t>周二008</t>
+  </si>
+  <si>
+    <t>09-30 02:45</t>
+  </si>
+  <si>
+    <t>周二009</t>
+  </si>
+  <si>
+    <t>周二010</t>
+  </si>
+  <si>
+    <t>周二011</t>
+  </si>
+  <si>
+    <t>斯洛伐克</t>
+  </si>
+  <si>
+    <t>周二012</t>
+  </si>
+  <si>
+    <t>周二013</t>
+  </si>
+  <si>
+    <t>周二014</t>
+  </si>
+  <si>
+    <t>周二015</t>
+  </si>
+  <si>
+    <t>09-30 08:00</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>09-30 14:00</t>
+  </si>
+  <si>
+    <t>09-30 18:30</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1415,7 +1493,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-29T11:00:06+08:00）</t>
+    <t>统计（截至 2026-09-29T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -2243,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X104"/>
+  <dimension ref="A1:X119"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -9455,72 +9533,1002 @@
         <v>432</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="G104" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="I104" s="3">
+        <v>25</v>
+      </c>
+      <c r="J104" s="3">
+        <v>8</v>
+      </c>
+      <c r="K104" s="4">
+        <v>6.061</v>
+      </c>
+      <c r="L104" s="5">
+        <v>0.739</v>
+      </c>
+      <c r="M104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S104" s="4"/>
+      <c r="T104" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" s="3">
+        <v>5.9</v>
+      </c>
+      <c r="I105" s="3">
+        <v>18</v>
+      </c>
+      <c r="J105" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K105" s="4">
+        <v>5.294</v>
+      </c>
+      <c r="L105" s="5">
+        <v>0.606</v>
+      </c>
+      <c r="M105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S105" s="4"/>
+      <c r="T105" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="3">
+        <v>10</v>
+      </c>
+      <c r="I106" s="3">
+        <v>55</v>
+      </c>
+      <c r="J106" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="K106" s="4">
+        <v>8.817</v>
+      </c>
+      <c r="L106" s="5">
+        <v>1.183</v>
+      </c>
+      <c r="M106" s="3"/>
+      <c r="N106" s="3"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S106" s="4"/>
+      <c r="T106" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X106" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H107" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="I107" s="3">
+        <v>28</v>
+      </c>
+      <c r="J107" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="K107" s="4">
+        <v>6.521</v>
+      </c>
+      <c r="L107" s="5">
+        <v>0.279</v>
+      </c>
+      <c r="M107" s="3"/>
+      <c r="N107" s="3"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S107" s="4"/>
+      <c r="T107" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X107" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="I108" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="J108" s="3">
+        <v>7</v>
+      </c>
+      <c r="K108" s="4">
+        <v>5.078</v>
+      </c>
+      <c r="L108" s="5">
+        <v>1.022</v>
+      </c>
+      <c r="M108" s="3"/>
+      <c r="N108" s="3"/>
+      <c r="O108" s="3"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S108" s="4"/>
+      <c r="T108" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X108" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D109" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H109" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="I109" s="3">
+        <v>8</v>
+      </c>
+      <c r="J109" s="3">
+        <v>28</v>
+      </c>
+      <c r="K109" s="4">
+        <v>6.222</v>
+      </c>
+      <c r="L109" s="5">
+        <v>0.478</v>
+      </c>
+      <c r="M109" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="N109" s="3">
+        <v>8.2</v>
+      </c>
+      <c r="O109" s="3">
+        <v>35</v>
+      </c>
+      <c r="P109" s="4">
+        <v>6.644</v>
+      </c>
+      <c r="Q109" s="5">
+        <v>0.856</v>
+      </c>
+      <c r="R109" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="S109" s="4">
+        <v>0.378</v>
+      </c>
+      <c r="T109" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="U109" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H110" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="I110" s="3">
+        <v>11</v>
+      </c>
+      <c r="J110" s="3">
+        <v>6.8</v>
+      </c>
+      <c r="K110" s="4">
+        <v>4.202</v>
+      </c>
+      <c r="L110" s="5">
+        <v>0.198</v>
+      </c>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+      <c r="O110" s="3"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S110" s="4"/>
+      <c r="T110" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H104" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="I104" s="3">
-        <v>8</v>
-      </c>
-      <c r="J104" s="3">
+      <c r="U110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H111" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="I111" s="3">
+        <v>23</v>
+      </c>
+      <c r="J111" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="K111" s="4">
+        <v>5.656</v>
+      </c>
+      <c r="L111" s="5">
+        <v>0.594</v>
+      </c>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+      <c r="O111" s="3"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S111" s="4"/>
+      <c r="T111" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H112" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="I112" s="3">
+        <v>5.15</v>
+      </c>
+      <c r="J112" s="3">
+        <v>12</v>
+      </c>
+      <c r="K112" s="4">
+        <v>3.603</v>
+      </c>
+      <c r="L112" s="5">
+        <v>0.197</v>
+      </c>
+      <c r="M112" s="3"/>
+      <c r="N112" s="3"/>
+      <c r="O112" s="3"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S112" s="4"/>
+      <c r="T112" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H113" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="I113" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="J113" s="3">
+        <v>24</v>
+      </c>
+      <c r="K113" s="4">
+        <v>4.959</v>
+      </c>
+      <c r="L113" s="5">
+        <v>0.441</v>
+      </c>
+      <c r="M113" s="3"/>
+      <c r="N113" s="3"/>
+      <c r="O113" s="3"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S113" s="4"/>
+      <c r="T113" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H114" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="I114" s="3">
+        <v>8.75</v>
+      </c>
+      <c r="J114" s="3">
+        <v>7.25</v>
+      </c>
+      <c r="K114" s="4">
+        <v>3.965</v>
+      </c>
+      <c r="L114" s="5">
+        <v>0.435</v>
+      </c>
+      <c r="M114" s="3"/>
+      <c r="N114" s="3"/>
+      <c r="O114" s="3"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S114" s="4"/>
+      <c r="T114" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" s="3">
+        <v>7.75</v>
+      </c>
+      <c r="I115" s="3">
+        <v>9</v>
+      </c>
+      <c r="J115" s="3">
+        <v>29</v>
+      </c>
+      <c r="K115" s="4">
+        <v>6.868</v>
+      </c>
+      <c r="L115" s="5">
+        <v>0.882</v>
+      </c>
+      <c r="M115" s="3"/>
+      <c r="N115" s="3"/>
+      <c r="O115" s="3"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S115" s="4"/>
+      <c r="T115" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H116" s="3">
+        <v>4.1</v>
+      </c>
+      <c r="I116" s="3">
+        <v>6</v>
+      </c>
+      <c r="J116" s="3">
+        <v>11</v>
+      </c>
+      <c r="K116" s="4">
+        <v>3.882</v>
+      </c>
+      <c r="L116" s="5">
+        <v>0.218</v>
+      </c>
+      <c r="M116" s="3"/>
+      <c r="N116" s="3"/>
+      <c r="O116" s="3"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S116" s="4"/>
+      <c r="T116" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U116" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V116" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H117" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="I117" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="J117" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="K117" s="4">
+        <v>5.337</v>
+      </c>
+      <c r="L117" s="5">
+        <v>0.463</v>
+      </c>
+      <c r="M117" s="3"/>
+      <c r="N117" s="3"/>
+      <c r="O117" s="3"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S117" s="4"/>
+      <c r="T117" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K104" s="4">
-        <v>6.118</v>
-      </c>
-      <c r="L104" s="5">
-        <v>0.382</v>
-      </c>
-      <c r="M104" s="3">
-        <v>6.7</v>
-      </c>
-      <c r="N104" s="3">
-        <v>8</v>
-      </c>
-      <c r="O104" s="3">
+      <c r="D118" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P104" s="4">
-        <v>6.222</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>0.478</v>
-      </c>
-      <c r="R104" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="S104" s="4">
-        <v>0.096</v>
-      </c>
-      <c r="T104" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="U104" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V104" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W104" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="X104" s="2" t="s">
+      <c r="F118" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="I118" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="J118" s="3">
+        <v>23</v>
+      </c>
+      <c r="K118" s="4">
+        <v>4.307</v>
+      </c>
+      <c r="L118" s="5">
+        <v>0.393</v>
+      </c>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+      <c r="O118" s="3"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S118" s="4"/>
+      <c r="T118" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U118" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V118" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X118" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H119" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="I119" s="3">
+        <v>12</v>
+      </c>
+      <c r="J119" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="K119" s="4">
+        <v>4.11</v>
+      </c>
+      <c r="L119" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="M119" s="3"/>
+      <c r="N119" s="3"/>
+      <c r="O119" s="3"/>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S119" s="4"/>
+      <c r="T119" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="U119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="X119" s="2" t="s">
         <v>30</v>
       </c>
     </row>
@@ -9542,33 +10550,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="B2">
         <v>328</v>
@@ -9594,7 +10602,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B3">
         <v>327</v>
@@ -9620,7 +10628,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="B4">
         <v>319</v>
@@ -9646,7 +10654,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B5">
         <v>311</v>
@@ -9672,7 +10680,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B6">
         <v>303</v>
@@ -9698,7 +10706,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B7">
         <v>285</v>
@@ -9724,7 +10732,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B8">
         <v>276</v>
@@ -9750,7 +10758,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B9">
         <v>255</v>
@@ -9776,7 +10784,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="B10">
         <v>235</v>
@@ -9802,7 +10810,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B11">
         <v>212</v>
@@ -9828,7 +10836,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -9847,43 +10855,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C5" s="13">
         <v>33</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -9891,35 +10899,35 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -9942,7 +10950,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
@@ -9965,7 +10973,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="B11" s="15">
         <v>20</v>
@@ -9988,7 +10996,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="B12" s="16">
         <v>33</v>
@@ -10011,7 +11019,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B13" s="2">
         <v>12</v>
@@ -10034,7 +11042,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="B14" s="2">
         <v>12</v>
@@ -10057,7 +11065,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B15" s="15">
         <v>18</v>
@@ -10080,7 +11088,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -10103,7 +11111,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="B17" s="15">
         <v>25</v>
@@ -10126,7 +11134,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -10165,25 +11173,25 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="B4">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="B5">
         <v>67</v>
@@ -10191,7 +11199,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="B6">
         <v>100</v>
@@ -10199,7 +11207,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -10207,7 +11215,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="B8" s="18">
         <v>0.14</v>
@@ -10215,7 +11223,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="B9" s="19">
         <v>0.596</v>
@@ -10223,7 +11231,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="B10" s="19">
         <v>0.583</v>
@@ -10231,7 +11239,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="B11" s="19">
         <v>0.598</v>
@@ -10239,35 +11247,35 @@
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -10277,15 +11285,15 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.557</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="B16">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C16">
         <v>75</v>
@@ -10295,42 +11303,42 @@
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.567</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -10350,7 +11358,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -10370,7 +11378,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -10390,7 +11398,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -10410,7 +11418,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B25">
         <v>6</v>
@@ -10430,7 +11438,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="B26">
         <v>7</v>
@@ -10450,7 +11458,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -10470,7 +11478,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -10490,7 +11498,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="B29">
         <v>5</v>
@@ -10510,7 +11518,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -10530,7 +11538,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -10550,7 +11558,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="B32">
         <v>7</v>
@@ -10570,7 +11578,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -10590,7 +11598,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -10610,7 +11618,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -10630,7 +11638,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -10650,7 +11658,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -10670,7 +11678,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -10690,7 +11698,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -10710,7 +11718,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -10730,7 +11738,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -10750,7 +11758,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -10770,7 +11778,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -10790,7 +11798,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -10806,7 +11814,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -10822,7 +11830,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -10842,7 +11850,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -10862,7 +11870,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -10882,7 +11890,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10898,7 +11906,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -10914,7 +11922,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -10934,7 +11942,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -10954,7 +11962,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -10970,7 +11978,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -10986,7 +11994,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -11002,7 +12010,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -11018,7 +12026,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -11038,7 +12046,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -11054,7 +12062,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -11070,7 +12078,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -11086,7 +12094,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -11102,7 +12110,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -11118,7 +12126,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -11134,7 +12142,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -11150,7 +12158,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -11166,7 +12174,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -11182,7 +12190,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -11198,7 +12206,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -11214,7 +12222,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -11230,7 +12238,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -11246,7 +12254,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -11262,7 +12270,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -11278,7 +12286,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -11298,7 +12306,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -11314,32 +12322,32 @@
     </row>
     <row r="76" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
     </row>
     <row r="77" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="B78">
         <v>11</v>
@@ -11359,7 +12367,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -11379,7 +12387,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="B80">
         <v>29</v>
@@ -11399,7 +12407,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -11419,7 +12427,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="B82">
         <v>20</v>
@@ -11439,12 +12447,12 @@
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -11463,7 +12471,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -11473,22 +12481,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -11498,17 +12506,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -11518,32 +12526,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -11553,22 +12561,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -11578,32 +12586,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -11613,27 +12621,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -11643,17 +12651,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="613">
   <si>
     <t>日期</t>
   </si>
@@ -1325,6 +1325,9 @@
     <t>09-28 17:00 / 09-29 11:00</t>
   </si>
   <si>
+    <t>09-30 11:00</t>
+  </si>
+  <si>
     <t>09-29 18:00</t>
   </si>
   <si>
@@ -1409,6 +1412,9 @@
     <t>09-30 14:00</t>
   </si>
   <si>
+    <t>09-29 17:00 / 09-30 11:00</t>
+  </si>
+  <si>
     <t>09-30 18:30</t>
   </si>
   <si>
@@ -1466,10 +1472,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-28（共 385 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-28，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-29（共 386 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-29，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1493,7 +1499,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-29T17:00:05+08:00）</t>
+    <t>统计（截至 2026-09-30T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -9516,16 +9522,16 @@
         <v>435</v>
       </c>
       <c r="U103" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V103" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W103" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W103" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X103" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.25">
@@ -9545,7 +9551,7 @@
         <v>264</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>32</v>
@@ -9575,19 +9581,19 @@
       </c>
       <c r="S104" s="4"/>
       <c r="T104" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U104" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="V104" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W104" s="2" t="s">
-        <v>30</v>
+        <v>322</v>
+      </c>
+      <c r="W104" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X104" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.25">
@@ -9598,16 +9604,16 @@
         <v>198</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>328</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G105" s="6" t="s">
         <v>32</v>
@@ -9637,19 +9643,19 @@
       </c>
       <c r="S105" s="4"/>
       <c r="T105" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U105" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V105" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W105" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W105" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X105" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.25">
@@ -9660,16 +9666,16 @@
         <v>201</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>32</v>
@@ -9699,19 +9705,19 @@
       </c>
       <c r="S106" s="4"/>
       <c r="T106" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U106" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="V106" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W106" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
+      </c>
+      <c r="W106" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X106" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.25">
@@ -9719,19 +9725,19 @@
         <v>432</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>315</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>32</v>
@@ -9761,19 +9767,19 @@
       </c>
       <c r="S107" s="4"/>
       <c r="T107" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U107" s="2" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="V107" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W107" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W107" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X107" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.25">
@@ -9781,19 +9787,19 @@
         <v>432</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G108" s="6" t="s">
         <v>32</v>
@@ -9823,19 +9829,19 @@
       </c>
       <c r="S108" s="4"/>
       <c r="T108" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U108" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="V108" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W108" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W108" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X108" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.25">
@@ -9843,19 +9849,19 @@
         <v>432</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>177</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>272</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G109" s="6" t="s">
         <v>32</v>
@@ -9897,19 +9903,19 @@
         <v>0.378</v>
       </c>
       <c r="T109" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U109" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V109" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W109" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W109" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X109" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.25">
@@ -9917,7 +9923,7 @@
         <v>432</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>237</v>
@@ -9929,7 +9935,7 @@
         <v>361</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>46</v>
@@ -9959,19 +9965,19 @@
       </c>
       <c r="S110" s="4"/>
       <c r="T110" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U110" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="V110" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W110" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
+      </c>
+      <c r="W110" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X110" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.25">
@@ -9979,7 +9985,7 @@
         <v>432</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>237</v>
@@ -9991,7 +9997,7 @@
         <v>363</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>32</v>
@@ -10021,19 +10027,19 @@
       </c>
       <c r="S111" s="4"/>
       <c r="T111" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U111" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
       </c>
       <c r="V111" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W111" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W111" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X111" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.25">
@@ -10041,7 +10047,7 @@
         <v>432</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>237</v>
@@ -10053,7 +10059,7 @@
         <v>360</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>32</v>
@@ -10083,19 +10089,19 @@
       </c>
       <c r="S112" s="4"/>
       <c r="T112" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U112" s="2" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="V112" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W112" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W112" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X112" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
@@ -10103,19 +10109,19 @@
         <v>432</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>343</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>32</v>
@@ -10145,19 +10151,19 @@
       </c>
       <c r="S113" s="4"/>
       <c r="T113" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U113" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V113" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W113" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W113" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X113" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.25">
@@ -10165,7 +10171,7 @@
         <v>432</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>237</v>
@@ -10177,7 +10183,7 @@
         <v>346</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>32</v>
@@ -10207,19 +10213,19 @@
       </c>
       <c r="S114" s="4"/>
       <c r="T114" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U114" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="V114" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W114" s="2" t="s">
-        <v>30</v>
+        <v>286</v>
+      </c>
+      <c r="W114" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X114" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.25">
@@ -10227,7 +10233,7 @@
         <v>432</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>237</v>
@@ -10239,7 +10245,7 @@
         <v>357</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>32</v>
@@ -10269,19 +10275,19 @@
       </c>
       <c r="S115" s="4"/>
       <c r="T115" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U115" s="2" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="V115" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W115" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
+      </c>
+      <c r="W115" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X115" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.25">
@@ -10289,7 +10295,7 @@
         <v>432</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>237</v>
@@ -10301,7 +10307,7 @@
         <v>347</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>32</v>
@@ -10331,19 +10337,19 @@
       </c>
       <c r="S116" s="4"/>
       <c r="T116" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U116" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V116" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W116" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="W116" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X116" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.25">
@@ -10351,7 +10357,7 @@
         <v>432</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>222</v>
@@ -10363,7 +10369,7 @@
         <v>372</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>32</v>
@@ -10393,7 +10399,7 @@
       </c>
       <c r="S117" s="4"/>
       <c r="T117" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U117" s="2" t="s">
         <v>30</v>
@@ -10410,7 +10416,7 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>205</v>
@@ -10425,7 +10431,7 @@
         <v>28</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>32</v>
@@ -10445,17 +10451,29 @@
       <c r="L118" s="5">
         <v>0.393</v>
       </c>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
-      <c r="O118" s="3"/>
-      <c r="P118" s="4"/>
-      <c r="Q118" s="4"/>
-      <c r="R118" s="2" t="s">
+      <c r="M118" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="N118" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="O118" s="3">
         <v>30</v>
       </c>
-      <c r="S118" s="4"/>
+      <c r="P118" s="4">
+        <v>4.648</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>0.052</v>
+      </c>
+      <c r="R118" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="S118" s="4">
+        <v>-0.341</v>
+      </c>
       <c r="T118" s="2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="U118" s="2" t="s">
         <v>30</v>
@@ -10472,7 +10490,7 @@
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>210</v>
@@ -10487,10 +10505,10 @@
         <v>55</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>46</v>
+        <v>466</v>
+      </c>
+      <c r="G119" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="H119" s="3">
         <v>4.4</v>
@@ -10507,17 +10525,29 @@
       <c r="L119" s="5">
         <v>0.29</v>
       </c>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-      <c r="O119" s="3"/>
-      <c r="P119" s="4"/>
-      <c r="Q119" s="4"/>
-      <c r="R119" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S119" s="4"/>
+      <c r="M119" s="3">
+        <v>4.4</v>
+      </c>
+      <c r="N119" s="3">
+        <v>12</v>
+      </c>
+      <c r="O119" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="P119" s="4">
+        <v>4.11</v>
+      </c>
+      <c r="Q119" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="S119" s="4">
+        <v>0</v>
+      </c>
       <c r="T119" s="2" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="U119" s="2" t="s">
         <v>30</v>
@@ -10550,36 +10580,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -10588,7 +10618,7 @@
         <v>57</v>
       </c>
       <c r="E2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2">
         <v>70</v>
@@ -10602,10 +10632,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B3">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -10623,15 +10653,15 @@
         <v>45</v>
       </c>
       <c r="H3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B4">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -10643,7 +10673,7 @@
         <v>68</v>
       </c>
       <c r="F4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>46</v>
@@ -10654,10 +10684,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B5">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C5">
         <v>15</v>
@@ -10666,7 +10696,7 @@
         <v>52</v>
       </c>
       <c r="E5">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F5">
         <v>52</v>
@@ -10680,10 +10710,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B6">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6">
         <v>19</v>
@@ -10701,15 +10731,15 @@
         <v>41</v>
       </c>
       <c r="H6">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C7">
         <v>17</v>
@@ -10721,7 +10751,7 @@
         <v>64</v>
       </c>
       <c r="F7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>53</v>
@@ -10732,10 +10762,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B8">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -10744,7 +10774,7 @@
         <v>38</v>
       </c>
       <c r="E8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>61</v>
@@ -10758,10 +10788,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B9">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>16</v>
@@ -10773,7 +10803,7 @@
         <v>63</v>
       </c>
       <c r="F9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>25</v>
@@ -10784,10 +10814,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B10">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C10">
         <v>11</v>
@@ -10796,7 +10826,7 @@
         <v>47</v>
       </c>
       <c r="E10">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10">
         <v>60</v>
@@ -10810,10 +10840,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B11">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C11">
         <v>18</v>
@@ -10822,7 +10852,7 @@
         <v>27</v>
       </c>
       <c r="E11">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11">
         <v>53</v>
@@ -10836,7 +10866,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -10855,43 +10885,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C5" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -10899,73 +10929,73 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B9" s="2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="15">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="C9" s="15">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2">
-        <v>6</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
       <c r="F9" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B10" s="2">
+        <v>4</v>
+      </c>
+      <c r="C10" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2">
         <v>3</v>
       </c>
-      <c r="C10" s="2">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="2">
-        <v>1</v>
-      </c>
       <c r="F10" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
@@ -10973,186 +11003,186 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B11" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="15">
+        <v>28</v>
+      </c>
+      <c r="G11" s="2">
         <v>1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="15">
-        <v>27</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B12" s="16">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>25</v>
+      </c>
+      <c r="F12" s="2">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2">
         <v>1</v>
-      </c>
-      <c r="E12" s="15">
-        <v>24</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B13" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B14" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2">
         <v>3</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
         <v>2</v>
       </c>
-      <c r="E14" s="2">
-        <v>6</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
         <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B15" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5</v>
+      </c>
+      <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="D15" s="2">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
       <c r="G15" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2">
         <v>5</v>
-      </c>
-      <c r="D16" s="2">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>13</v>
-      </c>
-      <c r="G16" s="2">
-        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B17" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
       <c r="F17" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11173,17 +11203,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -11191,23 +11221,23 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -11215,23 +11245,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B8" s="18">
-        <v>0.14</v>
+        <v>0.12280701754385964</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B9" s="19">
-        <v>0.596</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B10" s="19">
         <v>0.583</v>
@@ -11239,106 +11269,106 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B11" s="19">
-        <v>0.598</v>
+        <v>0.595</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.516</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B16">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D16">
         <v>10</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.572</v>
+        <v>0.565</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -11358,7 +11388,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -11378,7 +11408,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -11398,56 +11428,56 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="18">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F24" s="19">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="20">
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="F25" s="19">
-        <v>0.224</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" s="21">
         <v>0</v>
@@ -11458,7 +11488,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -11478,7 +11508,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -11498,36 +11528,36 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E29" s="21">
         <v>0</v>
       </c>
       <c r="F29" s="19">
-        <v>0.429</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="18">
         <v>0</v>
@@ -11538,7 +11568,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -11558,47 +11588,47 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E32" s="21">
         <v>0</v>
       </c>
       <c r="F32" s="19">
-        <v>0.566</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E33" s="20">
-        <v>0.2</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="F33" s="19">
-        <v>0.625</v>
+        <v>0.623</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -11618,27 +11648,27 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="18">
         <v>0</v>
       </c>
       <c r="F35" s="19">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -11658,7 +11688,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -11678,27 +11708,27 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38" s="18">
+        <v>5</v>
+      </c>
+      <c r="E38" s="21">
         <v>0</v>
       </c>
       <c r="F38" s="19">
-        <v>0.88</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -11718,7 +11748,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -11738,27 +11768,27 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" s="21">
         <v>0</v>
       </c>
       <c r="F41" s="19">
-        <v>1.035</v>
+        <v>1.033</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -11778,7 +11808,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -11798,23 +11828,27 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="19"/>
+        <v>1</v>
+      </c>
+      <c r="E44" s="18">
+        <v>0</v>
+      </c>
+      <c r="F44" s="19">
+        <v>1.183</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -11830,7 +11864,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -11850,7 +11884,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -11870,7 +11904,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -11890,7 +11924,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -11906,7 +11940,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -11922,7 +11956,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -11942,7 +11976,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -11962,7 +11996,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -11978,7 +12012,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -11994,7 +12028,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -12010,7 +12044,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -12026,7 +12060,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -12046,7 +12080,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -12062,7 +12096,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -12078,7 +12112,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -12094,7 +12128,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -12110,7 +12144,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -12126,7 +12160,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -12142,7 +12176,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -12158,7 +12192,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -12174,7 +12208,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -12190,7 +12224,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -12206,7 +12240,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -12222,7 +12256,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -12238,7 +12272,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -12254,7 +12288,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -12270,7 +12304,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -12286,7 +12320,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -12306,7 +12340,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -12322,32 +12356,32 @@
     </row>
     <row r="76" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="77" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B78">
         <v>11</v>
@@ -12367,7 +12401,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -12387,19 +12421,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B80">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E80" s="21">
-        <v>0.10344827586206896</v>
+        <v>0.1</v>
       </c>
       <c r="F80" s="22">
         <v>-0.001</v>
@@ -12407,7 +12441,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -12427,32 +12461,32 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E82" s="21">
-        <v>0.1</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="F82" s="22">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -12471,7 +12505,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -12481,22 +12515,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -12506,17 +12540,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -12526,32 +12560,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -12561,22 +12595,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -12586,32 +12620,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -12621,27 +12655,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -12651,17 +12685,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="614">
   <si>
     <t>日期</t>
   </si>
@@ -1325,7 +1325,7 @@
     <t>09-28 17:00 / 09-29 11:00</t>
   </si>
   <si>
-    <t>09-30 11:00</t>
+    <t>09-30 17:00</t>
   </si>
   <si>
     <t>09-29 18:00</t>
@@ -1418,6 +1418,9 @@
     <t>09-30 18:30</t>
   </si>
   <si>
+    <t>09-30 11:00 / 09-30 17:00</t>
+  </si>
+  <si>
     <t>编号</t>
   </si>
   <si>
@@ -1499,7 +1502,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-30T11:00:04+08:00）</t>
+    <t>统计（截至 2026-09-30T17:00:06+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -10402,16 +10405,16 @@
         <v>438</v>
       </c>
       <c r="U117" s="2" t="s">
-        <v>30</v>
+        <v>381</v>
       </c>
       <c r="V117" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W117" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W117" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X117" s="2" t="s">
-        <v>30</v>
+        <v>436</v>
       </c>
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.25">
@@ -10507,8 +10510,8 @@
       <c r="F119" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="G119" s="6" t="s">
-        <v>32</v>
+      <c r="G119" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H119" s="3">
         <v>4.4</v>
@@ -10526,28 +10529,28 @@
         <v>0.29</v>
       </c>
       <c r="M119" s="3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="N119" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O119" s="3">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="P119" s="4">
-        <v>4.11</v>
+        <v>4.286</v>
       </c>
       <c r="Q119" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="R119" s="6" t="s">
-        <v>80</v>
+        <v>0.314</v>
+      </c>
+      <c r="R119" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="S119" s="4">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="T119" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="U119" s="2" t="s">
         <v>30</v>
@@ -10580,33 +10583,33 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B2">
         <v>329</v>
@@ -10632,7 +10635,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B3">
         <v>328</v>
@@ -10658,7 +10661,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B4">
         <v>320</v>
@@ -10684,7 +10687,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5">
         <v>312</v>
@@ -10710,7 +10713,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B6">
         <v>304</v>
@@ -10736,7 +10739,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B7">
         <v>286</v>
@@ -10762,7 +10765,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B8">
         <v>277</v>
@@ -10788,7 +10791,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -10814,7 +10817,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -10840,7 +10843,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -10866,7 +10869,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -10885,43 +10888,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C5" s="13">
         <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -10929,35 +10932,35 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -10980,7 +10983,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B10" s="2">
         <v>4</v>
@@ -11003,7 +11006,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B11" s="15">
         <v>21</v>
@@ -11026,7 +11029,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B12" s="16">
         <v>34</v>
@@ -11049,7 +11052,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B13" s="2">
         <v>13</v>
@@ -11072,7 +11075,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -11095,7 +11098,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B15" s="15">
         <v>19</v>
@@ -11118,7 +11121,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -11141,7 +11144,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B17" s="15">
         <v>26</v>
@@ -11164,7 +11167,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -11203,17 +11206,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -11221,7 +11224,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B5">
         <v>69</v>
@@ -11229,15 +11232,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B6">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -11245,23 +11248,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B8" s="18">
-        <v>0.12280701754385964</v>
+        <v>0.12173913043478261</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B9" s="19">
-        <v>0.594</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B10" s="19">
         <v>0.583</v>
@@ -11269,43 +11272,43 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B11" s="19">
-        <v>0.595</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>14</v>
@@ -11315,60 +11318,60 @@
       </c>
       <c r="E15" s="18"/>
       <c r="F15" s="19">
-        <v>0.532</v>
+        <v>0.517</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B16">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16">
         <v>10</v>
       </c>
       <c r="E16" s="18"/>
       <c r="F16" s="19">
-        <v>0.565</v>
+        <v>0.568</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -11388,7 +11391,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B22">
         <v>3</v>
@@ -11408,7 +11411,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -11428,7 +11431,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -11448,7 +11451,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -11468,7 +11471,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B26">
         <v>8</v>
@@ -11488,7 +11491,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B27">
         <v>6</v>
@@ -11508,7 +11511,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -11528,7 +11531,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -11548,27 +11551,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30" s="18">
+        <v>5</v>
+      </c>
+      <c r="E30" s="21">
         <v>0</v>
       </c>
       <c r="F30" s="19">
-        <v>0.475</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -11588,7 +11591,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B32">
         <v>8</v>
@@ -11608,7 +11611,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B33">
         <v>11</v>
@@ -11628,7 +11631,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -11648,7 +11651,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -11668,7 +11671,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -11688,7 +11691,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -11708,7 +11711,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -11728,7 +11731,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -11748,7 +11751,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -11768,7 +11771,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -11788,7 +11791,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -11808,7 +11811,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -11828,7 +11831,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -11848,7 +11851,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -11864,7 +11867,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -11884,7 +11887,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -11904,7 +11907,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -11924,7 +11927,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -11940,7 +11943,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -11956,7 +11959,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -11976,7 +11979,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -11996,7 +11999,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -12012,7 +12015,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -12028,7 +12031,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -12044,7 +12047,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -12060,7 +12063,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -12080,7 +12083,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -12096,7 +12099,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -12112,7 +12115,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -12128,7 +12131,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -12144,7 +12147,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -12160,7 +12163,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -12176,7 +12179,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -12192,7 +12195,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -12208,7 +12211,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -12224,7 +12227,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -12240,7 +12243,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -12256,7 +12259,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -12272,7 +12275,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -12288,7 +12291,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -12304,7 +12307,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -12320,7 +12323,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -12340,7 +12343,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -12356,32 +12359,32 @@
     </row>
     <row r="76" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="77" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B78">
         <v>11</v>
@@ -12401,7 +12404,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -12421,7 +12424,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B80">
         <v>30</v>
@@ -12441,7 +12444,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -12461,7 +12464,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B82">
         <v>21</v>
@@ -12481,12 +12484,12 @@
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -12505,7 +12508,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -12515,22 +12518,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -12540,17 +12543,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -12560,32 +12563,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -12595,22 +12598,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -12620,32 +12623,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -12655,27 +12658,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -12685,17 +12688,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="615">
   <si>
     <t>日期</t>
   </si>
@@ -1415,6 +1415,9 @@
     <t>09-29 17:00 / 09-30 11:00</t>
   </si>
   <si>
+    <t>10-01 11:00</t>
+  </si>
+  <si>
     <t>09-30 18:30</t>
   </si>
   <si>
@@ -1475,10 +1478,10 @@
     <t>010</t>
   </si>
   <si>
-    <t>数据范围：2025-08-17 ~ 2026-09-29（共 386 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
-  </si>
-  <si>
-    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-29，警戒线 30 次）</t>
+    <t>数据范围：2025-08-17 ~ 2026-09-30（共 387 天）；灰色编号 = 近 7 天未出现（已停用）。</t>
+  </si>
+  <si>
+    <t>编号追踪：单元格 = 该编号该档进球数的"连续未出现次数"（该编号每踢一场未出该档 +1；截至 2026-09-30，警戒线 30 次）</t>
   </si>
   <si>
     <t>⚠ 达到警戒线的项目（按连续未出现次数排序）</t>
@@ -1502,7 +1505,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-09-30T17:00:06+08:00）</t>
+    <t>统计（截至 2026-10-01T11:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
@@ -10479,16 +10482,16 @@
         <v>465</v>
       </c>
       <c r="U118" s="2" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="V118" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W118" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
+      </c>
+      <c r="W118" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X118" s="2" t="s">
-        <v>30</v>
+        <v>466</v>
       </c>
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.25">
@@ -10508,7 +10511,7 @@
         <v>55</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>46</v>
@@ -10550,19 +10553,19 @@
         <v>0.024</v>
       </c>
       <c r="T119" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U119" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="V119" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W119" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="W119" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="X119" s="2" t="s">
-        <v>30</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -10583,36 +10586,36 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C2">
         <v>24</v>
@@ -10624,7 +10627,7 @@
         <v>69</v>
       </c>
       <c r="F2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2">
         <v>52</v>
@@ -10635,10 +10638,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B3">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C3">
         <v>26</v>
@@ -10647,7 +10650,7 @@
         <v>58</v>
       </c>
       <c r="E3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3">
         <v>73</v>
@@ -10661,7 +10664,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B4">
         <v>320</v>
@@ -10687,7 +10690,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B5">
         <v>312</v>
@@ -10713,7 +10716,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B6">
         <v>304</v>
@@ -10739,7 +10742,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B7">
         <v>286</v>
@@ -10765,7 +10768,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B8">
         <v>277</v>
@@ -10791,7 +10794,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B9">
         <v>256</v>
@@ -10817,7 +10820,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B10">
         <v>236</v>
@@ -10843,7 +10846,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B11">
         <v>213</v>
@@ -10869,7 +10872,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -10888,43 +10891,43 @@
   <sheetData>
     <row r="1" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C5" s="13">
         <v>34</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E5" s="13">
         <v>15</v>
@@ -10932,81 +10935,81 @@
     </row>
     <row r="7" spans="1:1" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B9" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B10" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <v>3</v>
       </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2">
-        <v>17</v>
+      <c r="F10" s="15">
+        <v>18</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B11" s="15">
         <v>21</v>
@@ -11029,7 +11032,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B12" s="16">
         <v>34</v>
@@ -11052,7 +11055,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B13" s="2">
         <v>13</v>
@@ -11075,7 +11078,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B14" s="2">
         <v>13</v>
@@ -11098,7 +11101,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B15" s="15">
         <v>19</v>
@@ -11121,7 +11124,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B16" s="2">
         <v>1</v>
@@ -11144,7 +11147,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B17" s="15">
         <v>26</v>
@@ -11167,7 +11170,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -11206,17 +11209,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B4">
         <v>118</v>
@@ -11224,7 +11227,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B5">
         <v>69</v>
@@ -11232,15 +11235,15 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B6">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B7">
         <v>14</v>
@@ -11248,23 +11251,23 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B8" s="18">
-        <v>0.12173913043478261</v>
+        <v>0.11965811965811966</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B9" s="19">
-        <v>0.593</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B10" s="19">
         <v>0.583</v>
@@ -11272,46 +11275,46 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B11" s="19">
-        <v>0.594</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="13" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B15">
         <v>15</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -11323,13 +11326,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B16">
         <v>91</v>
       </c>
       <c r="C16">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16">
         <v>10</v>
@@ -11341,37 +11344,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -11391,27 +11394,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="18">
         <v>0</v>
       </c>
       <c r="F22" s="19">
-        <v>0.069</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -11431,7 +11434,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -11451,7 +11454,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B25">
         <v>7</v>
@@ -11471,7 +11474,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B26">
         <v>8</v>
@@ -11491,27 +11494,27 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E27" s="20">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F27" s="19">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B28">
         <v>10</v>
@@ -11531,7 +11534,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B29">
         <v>7</v>
@@ -11551,7 +11554,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B30">
         <v>5</v>
@@ -11571,7 +11574,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -11591,7 +11594,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B32">
         <v>8</v>
@@ -11611,7 +11614,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B33">
         <v>11</v>
@@ -11631,7 +11634,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -11651,7 +11654,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -11671,7 +11674,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -11691,7 +11694,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -11711,7 +11714,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -11731,7 +11734,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -11751,7 +11754,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -11771,7 +11774,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B41">
         <v>6</v>
@@ -11791,7 +11794,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -11811,7 +11814,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -11831,7 +11834,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -11851,7 +11854,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -11867,7 +11870,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -11887,7 +11890,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -11907,7 +11910,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -11927,7 +11930,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -11943,7 +11946,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -11959,7 +11962,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -11979,7 +11982,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -11999,7 +12002,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -12015,7 +12018,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -12031,7 +12034,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -12047,7 +12050,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -12063,7 +12066,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -12083,7 +12086,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -12099,7 +12102,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -12115,7 +12118,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -12131,7 +12134,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -12147,7 +12150,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -12163,7 +12166,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -12179,7 +12182,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -12195,7 +12198,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -12211,7 +12214,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -12227,7 +12230,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -12243,7 +12246,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -12259,7 +12262,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -12275,7 +12278,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -12291,7 +12294,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -12307,7 +12310,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -12323,7 +12326,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -12343,7 +12346,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -12359,52 +12362,52 @@
     </row>
     <row r="76" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="77" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E78" s="21">
-        <v>0.09090909090909091</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="F78" s="22">
-        <v>-0.199</v>
+        <v>-0.211</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B79">
         <v>3</v>
@@ -12424,27 +12427,27 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B80">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E80" s="21">
-        <v>0.1</v>
+        <v>0.0967741935483871</v>
       </c>
       <c r="F80" s="22">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -12464,7 +12467,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B82">
         <v>21</v>
@@ -12484,12 +12487,12 @@
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -12508,7 +12511,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -12518,22 +12521,22 @@
     </row>
     <row r="3" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -12543,17 +12546,17 @@
     </row>
     <row r="8" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -12563,32 +12566,32 @@
     </row>
     <row r="12" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -12598,22 +12601,22 @@
     </row>
     <row r="19" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -12623,32 +12626,32 @@
     </row>
     <row r="24" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
@@ -12658,27 +12661,27 @@
     </row>
     <row r="31" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -12688,17 +12691,17 @@
     </row>
     <row r="37" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -1505,7 +1505,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-10-01T11:00:05+08:00）</t>
+    <t>统计（截至 2026-10-01T17:00:05+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>

--- a/docs/excel/竞彩1球-差值记录.xlsx
+++ b/docs/excel/竞彩1球-差值记录.xlsx
@@ -1505,7 +1505,7 @@
     <t>全部编号 × 进球数矩阵（数字=连续未出现次数；"从未"=历史数据中未出现过）</t>
   </si>
   <si>
-    <t>统计（截至 2026-10-01T17:00:05+08:00）</t>
+    <t>统计（截至 2026-10-02T11:00:04+08:00）</t>
   </si>
   <si>
     <t>总体概览</t>
